--- a/research/traditional_assets/database/data/philippines/philippines_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_beverage_soft.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0443</v>
+        <v>0.00928</v>
       </c>
       <c r="G2">
-        <v>0.04024526198439242</v>
+        <v>0.005827263267429762</v>
       </c>
       <c r="H2">
-        <v>0.04024526198439242</v>
+        <v>0.005827263267429762</v>
       </c>
       <c r="I2">
-        <v>-0.0189520624303233</v>
+        <v>-0.01045785639958377</v>
       </c>
       <c r="J2">
-        <v>-0.0189520624303233</v>
+        <v>-0.01045785639958377</v>
       </c>
       <c r="K2">
-        <v>-2.05</v>
+        <v>-1.39</v>
       </c>
       <c r="L2">
-        <v>-0.01142697881828316</v>
+        <v>-0.007232049947970863</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>19.6</v>
+        <v>36.6</v>
       </c>
       <c r="V2">
-        <v>0.1694036300777874</v>
+        <v>0.2828438948995363</v>
       </c>
       <c r="W2">
-        <v>-0.01284461152882205</v>
+        <v>-0.009297658862876253</v>
       </c>
       <c r="X2">
-        <v>0.06603423370677149</v>
+        <v>0.1153205838144405</v>
       </c>
       <c r="Y2">
-        <v>-0.07887884523559355</v>
+        <v>-0.1246182426773168</v>
       </c>
       <c r="Z2">
-        <v>2.036553524804178</v>
+        <v>1.801312089971884</v>
       </c>
       <c r="AA2">
-        <v>-0.03859688954478375</v>
+        <v>-0.01883786316776007</v>
       </c>
       <c r="AB2">
-        <v>0.06338566363198457</v>
+        <v>0.1123093160940747</v>
       </c>
       <c r="AC2">
-        <v>-0.1019825531767683</v>
+        <v>-0.1311471792618348</v>
       </c>
       <c r="AD2">
-        <v>10.1</v>
+        <v>7.68</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10.1</v>
+        <v>7.68</v>
       </c>
       <c r="AG2">
-        <v>-9.500000000000002</v>
+        <v>-28.92</v>
       </c>
       <c r="AH2">
-        <v>0.08028616852146264</v>
+        <v>0.05602567843594981</v>
       </c>
       <c r="AI2">
-        <v>0.06328320802005012</v>
+        <v>0.05618964003511852</v>
       </c>
       <c r="AJ2">
-        <v>-0.08945386064030134</v>
+        <v>-0.2878184713375797</v>
       </c>
       <c r="AK2">
-        <v>-0.06785714285714287</v>
+        <v>-0.288968824940048</v>
       </c>
       <c r="AL2">
-        <v>0.833</v>
+        <v>0.493</v>
       </c>
       <c r="AM2">
-        <v>0.3659999999999999</v>
+        <v>-0.03000000000000003</v>
       </c>
       <c r="AN2">
-        <v>8.14516129032258</v>
+        <v>4.173913043478261</v>
       </c>
       <c r="AO2">
-        <v>-4.081632653061225</v>
+        <v>-4.077079107505071</v>
       </c>
       <c r="AP2">
-        <v>-7.661290322580647</v>
+        <v>-15.71739130434783</v>
       </c>
       <c r="AQ2">
-        <v>-9.289617486338798</v>
+        <v>66.99999999999993</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0443</v>
+        <v>0.00928</v>
       </c>
       <c r="G3">
-        <v>0.04024526198439242</v>
+        <v>0.005827263267429762</v>
       </c>
       <c r="H3">
-        <v>0.04024526198439242</v>
+        <v>0.005827263267429762</v>
       </c>
       <c r="I3">
-        <v>-0.0189520624303233</v>
+        <v>-0.01045785639958377</v>
       </c>
       <c r="J3">
-        <v>-0.0189520624303233</v>
+        <v>-0.01045785639958377</v>
       </c>
       <c r="K3">
-        <v>-2.05</v>
+        <v>-1.39</v>
       </c>
       <c r="L3">
-        <v>-0.01142697881828316</v>
+        <v>-0.007232049947970863</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.6</v>
+        <v>36.6</v>
       </c>
       <c r="V3">
-        <v>0.1694036300777874</v>
+        <v>0.2828438948995363</v>
       </c>
       <c r="W3">
-        <v>-0.01284461152882205</v>
+        <v>-0.009297658862876253</v>
       </c>
       <c r="X3">
-        <v>0.06603423370677149</v>
+        <v>0.1153205838144405</v>
       </c>
       <c r="Y3">
-        <v>-0.07887884523559355</v>
+        <v>-0.1246182426773168</v>
       </c>
       <c r="Z3">
-        <v>2.036553524804178</v>
+        <v>1.801312089971884</v>
       </c>
       <c r="AA3">
-        <v>-0.03859688954478375</v>
+        <v>-0.01883786316776007</v>
       </c>
       <c r="AB3">
-        <v>0.06338566363198457</v>
+        <v>0.1123093160940747</v>
       </c>
       <c r="AC3">
-        <v>-0.1019825531767683</v>
+        <v>-0.1311471792618348</v>
       </c>
       <c r="AD3">
-        <v>10.1</v>
+        <v>7.68</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10.1</v>
+        <v>7.68</v>
       </c>
       <c r="AG3">
-        <v>-9.500000000000002</v>
+        <v>-28.92</v>
       </c>
       <c r="AH3">
-        <v>0.08028616852146264</v>
+        <v>0.05602567843594981</v>
       </c>
       <c r="AI3">
-        <v>0.06328320802005012</v>
+        <v>0.05618964003511852</v>
       </c>
       <c r="AJ3">
-        <v>-0.08945386064030134</v>
+        <v>-0.2878184713375797</v>
       </c>
       <c r="AK3">
-        <v>-0.06785714285714287</v>
+        <v>-0.288968824940048</v>
       </c>
       <c r="AL3">
-        <v>0.833</v>
+        <v>0.493</v>
       </c>
       <c r="AM3">
-        <v>0.3659999999999999</v>
+        <v>-0.03000000000000003</v>
       </c>
       <c r="AN3">
-        <v>8.14516129032258</v>
+        <v>4.173913043478261</v>
       </c>
       <c r="AO3">
-        <v>-4.081632653061225</v>
+        <v>-4.077079107505071</v>
       </c>
       <c r="AP3">
-        <v>-7.661290322580647</v>
+        <v>-15.71739130434783</v>
       </c>
       <c r="AQ3">
-        <v>-9.289617486338798</v>
+        <v>66.99999999999993</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/philippines/philippines_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_beverage_soft.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="pse_macay" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00928</v>
+        <v>0.0295</v>
+      </c>
+      <c r="E2">
+        <v>-0.342</v>
       </c>
       <c r="G2">
-        <v>0.005827263267429762</v>
+        <v>0.01707097933513028</v>
       </c>
       <c r="H2">
-        <v>0.005827263267429762</v>
+        <v>0.01707097933513028</v>
       </c>
       <c r="I2">
-        <v>-0.01045785639958377</v>
+        <v>0.01293800539083558</v>
       </c>
       <c r="J2">
-        <v>-0.01045785639958377</v>
+        <v>0.006680408012261507</v>
       </c>
       <c r="K2">
-        <v>-1.39</v>
+        <v>1.58</v>
       </c>
       <c r="L2">
-        <v>-0.007232049947970863</v>
+        <v>0.007097933513027854</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>36.6</v>
+        <v>25.3</v>
       </c>
       <c r="V2">
-        <v>0.2828438948995363</v>
+        <v>0.207037643207856</v>
       </c>
       <c r="W2">
-        <v>-0.009297658862876253</v>
+        <v>0.01224806201550388</v>
       </c>
       <c r="X2">
-        <v>0.1153205838144405</v>
+        <v>0.0983263470176213</v>
       </c>
       <c r="Y2">
-        <v>-0.1246182426773168</v>
+        <v>-0.08607828500211742</v>
       </c>
       <c r="Z2">
-        <v>1.801312089971884</v>
+        <v>2.224220623501199</v>
       </c>
       <c r="AA2">
-        <v>-0.01883786316776007</v>
+        <v>0.01485870127427469</v>
       </c>
       <c r="AB2">
-        <v>0.1123093160940747</v>
+        <v>0.08837851643093872</v>
       </c>
       <c r="AC2">
-        <v>-0.1311471792618348</v>
+        <v>-0.07351981515666403</v>
       </c>
       <c r="AD2">
-        <v>7.68</v>
+        <v>37.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.68</v>
+        <v>37.2</v>
       </c>
       <c r="AG2">
-        <v>-28.92</v>
+        <v>11.9</v>
       </c>
       <c r="AH2">
-        <v>0.05602567843594981</v>
+        <v>0.2333751568381431</v>
       </c>
       <c r="AI2">
-        <v>0.05618964003511852</v>
+        <v>0.2141623488773748</v>
       </c>
       <c r="AJ2">
-        <v>-0.2878184713375797</v>
+        <v>0.08873974645786728</v>
       </c>
       <c r="AK2">
-        <v>-0.288968824940048</v>
+        <v>0.08018867924528303</v>
       </c>
       <c r="AL2">
-        <v>0.493</v>
+        <v>1.79</v>
       </c>
       <c r="AM2">
-        <v>-0.03000000000000003</v>
+        <v>1.429</v>
       </c>
       <c r="AN2">
-        <v>4.173913043478261</v>
+        <v>5.2991452991453</v>
       </c>
       <c r="AO2">
-        <v>-4.077079107505071</v>
+        <v>1.608938547486033</v>
       </c>
       <c r="AP2">
-        <v>-15.71739130434783</v>
+        <v>1.695156695156696</v>
       </c>
       <c r="AQ2">
-        <v>66.99999999999993</v>
+        <v>2.015395381385584</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00928</v>
+        <v>0.0295</v>
+      </c>
+      <c r="E3">
+        <v>-0.342</v>
       </c>
       <c r="G3">
-        <v>0.005827263267429762</v>
+        <v>0.01707097933513028</v>
       </c>
       <c r="H3">
-        <v>0.005827263267429762</v>
+        <v>0.01707097933513028</v>
       </c>
       <c r="I3">
-        <v>-0.01045785639958377</v>
+        <v>0.01293800539083558</v>
       </c>
       <c r="J3">
-        <v>-0.01045785639958377</v>
+        <v>0.006680408012261507</v>
       </c>
       <c r="K3">
-        <v>-1.39</v>
+        <v>1.58</v>
       </c>
       <c r="L3">
-        <v>-0.007232049947970863</v>
+        <v>0.007097933513027854</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>36.6</v>
+        <v>25.3</v>
       </c>
       <c r="V3">
-        <v>0.2828438948995363</v>
+        <v>0.207037643207856</v>
       </c>
       <c r="W3">
-        <v>-0.009297658862876253</v>
+        <v>0.01224806201550388</v>
       </c>
       <c r="X3">
-        <v>0.1153205838144405</v>
+        <v>0.0983263470176213</v>
       </c>
       <c r="Y3">
-        <v>-0.1246182426773168</v>
+        <v>-0.08607828500211742</v>
       </c>
       <c r="Z3">
-        <v>1.801312089971884</v>
+        <v>2.224220623501199</v>
       </c>
       <c r="AA3">
-        <v>-0.01883786316776007</v>
+        <v>0.01485870127427469</v>
       </c>
       <c r="AB3">
-        <v>0.1123093160940747</v>
+        <v>0.08837851643093872</v>
       </c>
       <c r="AC3">
-        <v>-0.1311471792618348</v>
+        <v>-0.07351981515666403</v>
       </c>
       <c r="AD3">
-        <v>7.68</v>
+        <v>37.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.68</v>
+        <v>37.2</v>
       </c>
       <c r="AG3">
-        <v>-28.92</v>
+        <v>11.9</v>
       </c>
       <c r="AH3">
-        <v>0.05602567843594981</v>
+        <v>0.2333751568381431</v>
       </c>
       <c r="AI3">
-        <v>0.05618964003511852</v>
+        <v>0.2141623488773748</v>
       </c>
       <c r="AJ3">
-        <v>-0.2878184713375797</v>
+        <v>0.08873974645786728</v>
       </c>
       <c r="AK3">
-        <v>-0.288968824940048</v>
+        <v>0.08018867924528303</v>
       </c>
       <c r="AL3">
-        <v>0.493</v>
+        <v>1.79</v>
       </c>
       <c r="AM3">
-        <v>-0.03000000000000003</v>
+        <v>1.429</v>
       </c>
       <c r="AN3">
-        <v>4.173913043478261</v>
+        <v>5.2991452991453</v>
       </c>
       <c r="AO3">
-        <v>-4.077079107505071</v>
+        <v>1.608938547486033</v>
       </c>
       <c r="AP3">
-        <v>-15.71739130434783</v>
+        <v>1.695156695156696</v>
       </c>
       <c r="AQ3">
-        <v>66.99999999999993</v>
+        <v>2.015395381385584</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Macay Holdings, Inc. (PSE:MACAY)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PSE:MACAY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Beverage (Soft)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.60893854748603</v>
+      </c>
+      <c r="F2">
+        <v>4.59553806707795</v>
+      </c>
+      <c r="G2">
+        <v>5.2991452991453</v>
+      </c>
+      <c r="H2">
+        <v>3.17891737891738</v>
+      </c>
+      <c r="I2">
+        <v>0.233375156838143</v>
+      </c>
+      <c r="J2">
+        <v>0.14</v>
+      </c>
+      <c r="K2">
+        <v>122.2</v>
+      </c>
+      <c r="L2">
+        <v>145.416332220014</v>
+      </c>
+      <c r="M2">
+        <v>134.1</v>
+      </c>
+      <c r="N2">
+        <v>142.432332220014</v>
+      </c>
+      <c r="O2">
+        <v>37.2</v>
+      </c>
+      <c r="P2">
+        <v>22.316</v>
+      </c>
+      <c r="Q2">
+        <v>0.08837851643093871</v>
+      </c>
+      <c r="R2">
+        <v>0.0854781590230444</v>
+      </c>
+      <c r="S2">
+        <v>0.0557004277832879</v>
+      </c>
+      <c r="T2">
+        <v>0.038175</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.0983263470176213</v>
+      </c>
+      <c r="X2">
+        <v>0.0931786732826097</v>
+      </c>
+      <c r="Y2">
+        <v>0.806081706020375</v>
+      </c>
+      <c r="Z2">
+        <v>0.736373991130259</v>
+      </c>
+      <c r="AA2">
+        <v>37.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.07426723704438384</v>
+      </c>
+      <c r="AC2">
+        <v>1.608938547486033</v>
+      </c>
+      <c r="AD2">
+        <v>37.2</v>
+      </c>
+      <c r="AE2">
+        <v>1.79</v>
+      </c>
+      <c r="AF2">
+        <v>4.14</v>
+      </c>
+      <c r="AG2">
+        <v>7.02</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>122.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>29.17</v>
+      </c>
+      <c r="AR2">
+        <v>1.79</v>
+      </c>
+      <c r="AS2">
+        <v>37.2</v>
+      </c>
+      <c r="AT2">
+        <v>25.3</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08726182282180762</v>
+      </c>
+      <c r="C2">
+        <v>162.4900326125804</v>
+      </c>
+      <c r="D2">
+        <v>137.1900326125804</v>
+      </c>
+      <c r="E2">
+        <v>-37.2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>25.3</v>
+      </c>
+      <c r="H2">
+        <v>122.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K2">
+        <v>4.14</v>
+      </c>
+      <c r="L2">
+        <v>5.22</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>5.22</v>
+      </c>
+      <c r="O2">
+        <v>1.305</v>
+      </c>
+      <c r="P2">
+        <v>3.915</v>
+      </c>
+      <c r="Q2">
+        <v>8.055</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08726182282180762</v>
+      </c>
+      <c r="T2">
+        <v>0.6562503962404382</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08708791826475309</v>
+      </c>
+      <c r="C3">
+        <v>161.3901100694503</v>
+      </c>
+      <c r="D3">
+        <v>137.6841100694502</v>
+      </c>
+      <c r="E3">
+        <v>-35.606</v>
+      </c>
+      <c r="F3">
+        <v>1.594</v>
+      </c>
+      <c r="G3">
+        <v>25.3</v>
+      </c>
+      <c r="H3">
+        <v>122.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K3">
+        <v>4.14</v>
+      </c>
+      <c r="L3">
+        <v>5.22</v>
+      </c>
+      <c r="M3">
+        <v>0.0712518</v>
+      </c>
+      <c r="N3">
+        <v>5.1487482</v>
+      </c>
+      <c r="O3">
+        <v>1.28718705</v>
+      </c>
+      <c r="P3">
+        <v>3.86156115</v>
+      </c>
+      <c r="Q3">
+        <v>8.001561150000001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08762895784318495</v>
+      </c>
+      <c r="T3">
+        <v>0.6612219901513506</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.033525</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>73.26130708276843</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08691401370769859</v>
+      </c>
+      <c r="C4">
+        <v>160.2937591394392</v>
+      </c>
+      <c r="D4">
+        <v>138.1817591394392</v>
+      </c>
+      <c r="E4">
+        <v>-34.012</v>
+      </c>
+      <c r="F4">
+        <v>3.188</v>
+      </c>
+      <c r="G4">
+        <v>25.3</v>
+      </c>
+      <c r="H4">
+        <v>122.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K4">
+        <v>4.14</v>
+      </c>
+      <c r="L4">
+        <v>5.22</v>
+      </c>
+      <c r="M4">
+        <v>0.1425036</v>
+      </c>
+      <c r="N4">
+        <v>5.077496399999999</v>
+      </c>
+      <c r="O4">
+        <v>1.2693741</v>
+      </c>
+      <c r="P4">
+        <v>3.8081223</v>
+      </c>
+      <c r="Q4">
+        <v>7.9481223</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08800358541601896</v>
+      </c>
+      <c r="T4">
+        <v>0.6662950451624858</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.033525</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>36.63065354138421</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08674010915064406</v>
+      </c>
+      <c r="C5">
+        <v>159.2010186910319</v>
+      </c>
+      <c r="D5">
+        <v>138.6830186910319</v>
+      </c>
+      <c r="E5">
+        <v>-32.41800000000001</v>
+      </c>
+      <c r="F5">
+        <v>4.782</v>
+      </c>
+      <c r="G5">
+        <v>25.3</v>
+      </c>
+      <c r="H5">
+        <v>122.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K5">
+        <v>4.14</v>
+      </c>
+      <c r="L5">
+        <v>5.22</v>
+      </c>
+      <c r="M5">
+        <v>0.2137554</v>
+      </c>
+      <c r="N5">
+        <v>5.0062446</v>
+      </c>
+      <c r="O5">
+        <v>1.25156115</v>
+      </c>
+      <c r="P5">
+        <v>3.75468345</v>
+      </c>
+      <c r="Q5">
+        <v>7.89468345</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08838593726870522</v>
+      </c>
+      <c r="T5">
+        <v>0.6714726992460154</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.033525</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>24.42043569425614</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08656620459358955</v>
+      </c>
+      <c r="C6">
+        <v>158.1119281587539</v>
+      </c>
+      <c r="D6">
+        <v>139.1879281587539</v>
+      </c>
+      <c r="E6">
+        <v>-30.824</v>
+      </c>
+      <c r="F6">
+        <v>6.376</v>
+      </c>
+      <c r="G6">
+        <v>25.3</v>
+      </c>
+      <c r="H6">
+        <v>122.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K6">
+        <v>4.14</v>
+      </c>
+      <c r="L6">
+        <v>5.22</v>
+      </c>
+      <c r="M6">
+        <v>0.2850072</v>
+      </c>
+      <c r="N6">
+        <v>4.9349928</v>
+      </c>
+      <c r="O6">
+        <v>1.2337482</v>
+      </c>
+      <c r="P6">
+        <v>3.7012446</v>
+      </c>
+      <c r="Q6">
+        <v>7.8412446</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08877625478498911</v>
+      </c>
+      <c r="T6">
+        <v>0.6767582211229519</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.033525</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>18.31532677069211</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08639230003653503</v>
+      </c>
+      <c r="C7">
+        <v>157.0265275535132</v>
+      </c>
+      <c r="D7">
+        <v>139.6965275535132</v>
+      </c>
+      <c r="E7">
+        <v>-29.23</v>
+      </c>
+      <c r="F7">
+        <v>7.970000000000001</v>
+      </c>
+      <c r="G7">
+        <v>25.3</v>
+      </c>
+      <c r="H7">
+        <v>122.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K7">
+        <v>4.14</v>
+      </c>
+      <c r="L7">
+        <v>5.22</v>
+      </c>
+      <c r="M7">
+        <v>0.356259</v>
+      </c>
+      <c r="N7">
+        <v>4.863741</v>
+      </c>
+      <c r="O7">
+        <v>1.21593525</v>
+      </c>
+      <c r="P7">
+        <v>3.64780575</v>
+      </c>
+      <c r="Q7">
+        <v>7.78780575</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08917478951214214</v>
+      </c>
+      <c r="T7">
+        <v>0.6821550171446661</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.033525</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>14.65226141655369</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.08626789547948049</v>
+      </c>
+      <c r="C8">
+        <v>155.7986462629441</v>
+      </c>
+      <c r="D8">
+        <v>140.0626462629441</v>
+      </c>
+      <c r="E8">
+        <v>-27.636</v>
+      </c>
+      <c r="F8">
+        <v>9.564</v>
+      </c>
+      <c r="G8">
+        <v>25.3</v>
+      </c>
+      <c r="H8">
+        <v>122.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K8">
+        <v>4.14</v>
+      </c>
+      <c r="L8">
+        <v>5.22</v>
+      </c>
+      <c r="M8">
+        <v>0.4380312</v>
+      </c>
+      <c r="N8">
+        <v>4.7819688</v>
+      </c>
+      <c r="O8">
+        <v>1.1954922</v>
+      </c>
+      <c r="P8">
+        <v>3.5864766</v>
+      </c>
+      <c r="Q8">
+        <v>7.7264766</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08958180370157501</v>
+      </c>
+      <c r="T8">
+        <v>0.6876666386136507</v>
+      </c>
+      <c r="U8">
+        <v>0.0458</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.03435</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>11.91695933988264</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08610224092242599</v>
+      </c>
+      <c r="C9">
+        <v>154.6951518959568</v>
+      </c>
+      <c r="D9">
+        <v>140.5531518959568</v>
+      </c>
+      <c r="E9">
+        <v>-26.042</v>
+      </c>
+      <c r="F9">
+        <v>11.158</v>
+      </c>
+      <c r="G9">
+        <v>25.3</v>
+      </c>
+      <c r="H9">
+        <v>122.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K9">
+        <v>4.14</v>
+      </c>
+      <c r="L9">
+        <v>5.22</v>
+      </c>
+      <c r="M9">
+        <v>0.5110364000000001</v>
+      </c>
+      <c r="N9">
+        <v>4.7089636</v>
+      </c>
+      <c r="O9">
+        <v>1.1772409</v>
+      </c>
+      <c r="P9">
+        <v>3.5317227</v>
+      </c>
+      <c r="Q9">
+        <v>7.671722699999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08999757088432903</v>
+      </c>
+      <c r="T9">
+        <v>0.693296789576592</v>
+      </c>
+      <c r="U9">
+        <v>0.0458</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.03435</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>10.21453657704226</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08606858636537147</v>
+      </c>
+      <c r="C10">
+        <v>153.2012237287193</v>
+      </c>
+      <c r="D10">
+        <v>140.6532237287193</v>
+      </c>
+      <c r="E10">
+        <v>-24.448</v>
+      </c>
+      <c r="F10">
+        <v>12.752</v>
+      </c>
+      <c r="G10">
+        <v>25.3</v>
+      </c>
+      <c r="H10">
+        <v>122.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K10">
+        <v>4.14</v>
+      </c>
+      <c r="L10">
+        <v>5.22</v>
+      </c>
+      <c r="M10">
+        <v>0.6120960000000001</v>
+      </c>
+      <c r="N10">
+        <v>4.607904</v>
+      </c>
+      <c r="O10">
+        <v>1.151976</v>
+      </c>
+      <c r="P10">
+        <v>3.455928</v>
+      </c>
+      <c r="Q10">
+        <v>7.595927999999999</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09042237648409943</v>
+      </c>
+      <c r="T10">
+        <v>0.6990493351256842</v>
+      </c>
+      <c r="U10">
+        <v>0.048</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.036</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>8.528074027603513</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08602068180831696</v>
+      </c>
+      <c r="C11">
+        <v>151.7499139678896</v>
+      </c>
+      <c r="D11">
+        <v>140.7959139678896</v>
+      </c>
+      <c r="E11">
+        <v>-22.854</v>
+      </c>
+      <c r="F11">
+        <v>14.346</v>
+      </c>
+      <c r="G11">
+        <v>25.3</v>
+      </c>
+      <c r="H11">
+        <v>122.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K11">
+        <v>4.14</v>
+      </c>
+      <c r="L11">
+        <v>5.22</v>
+      </c>
+      <c r="M11">
+        <v>0.7101270000000001</v>
+      </c>
+      <c r="N11">
+        <v>4.509873</v>
+      </c>
+      <c r="O11">
+        <v>1.12746825</v>
+      </c>
+      <c r="P11">
+        <v>3.38240475</v>
+      </c>
+      <c r="Q11">
+        <v>7.52240475</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09085651847067797</v>
+      </c>
+      <c r="T11">
+        <v>0.7049283102472839</v>
+      </c>
+      <c r="U11">
+        <v>0.0495</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>7.350797815038717</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08588277725126242</v>
+      </c>
+      <c r="C12">
+        <v>150.5683025159825</v>
+      </c>
+      <c r="D12">
+        <v>141.2083025159825</v>
+      </c>
+      <c r="E12">
+        <v>-21.26</v>
+      </c>
+      <c r="F12">
+        <v>15.94</v>
+      </c>
+      <c r="G12">
+        <v>25.3</v>
+      </c>
+      <c r="H12">
+        <v>122.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K12">
+        <v>4.14</v>
+      </c>
+      <c r="L12">
+        <v>5.22</v>
+      </c>
+      <c r="M12">
+        <v>0.7890300000000001</v>
+      </c>
+      <c r="N12">
+        <v>4.430969999999999</v>
+      </c>
+      <c r="O12">
+        <v>1.1077425</v>
+      </c>
+      <c r="P12">
+        <v>3.3232275</v>
+      </c>
+      <c r="Q12">
+        <v>7.463227499999999</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09130030805695825</v>
+      </c>
+      <c r="T12">
+        <v>0.7109379292604747</v>
+      </c>
+      <c r="U12">
+        <v>0.0495</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>6.615718033534845</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08586037269420792</v>
+      </c>
+      <c r="C13">
+        <v>149.0415291291427</v>
+      </c>
+      <c r="D13">
+        <v>141.2755291291427</v>
+      </c>
+      <c r="E13">
+        <v>-19.666</v>
+      </c>
+      <c r="F13">
+        <v>17.534</v>
+      </c>
+      <c r="G13">
+        <v>25.3</v>
+      </c>
+      <c r="H13">
+        <v>122.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K13">
+        <v>4.14</v>
+      </c>
+      <c r="L13">
+        <v>5.22</v>
+      </c>
+      <c r="M13">
+        <v>0.8924806000000002</v>
+      </c>
+      <c r="N13">
+        <v>4.3275194</v>
+      </c>
+      <c r="O13">
+        <v>1.08187985</v>
+      </c>
+      <c r="P13">
+        <v>3.24563955</v>
+      </c>
+      <c r="Q13">
+        <v>7.38563955</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09175407044293024</v>
+      </c>
+      <c r="T13">
+        <v>0.7170825958919396</v>
+      </c>
+      <c r="U13">
+        <v>0.0509</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.038175</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>5.848866630826485</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08573296813715341</v>
+      </c>
+      <c r="C14">
+        <v>147.8310366490323</v>
+      </c>
+      <c r="D14">
+        <v>141.6590366490323</v>
+      </c>
+      <c r="E14">
+        <v>-18.072</v>
+      </c>
+      <c r="F14">
+        <v>19.128</v>
+      </c>
+      <c r="G14">
+        <v>25.3</v>
+      </c>
+      <c r="H14">
+        <v>122.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K14">
+        <v>4.14</v>
+      </c>
+      <c r="L14">
+        <v>5.22</v>
+      </c>
+      <c r="M14">
+        <v>0.9736152</v>
+      </c>
+      <c r="N14">
+        <v>4.2463848</v>
+      </c>
+      <c r="O14">
+        <v>1.0615962</v>
+      </c>
+      <c r="P14">
+        <v>3.1847886</v>
+      </c>
+      <c r="Q14">
+        <v>7.3247886</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09221814561040159</v>
+      </c>
+      <c r="T14">
+        <v>0.7233669140377558</v>
+      </c>
+      <c r="U14">
+        <v>0.0509</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.038175</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.36146107825761</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08560556358009887</v>
+      </c>
+      <c r="C15">
+        <v>146.6226319807958</v>
+      </c>
+      <c r="D15">
+        <v>142.0446319807958</v>
+      </c>
+      <c r="E15">
+        <v>-16.478</v>
+      </c>
+      <c r="F15">
+        <v>20.722</v>
+      </c>
+      <c r="G15">
+        <v>25.3</v>
+      </c>
+      <c r="H15">
+        <v>122.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K15">
+        <v>4.14</v>
+      </c>
+      <c r="L15">
+        <v>5.22</v>
+      </c>
+      <c r="M15">
+        <v>1.0547498</v>
+      </c>
+      <c r="N15">
+        <v>4.165250199999999</v>
+      </c>
+      <c r="O15">
+        <v>1.04131255</v>
+      </c>
+      <c r="P15">
+        <v>3.123937649999999</v>
+      </c>
+      <c r="Q15">
+        <v>7.263937649999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09269288917252744</v>
+      </c>
+      <c r="T15">
+        <v>0.7297956992673839</v>
+      </c>
+      <c r="U15">
+        <v>0.0509</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.038175</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>4.949040995314716</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08547815902304436</v>
+      </c>
+      <c r="C16">
+        <v>145.4163322200137</v>
+      </c>
+      <c r="D16">
+        <v>142.4323322200137</v>
+      </c>
+      <c r="E16">
+        <v>-14.884</v>
+      </c>
+      <c r="F16">
+        <v>22.316</v>
+      </c>
+      <c r="G16">
+        <v>25.3</v>
+      </c>
+      <c r="H16">
+        <v>122.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K16">
+        <v>4.14</v>
+      </c>
+      <c r="L16">
+        <v>5.22</v>
+      </c>
+      <c r="M16">
+        <v>1.1358844</v>
+      </c>
+      <c r="N16">
+        <v>4.0841156</v>
+      </c>
+      <c r="O16">
+        <v>1.0210289</v>
+      </c>
+      <c r="P16">
+        <v>3.063086699999999</v>
+      </c>
+      <c r="Q16">
+        <v>7.203086699999999</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09317867328260972</v>
+      </c>
+      <c r="T16">
+        <v>0.7363739911302591</v>
+      </c>
+      <c r="U16">
+        <v>0.0509</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.038175</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>4.595538067077952</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08564325446598985</v>
+      </c>
+      <c r="C17">
+        <v>143.3203404338816</v>
+      </c>
+      <c r="D17">
+        <v>141.9303404338816</v>
+      </c>
+      <c r="E17">
+        <v>-13.29</v>
+      </c>
+      <c r="F17">
+        <v>23.91</v>
+      </c>
+      <c r="G17">
+        <v>25.3</v>
+      </c>
+      <c r="H17">
+        <v>122.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K17">
+        <v>4.14</v>
+      </c>
+      <c r="L17">
+        <v>5.22</v>
+      </c>
+      <c r="M17">
+        <v>1.279185</v>
+      </c>
+      <c r="N17">
+        <v>3.940815</v>
+      </c>
+      <c r="O17">
+        <v>0.9852037499999999</v>
+      </c>
+      <c r="P17">
+        <v>2.95561125</v>
+      </c>
+      <c r="Q17">
+        <v>7.095611249999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09367588760704687</v>
+      </c>
+      <c r="T17">
+        <v>0.7431070663310845</v>
+      </c>
+      <c r="U17">
+        <v>0.0535</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.040125</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.080723273021494</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.0858593499089353</v>
+      </c>
+      <c r="C18">
+        <v>141.0745996035724</v>
+      </c>
+      <c r="D18">
+        <v>141.2785996035724</v>
+      </c>
+      <c r="E18">
+        <v>-11.696</v>
+      </c>
+      <c r="F18">
+        <v>25.504</v>
+      </c>
+      <c r="G18">
+        <v>25.3</v>
+      </c>
+      <c r="H18">
+        <v>122.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K18">
+        <v>4.14</v>
+      </c>
+      <c r="L18">
+        <v>5.22</v>
+      </c>
+      <c r="M18">
+        <v>1.4333248</v>
+      </c>
+      <c r="N18">
+        <v>3.786675199999999</v>
+      </c>
+      <c r="O18">
+        <v>0.9466687999999999</v>
+      </c>
+      <c r="P18">
+        <v>2.8400064</v>
+      </c>
+      <c r="Q18">
+        <v>6.980006399999999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09418494036778013</v>
+      </c>
+      <c r="T18">
+        <v>0.7500004528462151</v>
+      </c>
+      <c r="U18">
+        <v>0.0562</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.04215</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>3.641882147019293</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08637094535188081</v>
+      </c>
+      <c r="C19">
+        <v>137.9612375810547</v>
+      </c>
+      <c r="D19">
+        <v>139.7592375810547</v>
+      </c>
+      <c r="E19">
+        <v>-10.102</v>
+      </c>
+      <c r="F19">
+        <v>27.098</v>
+      </c>
+      <c r="G19">
+        <v>25.3</v>
+      </c>
+      <c r="H19">
+        <v>122.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K19">
+        <v>4.14</v>
+      </c>
+      <c r="L19">
+        <v>5.22</v>
+      </c>
+      <c r="M19">
+        <v>1.6502682</v>
+      </c>
+      <c r="N19">
+        <v>3.5697318</v>
+      </c>
+      <c r="O19">
+        <v>0.8924329499999999</v>
+      </c>
+      <c r="P19">
+        <v>2.67729885</v>
+      </c>
+      <c r="Q19">
+        <v>6.817298849999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09470625946009736</v>
+      </c>
+      <c r="T19">
+        <v>0.7570599450605057</v>
+      </c>
+      <c r="U19">
+        <v>0.0609</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.045675</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>3.16312221249855</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08757404079482628</v>
+      </c>
+      <c r="C20">
+        <v>132.9198360719074</v>
+      </c>
+      <c r="D20">
+        <v>136.3118360719074</v>
+      </c>
+      <c r="E20">
+        <v>-8.508000000000003</v>
+      </c>
+      <c r="F20">
+        <v>28.692</v>
+      </c>
+      <c r="G20">
+        <v>25.3</v>
+      </c>
+      <c r="H20">
+        <v>122.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K20">
+        <v>4.14</v>
+      </c>
+      <c r="L20">
+        <v>5.22</v>
+      </c>
+      <c r="M20">
+        <v>2.0141784</v>
+      </c>
+      <c r="N20">
+        <v>3.2058216</v>
+      </c>
+      <c r="O20">
+        <v>0.8014553999999999</v>
+      </c>
+      <c r="P20">
+        <v>2.4043662</v>
+      </c>
+      <c r="Q20">
+        <v>6.544366199999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09524029365222716</v>
+      </c>
+      <c r="T20">
+        <v>0.7642916200117299</v>
+      </c>
+      <c r="U20">
+        <v>0.0702</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.05265</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>2.591627434789292</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08826113623777176</v>
+      </c>
+      <c r="C21">
+        <v>129.4322434756052</v>
+      </c>
+      <c r="D21">
+        <v>134.4182434756052</v>
+      </c>
+      <c r="E21">
+        <v>-6.914000000000001</v>
+      </c>
+      <c r="F21">
+        <v>30.286</v>
+      </c>
+      <c r="G21">
+        <v>25.3</v>
+      </c>
+      <c r="H21">
+        <v>122.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K21">
+        <v>4.14</v>
+      </c>
+      <c r="L21">
+        <v>5.22</v>
+      </c>
+      <c r="M21">
+        <v>2.2684214</v>
+      </c>
+      <c r="N21">
+        <v>2.9515786</v>
+      </c>
+      <c r="O21">
+        <v>0.73789465</v>
+      </c>
+      <c r="P21">
+        <v>2.21368395</v>
+      </c>
+      <c r="Q21">
+        <v>6.35368395</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09578751387379231</v>
+      </c>
+      <c r="T21">
+        <v>0.7717018548382932</v>
+      </c>
+      <c r="U21">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.056175</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.301159740425655</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08831373168071724</v>
+      </c>
+      <c r="C22">
+        <v>127.6954591041677</v>
+      </c>
+      <c r="D22">
+        <v>134.2754591041677</v>
+      </c>
+      <c r="E22">
+        <v>-5.32</v>
+      </c>
+      <c r="F22">
+        <v>31.88</v>
+      </c>
+      <c r="G22">
+        <v>25.3</v>
+      </c>
+      <c r="H22">
+        <v>122.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K22">
+        <v>4.14</v>
+      </c>
+      <c r="L22">
+        <v>5.22</v>
+      </c>
+      <c r="M22">
+        <v>2.387812</v>
+      </c>
+      <c r="N22">
+        <v>2.832188</v>
+      </c>
+      <c r="O22">
+        <v>0.708047</v>
+      </c>
+      <c r="P22">
+        <v>2.124141</v>
+      </c>
+      <c r="Q22">
+        <v>6.264141</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09634841460089655</v>
+      </c>
+      <c r="T22">
+        <v>0.7792973455355204</v>
+      </c>
+      <c r="U22">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.056175</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.186101753404372</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08836632712366271</v>
+      </c>
+      <c r="C23">
+        <v>125.9589777532564</v>
+      </c>
+      <c r="D23">
+        <v>134.1329777532564</v>
+      </c>
+      <c r="E23">
+        <v>-3.726000000000006</v>
+      </c>
+      <c r="F23">
+        <v>33.474</v>
+      </c>
+      <c r="G23">
+        <v>25.3</v>
+      </c>
+      <c r="H23">
+        <v>122.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K23">
+        <v>4.14</v>
+      </c>
+      <c r="L23">
+        <v>5.22</v>
+      </c>
+      <c r="M23">
+        <v>2.507202599999999</v>
+      </c>
+      <c r="N23">
+        <v>2.7127974</v>
+      </c>
+      <c r="O23">
+        <v>0.6781993500000001</v>
+      </c>
+      <c r="P23">
+        <v>2.03459805</v>
+      </c>
+      <c r="Q23">
+        <v>6.17459805</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.0969235153464085</v>
+      </c>
+      <c r="T23">
+        <v>0.7870851271364749</v>
+      </c>
+      <c r="U23">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.056175</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.082001669908926</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.0911084225666082</v>
+      </c>
+      <c r="C24">
+        <v>117.3335015779319</v>
+      </c>
+      <c r="D24">
+        <v>127.1015015779319</v>
+      </c>
+      <c r="E24">
+        <v>-2.131999999999998</v>
+      </c>
+      <c r="F24">
+        <v>35.068</v>
+      </c>
+      <c r="G24">
+        <v>25.3</v>
+      </c>
+      <c r="H24">
+        <v>122.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K24">
+        <v>4.14</v>
+      </c>
+      <c r="L24">
+        <v>5.22</v>
+      </c>
+      <c r="M24">
+        <v>3.1982016</v>
+      </c>
+      <c r="N24">
+        <v>2.021798399999999</v>
+      </c>
+      <c r="O24">
+        <v>0.5054495999999998</v>
+      </c>
+      <c r="P24">
+        <v>1.516348799999999</v>
+      </c>
+      <c r="Q24">
+        <v>5.656348799999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.0975133622648823</v>
+      </c>
+      <c r="T24">
+        <v>0.7950725954451463</v>
+      </c>
+      <c r="U24">
+        <v>0.0912</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.0684</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>1.632167278010241</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09128326800955369</v>
+      </c>
+      <c r="C25">
+        <v>115.3160691358366</v>
+      </c>
+      <c r="D25">
+        <v>126.6780691358366</v>
+      </c>
+      <c r="E25">
+        <v>-0.5379999999999967</v>
+      </c>
+      <c r="F25">
+        <v>36.66200000000001</v>
+      </c>
+      <c r="G25">
+        <v>25.3</v>
+      </c>
+      <c r="H25">
+        <v>122.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K25">
+        <v>4.14</v>
+      </c>
+      <c r="L25">
+        <v>5.22</v>
+      </c>
+      <c r="M25">
+        <v>3.343574400000001</v>
+      </c>
+      <c r="N25">
+        <v>1.876425599999999</v>
+      </c>
+      <c r="O25">
+        <v>0.4691063999999998</v>
+      </c>
+      <c r="P25">
+        <v>1.407319199999999</v>
+      </c>
+      <c r="Q25">
+        <v>5.547319199999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09811852988253725</v>
+      </c>
+      <c r="T25">
+        <v>0.8032675304631338</v>
+      </c>
+      <c r="U25">
+        <v>0.0912</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.0684</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>1.561203483314144</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1048133176554647</v>
+      </c>
+      <c r="C26">
+        <v>87.75820873116061</v>
+      </c>
+      <c r="D26">
+        <v>100.7142087311606</v>
+      </c>
+      <c r="E26">
+        <v>1.055999999999997</v>
+      </c>
+      <c r="F26">
+        <v>38.256</v>
+      </c>
+      <c r="G26">
+        <v>25.3</v>
+      </c>
+      <c r="H26">
+        <v>122.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K26">
+        <v>4.14</v>
+      </c>
+      <c r="L26">
+        <v>5.22</v>
+      </c>
+      <c r="M26">
+        <v>5.990889600000001</v>
+      </c>
+      <c r="N26">
+        <v>-0.7708896000000012</v>
+      </c>
+      <c r="O26">
+        <v>-0.1927224000000003</v>
+      </c>
+      <c r="P26">
+        <v>-0.5781672000000009</v>
+      </c>
+      <c r="Q26">
+        <v>3.561832799999999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09923193252890009</v>
+      </c>
+      <c r="T26">
+        <v>0.8183447786000313</v>
+      </c>
+      <c r="U26">
+        <v>0.1566</v>
+      </c>
+      <c r="V26">
+        <v>0.2178307542172034</v>
+      </c>
+      <c r="W26">
+        <v>0.122487703889586</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.8713230168688134</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1059913176554647</v>
+      </c>
+      <c r="C27">
+        <v>84.39848449735914</v>
+      </c>
+      <c r="D27">
+        <v>98.94848449735915</v>
+      </c>
+      <c r="E27">
+        <v>2.649999999999999</v>
+      </c>
+      <c r="F27">
+        <v>39.85</v>
+      </c>
+      <c r="G27">
+        <v>25.3</v>
+      </c>
+      <c r="H27">
+        <v>122.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K27">
+        <v>4.14</v>
+      </c>
+      <c r="L27">
+        <v>5.22</v>
+      </c>
+      <c r="M27">
+        <v>6.240510000000001</v>
+      </c>
+      <c r="N27">
+        <v>-1.020510000000002</v>
+      </c>
+      <c r="O27">
+        <v>-0.2551275000000004</v>
+      </c>
+      <c r="P27">
+        <v>-0.7653825000000012</v>
+      </c>
+      <c r="Q27">
+        <v>3.374617499999998</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1000376916292854</v>
+      </c>
+      <c r="T27">
+        <v>0.8292560423146984</v>
+      </c>
+      <c r="U27">
+        <v>0.1566</v>
+      </c>
+      <c r="V27">
+        <v>0.2091175240485152</v>
+      </c>
+      <c r="W27">
+        <v>0.1238521957340025</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.8364700961940609</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1071693176554647</v>
+      </c>
+      <c r="C28">
+        <v>81.09960694796953</v>
+      </c>
+      <c r="D28">
+        <v>97.24360694796954</v>
+      </c>
+      <c r="E28">
+        <v>4.244</v>
+      </c>
+      <c r="F28">
+        <v>41.444</v>
+      </c>
+      <c r="G28">
+        <v>25.3</v>
+      </c>
+      <c r="H28">
+        <v>122.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K28">
+        <v>4.14</v>
+      </c>
+      <c r="L28">
+        <v>5.22</v>
+      </c>
+      <c r="M28">
+        <v>6.490130400000001</v>
+      </c>
+      <c r="N28">
+        <v>-1.270130400000001</v>
+      </c>
+      <c r="O28">
+        <v>-0.3175326000000003</v>
+      </c>
+      <c r="P28">
+        <v>-0.9525978000000008</v>
+      </c>
+      <c r="Q28">
+        <v>3.187402199999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1008652280026541</v>
+      </c>
+      <c r="T28">
+        <v>0.8404622050486809</v>
+      </c>
+      <c r="U28">
+        <v>0.1566</v>
+      </c>
+      <c r="V28">
+        <v>0.2010745423543416</v>
+      </c>
+      <c r="W28">
+        <v>0.1251117266673101</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.8042981694173663</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1230747061804256</v>
+      </c>
+      <c r="C29">
+        <v>61.15256342901993</v>
+      </c>
+      <c r="D29">
+        <v>78.89056342901993</v>
+      </c>
+      <c r="E29">
+        <v>5.838000000000001</v>
+      </c>
+      <c r="F29">
+        <v>43.038</v>
+      </c>
+      <c r="G29">
+        <v>25.3</v>
+      </c>
+      <c r="H29">
+        <v>122.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K29">
+        <v>4.14</v>
+      </c>
+      <c r="L29">
+        <v>5.22</v>
+      </c>
+      <c r="M29">
+        <v>8.9863344</v>
+      </c>
+      <c r="N29">
+        <v>-3.766334400000001</v>
+      </c>
+      <c r="O29">
+        <v>-0.9415836000000002</v>
+      </c>
+      <c r="P29">
+        <v>-2.8247508</v>
+      </c>
+      <c r="Q29">
+        <v>1.315249199999999</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1025830921190753</v>
+      </c>
+      <c r="T29">
+        <v>0.8637248258385307</v>
+      </c>
+      <c r="U29">
+        <v>0.2088</v>
+      </c>
+      <c r="V29">
+        <v>0.1452205028114689</v>
+      </c>
+      <c r="W29">
+        <v>0.1784779590129653</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.5808820112458757</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1247747061804256</v>
+      </c>
+      <c r="C30">
+        <v>57.99864000749771</v>
+      </c>
+      <c r="D30">
+        <v>77.33064000749772</v>
+      </c>
+      <c r="E30">
+        <v>7.432000000000002</v>
+      </c>
+      <c r="F30">
+        <v>44.63200000000001</v>
+      </c>
+      <c r="G30">
+        <v>25.3</v>
+      </c>
+      <c r="H30">
+        <v>122.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K30">
+        <v>4.14</v>
+      </c>
+      <c r="L30">
+        <v>5.22</v>
+      </c>
+      <c r="M30">
+        <v>9.319161600000001</v>
+      </c>
+      <c r="N30">
+        <v>-4.099161600000001</v>
+      </c>
+      <c r="O30">
+        <v>-1.0247904</v>
+      </c>
+      <c r="P30">
+        <v>-3.074371200000001</v>
+      </c>
+      <c r="Q30">
+        <v>1.065628799999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1034689683985069</v>
+      </c>
+      <c r="T30">
+        <v>0.8757210039751772</v>
+      </c>
+      <c r="U30">
+        <v>0.2088</v>
+      </c>
+      <c r="V30">
+        <v>0.1400340562824879</v>
+      </c>
+      <c r="W30">
+        <v>0.1795608890482165</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.5601362251299515</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1264747061804256</v>
+      </c>
+      <c r="C31">
+        <v>54.90520996957767</v>
+      </c>
+      <c r="D31">
+        <v>75.83120996957767</v>
+      </c>
+      <c r="E31">
+        <v>9.025999999999996</v>
+      </c>
+      <c r="F31">
+        <v>46.226</v>
+      </c>
+      <c r="G31">
+        <v>25.3</v>
+      </c>
+      <c r="H31">
+        <v>122.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K31">
+        <v>4.14</v>
+      </c>
+      <c r="L31">
+        <v>5.22</v>
+      </c>
+      <c r="M31">
+        <v>9.6519888</v>
+      </c>
+      <c r="N31">
+        <v>-4.4319888</v>
+      </c>
+      <c r="O31">
+        <v>-1.1079972</v>
+      </c>
+      <c r="P31">
+        <v>-3.3239916</v>
+      </c>
+      <c r="Q31">
+        <v>0.8160083999999994</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1043797989393309</v>
+      </c>
+      <c r="T31">
+        <v>0.8880551026227147</v>
+      </c>
+      <c r="U31">
+        <v>0.2088</v>
+      </c>
+      <c r="V31">
+        <v>0.1352052957210228</v>
+      </c>
+      <c r="W31">
+        <v>0.1805691342534504</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5408211828840912</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1281747061804256</v>
+      </c>
+      <c r="C32">
+        <v>51.86882137377028</v>
+      </c>
+      <c r="D32">
+        <v>74.38882137377028</v>
+      </c>
+      <c r="E32">
+        <v>10.62</v>
+      </c>
+      <c r="F32">
+        <v>47.82</v>
+      </c>
+      <c r="G32">
+        <v>25.3</v>
+      </c>
+      <c r="H32">
+        <v>122.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K32">
+        <v>4.14</v>
+      </c>
+      <c r="L32">
+        <v>5.22</v>
+      </c>
+      <c r="M32">
+        <v>9.984816</v>
+      </c>
+      <c r="N32">
+        <v>-4.764816000000001</v>
+      </c>
+      <c r="O32">
+        <v>-1.191204</v>
+      </c>
+      <c r="P32">
+        <v>-3.573612000000001</v>
+      </c>
+      <c r="Q32">
+        <v>0.566387999999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1053166532098928</v>
+      </c>
+      <c r="T32">
+        <v>0.9007416040887535</v>
+      </c>
+      <c r="U32">
+        <v>0.2088</v>
+      </c>
+      <c r="V32">
+        <v>0.130698452530322</v>
+      </c>
+      <c r="W32">
+        <v>0.1815101631116688</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.5227938101212881</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1298747061804256</v>
+      </c>
+      <c r="C33">
+        <v>48.88628001427492</v>
+      </c>
+      <c r="D33">
+        <v>73.00028001427492</v>
+      </c>
+      <c r="E33">
+        <v>12.214</v>
+      </c>
+      <c r="F33">
+        <v>49.414</v>
+      </c>
+      <c r="G33">
+        <v>25.3</v>
+      </c>
+      <c r="H33">
+        <v>122.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K33">
+        <v>4.14</v>
+      </c>
+      <c r="L33">
+        <v>5.22</v>
+      </c>
+      <c r="M33">
+        <v>10.3176432</v>
+      </c>
+      <c r="N33">
+        <v>-5.097643200000001</v>
+      </c>
+      <c r="O33">
+        <v>-1.2744108</v>
+      </c>
+      <c r="P33">
+        <v>-3.823232400000001</v>
+      </c>
+      <c r="Q33">
+        <v>0.3167675999999986</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1062806626767028</v>
+      </c>
+      <c r="T33">
+        <v>0.9137958302349674</v>
+      </c>
+      <c r="U33">
+        <v>0.2088</v>
+      </c>
+      <c r="V33">
+        <v>0.1264823734164407</v>
+      </c>
+      <c r="W33">
+        <v>0.1823904804306472</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5059294936657627</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1414134204486269</v>
+      </c>
+      <c r="C34">
+        <v>39.08351581071621</v>
+      </c>
+      <c r="D34">
+        <v>64.79151581071622</v>
+      </c>
+      <c r="E34">
+        <v>13.808</v>
+      </c>
+      <c r="F34">
+        <v>51.008</v>
+      </c>
+      <c r="G34">
+        <v>25.3</v>
+      </c>
+      <c r="H34">
+        <v>122.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K34">
+        <v>4.14</v>
+      </c>
+      <c r="L34">
+        <v>5.22</v>
+      </c>
+      <c r="M34">
+        <v>12.1807104</v>
+      </c>
+      <c r="N34">
+        <v>-6.960710400000001</v>
+      </c>
+      <c r="O34">
+        <v>-1.7401776</v>
+      </c>
+      <c r="P34">
+        <v>-5.220532800000001</v>
+      </c>
+      <c r="Q34">
+        <v>-1.080532800000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1076240757575387</v>
+      </c>
+      <c r="T34">
+        <v>0.9319877866096744</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.1071366083869788</v>
+      </c>
+      <c r="W34">
+        <v>0.2132157779171895</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.4285464335479152</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1434134204486269</v>
+      </c>
+      <c r="C35">
+        <v>36.25083122258472</v>
+      </c>
+      <c r="D35">
+        <v>63.55283122258473</v>
+      </c>
+      <c r="E35">
+        <v>15.402</v>
+      </c>
+      <c r="F35">
+        <v>52.602</v>
+      </c>
+      <c r="G35">
+        <v>25.3</v>
+      </c>
+      <c r="H35">
+        <v>122.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K35">
+        <v>4.14</v>
+      </c>
+      <c r="L35">
+        <v>5.22</v>
+      </c>
+      <c r="M35">
+        <v>12.5613576</v>
+      </c>
+      <c r="N35">
+        <v>-7.341357600000001</v>
+      </c>
+      <c r="O35">
+        <v>-1.8353394</v>
+      </c>
+      <c r="P35">
+        <v>-5.506018200000001</v>
+      </c>
+      <c r="Q35">
+        <v>-1.366018200000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1086513007688452</v>
+      </c>
+      <c r="T35">
+        <v>0.9458980520814606</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.1038900444964643</v>
+      </c>
+      <c r="W35">
+        <v>0.2139910573742443</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.4155601779858571</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1454134204486269</v>
+      </c>
+      <c r="C36">
+        <v>33.46462050548822</v>
+      </c>
+      <c r="D36">
+        <v>62.36062050548822</v>
+      </c>
+      <c r="E36">
+        <v>16.996</v>
+      </c>
+      <c r="F36">
+        <v>54.19600000000001</v>
+      </c>
+      <c r="G36">
+        <v>25.3</v>
+      </c>
+      <c r="H36">
+        <v>122.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K36">
+        <v>4.14</v>
+      </c>
+      <c r="L36">
+        <v>5.22</v>
+      </c>
+      <c r="M36">
+        <v>12.9420048</v>
+      </c>
+      <c r="N36">
+        <v>-7.722004800000001</v>
+      </c>
+      <c r="O36">
+        <v>-1.9305012</v>
+      </c>
+      <c r="P36">
+        <v>-5.791503600000001</v>
+      </c>
+      <c r="Q36">
+        <v>-1.651503600000002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1097096538107974</v>
+      </c>
+      <c r="T36">
+        <v>0.9602298407493615</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.1008344549524506</v>
+      </c>
+      <c r="W36">
+        <v>0.2147207321573548</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.4033378198098025</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1474134204486269</v>
+      </c>
+      <c r="C37">
+        <v>30.72231635950132</v>
+      </c>
+      <c r="D37">
+        <v>61.21231635950133</v>
+      </c>
+      <c r="E37">
+        <v>18.59</v>
+      </c>
+      <c r="F37">
+        <v>55.79000000000001</v>
+      </c>
+      <c r="G37">
+        <v>25.3</v>
+      </c>
+      <c r="H37">
+        <v>122.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K37">
+        <v>4.14</v>
+      </c>
+      <c r="L37">
+        <v>5.22</v>
+      </c>
+      <c r="M37">
+        <v>13.322652</v>
+      </c>
+      <c r="N37">
+        <v>-8.102652000000003</v>
+      </c>
+      <c r="O37">
+        <v>-2.025663000000001</v>
+      </c>
+      <c r="P37">
+        <v>-6.076989000000002</v>
+      </c>
+      <c r="Q37">
+        <v>-1.936989000000002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1108005715617328</v>
+      </c>
+      <c r="T37">
+        <v>0.9750026075301209</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.09795347052523776</v>
+      </c>
+      <c r="W37">
+        <v>0.2154087112385732</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3918138821009509</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1494134204486269</v>
+      </c>
+      <c r="C38">
+        <v>28.02153716198195</v>
+      </c>
+      <c r="D38">
+        <v>60.10553716198196</v>
+      </c>
+      <c r="E38">
+        <v>20.184</v>
+      </c>
+      <c r="F38">
+        <v>57.384</v>
+      </c>
+      <c r="G38">
+        <v>25.3</v>
+      </c>
+      <c r="H38">
+        <v>122.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K38">
+        <v>4.14</v>
+      </c>
+      <c r="L38">
+        <v>5.22</v>
+      </c>
+      <c r="M38">
+        <v>13.7032992</v>
+      </c>
+      <c r="N38">
+        <v>-8.483299200000001</v>
+      </c>
+      <c r="O38">
+        <v>-2.1208248</v>
+      </c>
+      <c r="P38">
+        <v>-6.362474400000001</v>
+      </c>
+      <c r="Q38">
+        <v>-2.222474400000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1119255804923848</v>
+      </c>
+      <c r="T38">
+        <v>0.9902370232727791</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.09523254078842561</v>
+      </c>
+      <c r="W38">
+        <v>0.216058469259724</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3809301631537023</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1514134204486269</v>
+      </c>
+      <c r="C39">
+        <v>25.36007047954687</v>
+      </c>
+      <c r="D39">
+        <v>59.03807047954687</v>
+      </c>
+      <c r="E39">
+        <v>21.778</v>
+      </c>
+      <c r="F39">
+        <v>58.978</v>
+      </c>
+      <c r="G39">
+        <v>25.3</v>
+      </c>
+      <c r="H39">
+        <v>122.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K39">
+        <v>4.14</v>
+      </c>
+      <c r="L39">
+        <v>5.22</v>
+      </c>
+      <c r="M39">
+        <v>14.0839464</v>
+      </c>
+      <c r="N39">
+        <v>-8.8639464</v>
+      </c>
+      <c r="O39">
+        <v>-2.2159866</v>
+      </c>
+      <c r="P39">
+        <v>-6.6479598</v>
+      </c>
+      <c r="Q39">
+        <v>-2.5079598</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.113086303992264</v>
+      </c>
+      <c r="T39">
+        <v>1.005955071261236</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.09265868833468437</v>
+      </c>
+      <c r="W39">
+        <v>0.2166731052256774</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.3706347533387375</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1534134204486269</v>
+      </c>
+      <c r="C40">
+        <v>22.73585830633964</v>
+      </c>
+      <c r="D40">
+        <v>58.00785830633964</v>
+      </c>
+      <c r="E40">
+        <v>23.372</v>
+      </c>
+      <c r="F40">
+        <v>60.572</v>
+      </c>
+      <c r="G40">
+        <v>25.3</v>
+      </c>
+      <c r="H40">
+        <v>122.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K40">
+        <v>4.14</v>
+      </c>
+      <c r="L40">
+        <v>5.22</v>
+      </c>
+      <c r="M40">
+        <v>14.4645936</v>
+      </c>
+      <c r="N40">
+        <v>-9.244593600000002</v>
+      </c>
+      <c r="O40">
+        <v>-2.3111484</v>
+      </c>
+      <c r="P40">
+        <v>-6.933445200000001</v>
+      </c>
+      <c r="Q40">
+        <v>-2.793445200000002</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1142844701856876</v>
+      </c>
+      <c r="T40">
+        <v>1.022180153055772</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.0902203017995611</v>
+      </c>
+      <c r="W40">
+        <v>0.2172553919302648</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.3608812071982443</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1554134204486269</v>
+      </c>
+      <c r="C41">
+        <v>20.14698382134167</v>
+      </c>
+      <c r="D41">
+        <v>57.01298382134168</v>
+      </c>
+      <c r="E41">
+        <v>24.966</v>
+      </c>
+      <c r="F41">
+        <v>62.166</v>
+      </c>
+      <c r="G41">
+        <v>25.3</v>
+      </c>
+      <c r="H41">
+        <v>122.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K41">
+        <v>4.14</v>
+      </c>
+      <c r="L41">
+        <v>5.22</v>
+      </c>
+      <c r="M41">
+        <v>14.8452408</v>
+      </c>
+      <c r="N41">
+        <v>-9.6252408</v>
+      </c>
+      <c r="O41">
+        <v>-2.4063102</v>
+      </c>
+      <c r="P41">
+        <v>-7.2189306</v>
+      </c>
+      <c r="Q41">
+        <v>-3.078930600000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1155219205166005</v>
+      </c>
+      <c r="T41">
+        <v>1.038937204745211</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.08790696072777747</v>
+      </c>
+      <c r="W41">
+        <v>0.2178078177782067</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3516278429111099</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1574134204486269</v>
+      </c>
+      <c r="C42">
+        <v>17.59165948543256</v>
+      </c>
+      <c r="D42">
+        <v>56.05165948543257</v>
+      </c>
+      <c r="E42">
+        <v>26.56</v>
+      </c>
+      <c r="F42">
+        <v>63.76000000000001</v>
+      </c>
+      <c r="G42">
+        <v>25.3</v>
+      </c>
+      <c r="H42">
+        <v>122.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K42">
+        <v>4.14</v>
+      </c>
+      <c r="L42">
+        <v>5.22</v>
+      </c>
+      <c r="M42">
+        <v>15.225888</v>
+      </c>
+      <c r="N42">
+        <v>-10.005888</v>
+      </c>
+      <c r="O42">
+        <v>-2.501472000000001</v>
+      </c>
+      <c r="P42">
+        <v>-7.504416000000002</v>
+      </c>
+      <c r="Q42">
+        <v>-3.364416000000002</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1168006191918772</v>
+      </c>
+      <c r="T42">
+        <v>1.056252824824298</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.08570928670958304</v>
+      </c>
+      <c r="W42">
+        <v>0.2183326223337516</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3428371468383321</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1594134204486269</v>
+      </c>
+      <c r="C43">
+        <v>15.06821632269086</v>
+      </c>
+      <c r="D43">
+        <v>55.12221632269087</v>
+      </c>
+      <c r="E43">
+        <v>28.15400000000001</v>
+      </c>
+      <c r="F43">
+        <v>65.35400000000001</v>
+      </c>
+      <c r="G43">
+        <v>25.3</v>
+      </c>
+      <c r="H43">
+        <v>122.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K43">
+        <v>4.14</v>
+      </c>
+      <c r="L43">
+        <v>5.22</v>
+      </c>
+      <c r="M43">
+        <v>15.6065352</v>
+      </c>
+      <c r="N43">
+        <v>-10.3865352</v>
+      </c>
+      <c r="O43">
+        <v>-2.596633800000001</v>
+      </c>
+      <c r="P43">
+        <v>-7.789901400000003</v>
+      </c>
+      <c r="Q43">
+        <v>-3.649901400000004</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1181226635849598</v>
+      </c>
+      <c r="T43">
+        <v>1.074155415075557</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.08361881630203222</v>
+      </c>
+      <c r="W43">
+        <v>0.2188318266670747</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3344752652081289</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1614134204486269</v>
+      </c>
+      <c r="C44">
+        <v>12.57509425071858</v>
+      </c>
+      <c r="D44">
+        <v>54.22309425071857</v>
+      </c>
+      <c r="E44">
+        <v>29.74799999999999</v>
+      </c>
+      <c r="F44">
+        <v>66.94799999999999</v>
+      </c>
+      <c r="G44">
+        <v>25.3</v>
+      </c>
+      <c r="H44">
+        <v>122.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K44">
+        <v>4.14</v>
+      </c>
+      <c r="L44">
+        <v>5.22</v>
+      </c>
+      <c r="M44">
+        <v>15.9871824</v>
+      </c>
+      <c r="N44">
+        <v>-10.7671824</v>
+      </c>
+      <c r="O44">
+        <v>-2.6917956</v>
+      </c>
+      <c r="P44">
+        <v>-8.0753868</v>
+      </c>
+      <c r="Q44">
+        <v>-3.935386800000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.119490295715735</v>
+      </c>
+      <c r="T44">
+        <v>1.092675336025135</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.0816278921043648</v>
+      </c>
+      <c r="W44">
+        <v>0.2193072593654777</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3265115684174593</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1634134204486269</v>
+      </c>
+      <c r="C45">
+        <v>10.11083334213413</v>
+      </c>
+      <c r="D45">
+        <v>53.35283334213413</v>
+      </c>
+      <c r="E45">
+        <v>31.342</v>
+      </c>
+      <c r="F45">
+        <v>68.542</v>
+      </c>
+      <c r="G45">
+        <v>25.3</v>
+      </c>
+      <c r="H45">
+        <v>122.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K45">
+        <v>4.14</v>
+      </c>
+      <c r="L45">
+        <v>5.22</v>
+      </c>
+      <c r="M45">
+        <v>16.3678296</v>
+      </c>
+      <c r="N45">
+        <v>-11.1478296</v>
+      </c>
+      <c r="O45">
+        <v>-2.7869574</v>
+      </c>
+      <c r="P45">
+        <v>-8.360872200000001</v>
+      </c>
+      <c r="Q45">
+        <v>-4.220872200000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.120905914938818</v>
+      </c>
+      <c r="T45">
+        <v>1.111845078762418</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.07972956903217027</v>
+      </c>
+      <c r="W45">
+        <v>0.2197605789151178</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3189182761286811</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1654134204486269</v>
+      </c>
+      <c r="C46">
+        <v>7.674065914272362</v>
+      </c>
+      <c r="D46">
+        <v>52.51006591427237</v>
+      </c>
+      <c r="E46">
+        <v>32.93600000000001</v>
+      </c>
+      <c r="F46">
+        <v>70.13600000000001</v>
+      </c>
+      <c r="G46">
+        <v>25.3</v>
+      </c>
+      <c r="H46">
+        <v>122.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K46">
+        <v>4.14</v>
+      </c>
+      <c r="L46">
+        <v>5.22</v>
+      </c>
+      <c r="M46">
+        <v>16.7484768</v>
+      </c>
+      <c r="N46">
+        <v>-11.5284768</v>
+      </c>
+      <c r="O46">
+        <v>-2.882119200000001</v>
+      </c>
+      <c r="P46">
+        <v>-8.646357600000002</v>
+      </c>
+      <c r="Q46">
+        <v>-4.506357600000002</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1223720919912969</v>
+      </c>
+      <c r="T46">
+        <v>1.13169945516889</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.0779175333723482</v>
+      </c>
+      <c r="W46">
+        <v>0.2201932930306833</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3116701334893928</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1674134204486269</v>
+      </c>
+      <c r="C47">
+        <v>5.26350935693786</v>
+      </c>
+      <c r="D47">
+        <v>51.69350935693787</v>
+      </c>
+      <c r="E47">
+        <v>34.53</v>
+      </c>
+      <c r="F47">
+        <v>71.73</v>
+      </c>
+      <c r="G47">
+        <v>25.3</v>
+      </c>
+      <c r="H47">
+        <v>122.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K47">
+        <v>4.14</v>
+      </c>
+      <c r="L47">
+        <v>5.22</v>
+      </c>
+      <c r="M47">
+        <v>17.129124</v>
+      </c>
+      <c r="N47">
+        <v>-11.909124</v>
+      </c>
+      <c r="O47">
+        <v>-2.977281000000001</v>
+      </c>
+      <c r="P47">
+        <v>-8.931843000000001</v>
+      </c>
+      <c r="Q47">
+        <v>-4.791843000000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1238915845729569</v>
+      </c>
+      <c r="T47">
+        <v>1.152275808899234</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.07618603263074047</v>
+      </c>
+      <c r="W47">
+        <v>0.2206067754077792</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3047441305229619</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1694134204486269</v>
+      </c>
+      <c r="C48">
+        <v>2.877959619102626</v>
+      </c>
+      <c r="D48">
+        <v>50.90195961910264</v>
+      </c>
+      <c r="E48">
+        <v>36.12400000000001</v>
+      </c>
+      <c r="F48">
+        <v>73.32400000000001</v>
+      </c>
+      <c r="G48">
+        <v>25.3</v>
+      </c>
+      <c r="H48">
+        <v>122.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K48">
+        <v>4.14</v>
+      </c>
+      <c r="L48">
+        <v>5.22</v>
+      </c>
+      <c r="M48">
+        <v>17.5097712</v>
+      </c>
+      <c r="N48">
+        <v>-12.2897712</v>
+      </c>
+      <c r="O48">
+        <v>-3.072442800000001</v>
+      </c>
+      <c r="P48">
+        <v>-9.217328400000003</v>
+      </c>
+      <c r="Q48">
+        <v>-5.077328400000003</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1254673546576413</v>
+      </c>
+      <c r="T48">
+        <v>1.173614249804775</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.07452981453007219</v>
+      </c>
+      <c r="W48">
+        <v>0.2210022802902188</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2981192581202887</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.171413420448627</v>
+      </c>
+      <c r="C49">
+        <v>0.516285284983141</v>
+      </c>
+      <c r="D49">
+        <v>50.13428528498315</v>
+      </c>
+      <c r="E49">
+        <v>37.718</v>
+      </c>
+      <c r="F49">
+        <v>74.91800000000001</v>
+      </c>
+      <c r="G49">
+        <v>25.3</v>
+      </c>
+      <c r="H49">
+        <v>122.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K49">
+        <v>4.14</v>
+      </c>
+      <c r="L49">
+        <v>5.22</v>
+      </c>
+      <c r="M49">
+        <v>17.8904184</v>
+      </c>
+      <c r="N49">
+        <v>-12.6704184</v>
+      </c>
+      <c r="O49">
+        <v>-3.167604600000001</v>
+      </c>
+      <c r="P49">
+        <v>-9.502813800000002</v>
+      </c>
+      <c r="Q49">
+        <v>-5.362813800000002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1271025877643892</v>
+      </c>
+      <c r="T49">
+        <v>1.195757914895431</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.07294407379538982</v>
+      </c>
+      <c r="W49">
+        <v>0.2213809551776609</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2917762951815592</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1734134204486269</v>
+      </c>
+      <c r="C50">
+        <v>-1.822577821799214</v>
+      </c>
+      <c r="D50">
+        <v>49.38942217820078</v>
+      </c>
+      <c r="E50">
+        <v>39.312</v>
+      </c>
+      <c r="F50">
+        <v>76.512</v>
+      </c>
+      <c r="G50">
+        <v>25.3</v>
+      </c>
+      <c r="H50">
+        <v>122.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K50">
+        <v>4.14</v>
+      </c>
+      <c r="L50">
+        <v>5.22</v>
+      </c>
+      <c r="M50">
+        <v>18.2710656</v>
+      </c>
+      <c r="N50">
+        <v>-13.0510656</v>
+      </c>
+      <c r="O50">
+        <v>-3.2627664</v>
+      </c>
+      <c r="P50">
+        <v>-9.788299200000001</v>
+      </c>
+      <c r="Q50">
+        <v>-5.648299200000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.128800714452166</v>
+      </c>
+      <c r="T50">
+        <v>1.218753259412651</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.0714244055913192</v>
+      </c>
+      <c r="W50">
+        <v>0.221743851944793</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2856976223652767</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.175413420448627</v>
+      </c>
+      <c r="C51">
+        <v>-4.139631560092425</v>
+      </c>
+      <c r="D51">
+        <v>48.66636843990757</v>
+      </c>
+      <c r="E51">
+        <v>40.90599999999999</v>
+      </c>
+      <c r="F51">
+        <v>78.10599999999999</v>
+      </c>
+      <c r="G51">
+        <v>25.3</v>
+      </c>
+      <c r="H51">
+        <v>122.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K51">
+        <v>4.14</v>
+      </c>
+      <c r="L51">
+        <v>5.22</v>
+      </c>
+      <c r="M51">
+        <v>18.6517128</v>
+      </c>
+      <c r="N51">
+        <v>-13.4317128</v>
+      </c>
+      <c r="O51">
+        <v>-3.3579282</v>
+      </c>
+      <c r="P51">
+        <v>-10.0737846</v>
+      </c>
+      <c r="Q51">
+        <v>-5.9337846</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1305654343433849</v>
+      </c>
+      <c r="T51">
+        <v>1.242650382146232</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.06996676466088413</v>
+      </c>
+      <c r="W51">
+        <v>0.2220919365989809</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2798670586435364</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1774134204486269</v>
+      </c>
+      <c r="C52">
+        <v>-6.435819966992668</v>
+      </c>
+      <c r="D52">
+        <v>47.96418003300734</v>
+      </c>
+      <c r="E52">
+        <v>42.5</v>
+      </c>
+      <c r="F52">
+        <v>79.7</v>
+      </c>
+      <c r="G52">
+        <v>25.3</v>
+      </c>
+      <c r="H52">
+        <v>122.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K52">
+        <v>4.14</v>
+      </c>
+      <c r="L52">
+        <v>5.22</v>
+      </c>
+      <c r="M52">
+        <v>19.03236</v>
+      </c>
+      <c r="N52">
+        <v>-13.81236</v>
+      </c>
+      <c r="O52">
+        <v>-3.45309</v>
+      </c>
+      <c r="P52">
+        <v>-10.35927</v>
+      </c>
+      <c r="Q52">
+        <v>-6.219270000000003</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1324007430302526</v>
+      </c>
+      <c r="T52">
+        <v>1.267503389789157</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.06856742936766644</v>
+      </c>
+      <c r="W52">
+        <v>0.2224260978670013</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2742697174706656</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1794134204486269</v>
+      </c>
+      <c r="C53">
+        <v>-8.712033369952053</v>
+      </c>
+      <c r="D53">
+        <v>47.28196663004796</v>
+      </c>
+      <c r="E53">
+        <v>44.09400000000001</v>
+      </c>
+      <c r="F53">
+        <v>81.29400000000001</v>
+      </c>
+      <c r="G53">
+        <v>25.3</v>
+      </c>
+      <c r="H53">
+        <v>122.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K53">
+        <v>4.14</v>
+      </c>
+      <c r="L53">
+        <v>5.22</v>
+      </c>
+      <c r="M53">
+        <v>19.4130072</v>
+      </c>
+      <c r="N53">
+        <v>-14.1930072</v>
+      </c>
+      <c r="O53">
+        <v>-3.548251800000001</v>
+      </c>
+      <c r="P53">
+        <v>-10.6447554</v>
+      </c>
+      <c r="Q53">
+        <v>-6.504755400000003</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1343109622757679</v>
+      </c>
+      <c r="T53">
+        <v>1.293370805907303</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.06722296996830042</v>
+      </c>
+      <c r="W53">
+        <v>0.2227471547715699</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.2688918798732016</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1814134204486269</v>
+      </c>
+      <c r="C54">
+        <v>-10.96911215287879</v>
+      </c>
+      <c r="D54">
+        <v>46.61888784712121</v>
+      </c>
+      <c r="E54">
+        <v>45.688</v>
+      </c>
+      <c r="F54">
+        <v>82.88800000000001</v>
+      </c>
+      <c r="G54">
+        <v>25.3</v>
+      </c>
+      <c r="H54">
+        <v>122.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K54">
+        <v>4.14</v>
+      </c>
+      <c r="L54">
+        <v>5.22</v>
+      </c>
+      <c r="M54">
+        <v>19.7936544</v>
+      </c>
+      <c r="N54">
+        <v>-14.5736544</v>
+      </c>
+      <c r="O54">
+        <v>-3.643413600000001</v>
+      </c>
+      <c r="P54">
+        <v>-10.9302408</v>
+      </c>
+      <c r="Q54">
+        <v>-6.790240800000002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1363007739898465</v>
+      </c>
+      <c r="T54">
+        <v>1.320316031030372</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.06593022054583311</v>
+      </c>
+      <c r="W54">
+        <v>0.2230558633336551</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2637208821833323</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1834134204486269</v>
+      </c>
+      <c r="C55">
+        <v>-13.20785020972716</v>
+      </c>
+      <c r="D55">
+        <v>45.97414979027285</v>
+      </c>
+      <c r="E55">
+        <v>47.28200000000001</v>
+      </c>
+      <c r="F55">
+        <v>84.48200000000001</v>
+      </c>
+      <c r="G55">
+        <v>25.3</v>
+      </c>
+      <c r="H55">
+        <v>122.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K55">
+        <v>4.14</v>
+      </c>
+      <c r="L55">
+        <v>5.22</v>
+      </c>
+      <c r="M55">
+        <v>20.1743016</v>
+      </c>
+      <c r="N55">
+        <v>-14.9543016</v>
+      </c>
+      <c r="O55">
+        <v>-3.738575400000001</v>
+      </c>
+      <c r="P55">
+        <v>-11.2157262</v>
+      </c>
+      <c r="Q55">
+        <v>-7.075726200000003</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1383752585428219</v>
+      </c>
+      <c r="T55">
+        <v>1.348407861477827</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.06468625412044002</v>
+      </c>
+      <c r="W55">
+        <v>0.2233529225160389</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2587450164817601</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1854134204486269</v>
+      </c>
+      <c r="C56">
+        <v>-15.42899811541812</v>
+      </c>
+      <c r="D56">
+        <v>45.34700188458188</v>
+      </c>
+      <c r="E56">
+        <v>48.876</v>
+      </c>
+      <c r="F56">
+        <v>86.07600000000001</v>
+      </c>
+      <c r="G56">
+        <v>25.3</v>
+      </c>
+      <c r="H56">
+        <v>122.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K56">
+        <v>4.14</v>
+      </c>
+      <c r="L56">
+        <v>5.22</v>
+      </c>
+      <c r="M56">
+        <v>20.5549488</v>
+      </c>
+      <c r="N56">
+        <v>-15.3349488</v>
+      </c>
+      <c r="O56">
+        <v>-3.833737200000001</v>
+      </c>
+      <c r="P56">
+        <v>-11.5012116</v>
+      </c>
+      <c r="Q56">
+        <v>-7.361211600000002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1405399380763615</v>
+      </c>
+      <c r="T56">
+        <v>1.37772107585778</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.06348836052561706</v>
+      </c>
+      <c r="W56">
+        <v>0.2236389795064827</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2539534421024682</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.187413420448627</v>
+      </c>
+      <c r="C57">
+        <v>-17.63326604071977</v>
+      </c>
+      <c r="D57">
+        <v>44.73673395928024</v>
+      </c>
+      <c r="E57">
+        <v>50.47000000000001</v>
+      </c>
+      <c r="F57">
+        <v>87.67000000000002</v>
+      </c>
+      <c r="G57">
+        <v>25.3</v>
+      </c>
+      <c r="H57">
+        <v>122.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K57">
+        <v>4.14</v>
+      </c>
+      <c r="L57">
+        <v>5.22</v>
+      </c>
+      <c r="M57">
+        <v>20.935596</v>
+      </c>
+      <c r="N57">
+        <v>-15.71559600000001</v>
+      </c>
+      <c r="O57">
+        <v>-3.928899000000001</v>
+      </c>
+      <c r="P57">
+        <v>-11.786697</v>
+      </c>
+      <c r="Q57">
+        <v>-7.646697000000004</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1428008255891696</v>
+      </c>
+      <c r="T57">
+        <v>1.40833709976573</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.06233402669787857</v>
+      </c>
+      <c r="W57">
+        <v>0.2239146344245466</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2493361067915142</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.189413420448627</v>
+      </c>
+      <c r="C58">
+        <v>-19.82132643488683</v>
+      </c>
+      <c r="D58">
+        <v>44.14267356511318</v>
+      </c>
+      <c r="E58">
+        <v>52.06400000000001</v>
+      </c>
+      <c r="F58">
+        <v>89.26400000000001</v>
+      </c>
+      <c r="G58">
+        <v>25.3</v>
+      </c>
+      <c r="H58">
+        <v>122.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K58">
+        <v>4.14</v>
+      </c>
+      <c r="L58">
+        <v>5.22</v>
+      </c>
+      <c r="M58">
+        <v>21.3162432</v>
+      </c>
+      <c r="N58">
+        <v>-16.0962432</v>
+      </c>
+      <c r="O58">
+        <v>-4.024060800000001</v>
+      </c>
+      <c r="P58">
+        <v>-12.0721824</v>
+      </c>
+      <c r="Q58">
+        <v>-7.932182400000003</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1451644807161961</v>
+      </c>
+      <c r="T58">
+        <v>1.440344761124043</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.06122091907827359</v>
+      </c>
+      <c r="W58">
+        <v>0.2241804445241083</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2448836763130944</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.191413420448627</v>
+      </c>
+      <c r="C59">
+        <v>-21.99381649736431</v>
+      </c>
+      <c r="D59">
+        <v>43.56418350263571</v>
+      </c>
+      <c r="E59">
+        <v>53.65800000000002</v>
+      </c>
+      <c r="F59">
+        <v>90.85800000000002</v>
+      </c>
+      <c r="G59">
+        <v>25.3</v>
+      </c>
+      <c r="H59">
+        <v>122.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K59">
+        <v>4.14</v>
+      </c>
+      <c r="L59">
+        <v>5.22</v>
+      </c>
+      <c r="M59">
+        <v>21.6968904</v>
+      </c>
+      <c r="N59">
+        <v>-16.47689040000001</v>
+      </c>
+      <c r="O59">
+        <v>-4.119222600000001</v>
+      </c>
+      <c r="P59">
+        <v>-12.35766780000001</v>
+      </c>
+      <c r="Q59">
+        <v>-8.217667800000005</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1476380732909914</v>
+      </c>
+      <c r="T59">
+        <v>1.473841150917625</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.06014686786637406</v>
+      </c>
+      <c r="W59">
+        <v>0.2244369279535099</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2405874714654962</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1934134204486269</v>
+      </c>
+      <c r="C60">
+        <v>-24.15134045765478</v>
+      </c>
+      <c r="D60">
+        <v>43.00065954234521</v>
+      </c>
+      <c r="E60">
+        <v>55.252</v>
+      </c>
+      <c r="F60">
+        <v>92.452</v>
+      </c>
+      <c r="G60">
+        <v>25.3</v>
+      </c>
+      <c r="H60">
+        <v>122.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K60">
+        <v>4.14</v>
+      </c>
+      <c r="L60">
+        <v>5.22</v>
+      </c>
+      <c r="M60">
+        <v>22.0775376</v>
+      </c>
+      <c r="N60">
+        <v>-16.8575376</v>
+      </c>
+      <c r="O60">
+        <v>-4.2143844</v>
+      </c>
+      <c r="P60">
+        <v>-12.6431532</v>
+      </c>
+      <c r="Q60">
+        <v>-8.5031532</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1502294559883959</v>
+      </c>
+      <c r="T60">
+        <v>1.508932606891853</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.05910985290316072</v>
+      </c>
+      <c r="W60">
+        <v>0.2246845671267252</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2364394116126428</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1954134204486269</v>
+      </c>
+      <c r="C61">
+        <v>-26.29447168049849</v>
+      </c>
+      <c r="D61">
+        <v>42.45152831950151</v>
+      </c>
+      <c r="E61">
+        <v>56.84599999999999</v>
+      </c>
+      <c r="F61">
+        <v>94.04599999999999</v>
+      </c>
+      <c r="G61">
+        <v>25.3</v>
+      </c>
+      <c r="H61">
+        <v>122.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K61">
+        <v>4.14</v>
+      </c>
+      <c r="L61">
+        <v>5.22</v>
+      </c>
+      <c r="M61">
+        <v>22.4581848</v>
+      </c>
+      <c r="N61">
+        <v>-17.2381848</v>
+      </c>
+      <c r="O61">
+        <v>-4.3095462</v>
+      </c>
+      <c r="P61">
+        <v>-12.9286386</v>
+      </c>
+      <c r="Q61">
+        <v>-8.788638599999999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.152947247597869</v>
+      </c>
+      <c r="T61">
+        <v>1.545735841206289</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.05810799098954783</v>
+      </c>
+      <c r="W61">
+        <v>0.224923811751696</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2324319639581913</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1974134204486269</v>
+      </c>
+      <c r="C62">
+        <v>-28.42375461178426</v>
+      </c>
+      <c r="D62">
+        <v>41.91624538821574</v>
+      </c>
+      <c r="E62">
+        <v>58.44</v>
+      </c>
+      <c r="F62">
+        <v>95.64</v>
+      </c>
+      <c r="G62">
+        <v>25.3</v>
+      </c>
+      <c r="H62">
+        <v>122.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K62">
+        <v>4.14</v>
+      </c>
+      <c r="L62">
+        <v>5.22</v>
+      </c>
+      <c r="M62">
+        <v>22.838832</v>
+      </c>
+      <c r="N62">
+        <v>-17.618832</v>
+      </c>
+      <c r="O62">
+        <v>-4.404708</v>
+      </c>
+      <c r="P62">
+        <v>-13.214124</v>
+      </c>
+      <c r="Q62">
+        <v>-9.074124000000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1558009287878157</v>
+      </c>
+      <c r="T62">
+        <v>1.584379237236446</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.05713952447305536</v>
+      </c>
+      <c r="W62">
+        <v>0.2251550815558344</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2285580978922214</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1994134204486269</v>
+      </c>
+      <c r="C63">
+        <v>-30.53970657907485</v>
+      </c>
+      <c r="D63">
+        <v>41.39429342092515</v>
+      </c>
+      <c r="E63">
+        <v>60.03399999999999</v>
+      </c>
+      <c r="F63">
+        <v>97.23399999999999</v>
+      </c>
+      <c r="G63">
+        <v>25.3</v>
+      </c>
+      <c r="H63">
+        <v>122.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K63">
+        <v>4.14</v>
+      </c>
+      <c r="L63">
+        <v>5.22</v>
+      </c>
+      <c r="M63">
+        <v>23.2194792</v>
+      </c>
+      <c r="N63">
+        <v>-17.9994792</v>
+      </c>
+      <c r="O63">
+        <v>-4.4998698</v>
+      </c>
+      <c r="P63">
+        <v>-13.4996094</v>
+      </c>
+      <c r="Q63">
+        <v>-9.3596094</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1588009526028879</v>
+      </c>
+      <c r="T63">
+        <v>1.625004345883535</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.05620281095710364</v>
+      </c>
+      <c r="W63">
+        <v>0.2253787687434436</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2248112438284146</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2014134204486269</v>
+      </c>
+      <c r="C64">
+        <v>-32.64281945926302</v>
+      </c>
+      <c r="D64">
+        <v>40.88518054073698</v>
+      </c>
+      <c r="E64">
+        <v>61.628</v>
+      </c>
+      <c r="F64">
+        <v>98.828</v>
+      </c>
+      <c r="G64">
+        <v>25.3</v>
+      </c>
+      <c r="H64">
+        <v>122.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K64">
+        <v>4.14</v>
+      </c>
+      <c r="L64">
+        <v>5.22</v>
+      </c>
+      <c r="M64">
+        <v>23.6001264</v>
+      </c>
+      <c r="N64">
+        <v>-18.3801264</v>
+      </c>
+      <c r="O64">
+        <v>-4.5950316</v>
+      </c>
+      <c r="P64">
+        <v>-13.7850948</v>
+      </c>
+      <c r="Q64">
+        <v>-9.645094800000003</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1619588724082271</v>
+      </c>
+      <c r="T64">
+        <v>1.667767618143628</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.05529631400618261</v>
+      </c>
+      <c r="W64">
+        <v>0.2255952402153236</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2211852560247304</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2034134204486269</v>
+      </c>
+      <c r="C65">
+        <v>-34.73356122465873</v>
+      </c>
+      <c r="D65">
+        <v>40.38843877534129</v>
+      </c>
+      <c r="E65">
+        <v>63.22200000000001</v>
+      </c>
+      <c r="F65">
+        <v>100.422</v>
+      </c>
+      <c r="G65">
+        <v>25.3</v>
+      </c>
+      <c r="H65">
+        <v>122.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K65">
+        <v>4.14</v>
+      </c>
+      <c r="L65">
+        <v>5.22</v>
+      </c>
+      <c r="M65">
+        <v>23.9807736</v>
+      </c>
+      <c r="N65">
+        <v>-18.7607736</v>
+      </c>
+      <c r="O65">
+        <v>-4.690193400000001</v>
+      </c>
+      <c r="P65">
+        <v>-14.0705802</v>
+      </c>
+      <c r="Q65">
+        <v>-9.930580200000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1652874905814224</v>
+      </c>
+      <c r="T65">
+        <v>1.712842418633996</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.0544185947362432</v>
+      </c>
+      <c r="W65">
+        <v>0.2258048395769851</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2176743789449728</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2054134204486269</v>
+      </c>
+      <c r="C66">
+        <v>-36.81237737772238</v>
+      </c>
+      <c r="D66">
+        <v>39.90362262227762</v>
+      </c>
+      <c r="E66">
+        <v>64.816</v>
+      </c>
+      <c r="F66">
+        <v>102.016</v>
+      </c>
+      <c r="G66">
+        <v>25.3</v>
+      </c>
+      <c r="H66">
+        <v>122.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K66">
+        <v>4.14</v>
+      </c>
+      <c r="L66">
+        <v>5.22</v>
+      </c>
+      <c r="M66">
+        <v>24.3614208</v>
+      </c>
+      <c r="N66">
+        <v>-19.1414208</v>
+      </c>
+      <c r="O66">
+        <v>-4.785355200000001</v>
+      </c>
+      <c r="P66">
+        <v>-14.3560656</v>
+      </c>
+      <c r="Q66">
+        <v>-10.2160656</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.168801031986462</v>
+      </c>
+      <c r="T66">
+        <v>1.760421374707163</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.0535683041934894</v>
+      </c>
+      <c r="W66">
+        <v>0.2260078889585947</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2142732167739576</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2074134204486269</v>
+      </c>
+      <c r="C67">
+        <v>-38.87969228369022</v>
+      </c>
+      <c r="D67">
+        <v>39.43030771630979</v>
+      </c>
+      <c r="E67">
+        <v>66.41000000000001</v>
+      </c>
+      <c r="F67">
+        <v>103.61</v>
+      </c>
+      <c r="G67">
+        <v>25.3</v>
+      </c>
+      <c r="H67">
+        <v>122.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K67">
+        <v>4.14</v>
+      </c>
+      <c r="L67">
+        <v>5.22</v>
+      </c>
+      <c r="M67">
+        <v>24.742068</v>
+      </c>
+      <c r="N67">
+        <v>-19.522068</v>
+      </c>
+      <c r="O67">
+        <v>-4.880517000000001</v>
+      </c>
+      <c r="P67">
+        <v>-14.641551</v>
+      </c>
+      <c r="Q67">
+        <v>-10.501551</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1725153471860751</v>
+      </c>
+      <c r="T67">
+        <v>1.810719128270225</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.05274417643666648</v>
+      </c>
+      <c r="W67">
+        <v>0.2262046906669241</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2109767057466659</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2094134204486269</v>
+      </c>
+      <c r="C68">
+        <v>-40.93591040946987</v>
+      </c>
+      <c r="D68">
+        <v>38.96808959053014</v>
+      </c>
+      <c r="E68">
+        <v>68.004</v>
+      </c>
+      <c r="F68">
+        <v>105.204</v>
+      </c>
+      <c r="G68">
+        <v>25.3</v>
+      </c>
+      <c r="H68">
+        <v>122.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K68">
+        <v>4.14</v>
+      </c>
+      <c r="L68">
+        <v>5.22</v>
+      </c>
+      <c r="M68">
+        <v>25.1227152</v>
+      </c>
+      <c r="N68">
+        <v>-19.9027152</v>
+      </c>
+      <c r="O68">
+        <v>-4.975678800000001</v>
+      </c>
+      <c r="P68">
+        <v>-14.9270364</v>
+      </c>
+      <c r="Q68">
+        <v>-10.7870364</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1764481515150773</v>
+      </c>
+      <c r="T68">
+        <v>1.863975573219349</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.05194502224823214</v>
+      </c>
+      <c r="W68">
+        <v>0.2263955286871222</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2077800889929285</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2114134204486269</v>
+      </c>
+      <c r="C69">
+        <v>-42.98141747640882</v>
+      </c>
+      <c r="D69">
+        <v>38.51658252359119</v>
+      </c>
+      <c r="E69">
+        <v>69.59800000000001</v>
+      </c>
+      <c r="F69">
+        <v>106.798</v>
+      </c>
+      <c r="G69">
+        <v>25.3</v>
+      </c>
+      <c r="H69">
+        <v>122.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K69">
+        <v>4.14</v>
+      </c>
+      <c r="L69">
+        <v>5.22</v>
+      </c>
+      <c r="M69">
+        <v>25.5033624</v>
+      </c>
+      <c r="N69">
+        <v>-20.28336240000001</v>
+      </c>
+      <c r="O69">
+        <v>-5.070840600000001</v>
+      </c>
+      <c r="P69">
+        <v>-15.2125218</v>
+      </c>
+      <c r="Q69">
+        <v>-11.0725218</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1806193076215948</v>
+      </c>
+      <c r="T69">
+        <v>1.920459681498723</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.05116972340870628</v>
+      </c>
+      <c r="W69">
+        <v>0.226580670050001</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2046788936348252</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2134134204486269</v>
+      </c>
+      <c r="C70">
+        <v>-45.01658153384075</v>
+      </c>
+      <c r="D70">
+        <v>38.07541846615926</v>
+      </c>
+      <c r="E70">
+        <v>71.19200000000001</v>
+      </c>
+      <c r="F70">
+        <v>108.392</v>
+      </c>
+      <c r="G70">
+        <v>25.3</v>
+      </c>
+      <c r="H70">
+        <v>122.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K70">
+        <v>4.14</v>
+      </c>
+      <c r="L70">
+        <v>5.22</v>
+      </c>
+      <c r="M70">
+        <v>25.8840096</v>
+      </c>
+      <c r="N70">
+        <v>-20.6640096</v>
+      </c>
+      <c r="O70">
+        <v>-5.166002400000001</v>
+      </c>
+      <c r="P70">
+        <v>-15.4980072</v>
+      </c>
+      <c r="Q70">
+        <v>-11.3580072</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1850511609847697</v>
+      </c>
+      <c r="T70">
+        <v>1.980474046545558</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.05041722747622532</v>
+      </c>
+      <c r="W70">
+        <v>0.2267603660786774</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2016689099049013</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2154134204486269</v>
+      </c>
+      <c r="C71">
+        <v>-47.04175395968973</v>
+      </c>
+      <c r="D71">
+        <v>37.64424604031029</v>
+      </c>
+      <c r="E71">
+        <v>72.78600000000002</v>
+      </c>
+      <c r="F71">
+        <v>109.986</v>
+      </c>
+      <c r="G71">
+        <v>25.3</v>
+      </c>
+      <c r="H71">
+        <v>122.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K71">
+        <v>4.14</v>
+      </c>
+      <c r="L71">
+        <v>5.22</v>
+      </c>
+      <c r="M71">
+        <v>26.2646568</v>
+      </c>
+      <c r="N71">
+        <v>-21.04465680000001</v>
+      </c>
+      <c r="O71">
+        <v>-5.261164200000001</v>
+      </c>
+      <c r="P71">
+        <v>-15.7834926</v>
+      </c>
+      <c r="Q71">
+        <v>-11.64349260000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1897689403713752</v>
+      </c>
+      <c r="T71">
+        <v>2.044360306111544</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.04968654302004813</v>
+      </c>
+      <c r="W71">
+        <v>0.2269348535268125</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1987461720801925</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2174134204486269</v>
+      </c>
+      <c r="C72">
+        <v>-49.05727039384968</v>
+      </c>
+      <c r="D72">
+        <v>37.22272960615033</v>
+      </c>
+      <c r="E72">
+        <v>74.38000000000001</v>
+      </c>
+      <c r="F72">
+        <v>111.58</v>
+      </c>
+      <c r="G72">
+        <v>25.3</v>
+      </c>
+      <c r="H72">
+        <v>122.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K72">
+        <v>4.14</v>
+      </c>
+      <c r="L72">
+        <v>5.22</v>
+      </c>
+      <c r="M72">
+        <v>26.645304</v>
+      </c>
+      <c r="N72">
+        <v>-21.425304</v>
+      </c>
+      <c r="O72">
+        <v>-5.356326000000001</v>
+      </c>
+      <c r="P72">
+        <v>-16.068978</v>
+      </c>
+      <c r="Q72">
+        <v>-11.928978</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1948012383837543</v>
+      </c>
+      <c r="T72">
+        <v>2.112505649648595</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.04897673526261888</v>
+      </c>
+      <c r="W72">
+        <v>0.2271043556192866</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1959069410504755</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2194134204486269</v>
+      </c>
+      <c r="C73">
+        <v>-51.06345160954996</v>
+      </c>
+      <c r="D73">
+        <v>36.81054839045004</v>
+      </c>
+      <c r="E73">
+        <v>75.97399999999999</v>
+      </c>
+      <c r="F73">
+        <v>113.174</v>
+      </c>
+      <c r="G73">
+        <v>25.3</v>
+      </c>
+      <c r="H73">
+        <v>122.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K73">
+        <v>4.14</v>
+      </c>
+      <c r="L73">
+        <v>5.22</v>
+      </c>
+      <c r="M73">
+        <v>27.0259512</v>
+      </c>
+      <c r="N73">
+        <v>-21.8059512</v>
+      </c>
+      <c r="O73">
+        <v>-5.4514878</v>
+      </c>
+      <c r="P73">
+        <v>-16.3544634</v>
+      </c>
+      <c r="Q73">
+        <v>-12.2144634</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.20018059143147</v>
+      </c>
+      <c r="T73">
+        <v>2.185350672050271</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.04828692208990595</v>
+      </c>
+      <c r="W73">
+        <v>0.2272690830049305</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1931476883596237</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2214134204486269</v>
+      </c>
+      <c r="C74">
+        <v>-53.06060432746102</v>
+      </c>
+      <c r="D74">
+        <v>36.40739567253898</v>
+      </c>
+      <c r="E74">
+        <v>77.568</v>
+      </c>
+      <c r="F74">
+        <v>114.768</v>
+      </c>
+      <c r="G74">
+        <v>25.3</v>
+      </c>
+      <c r="H74">
+        <v>122.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K74">
+        <v>4.14</v>
+      </c>
+      <c r="L74">
+        <v>5.22</v>
+      </c>
+      <c r="M74">
+        <v>27.4065984</v>
+      </c>
+      <c r="N74">
+        <v>-22.1865984</v>
+      </c>
+      <c r="O74">
+        <v>-5.5466496</v>
+      </c>
+      <c r="P74">
+        <v>-16.6399488</v>
+      </c>
+      <c r="Q74">
+        <v>-12.4999488</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2059441839825939</v>
+      </c>
+      <c r="T74">
+        <v>2.26339891033778</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0476162703942128</v>
+      </c>
+      <c r="W74">
+        <v>0.227429234629862</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1904650815768512</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2234134204486269</v>
+      </c>
+      <c r="C75">
+        <v>-55.04902197688287</v>
+      </c>
+      <c r="D75">
+        <v>36.01297802311713</v>
+      </c>
+      <c r="E75">
+        <v>79.16199999999999</v>
+      </c>
+      <c r="F75">
+        <v>116.362</v>
+      </c>
+      <c r="G75">
+        <v>25.3</v>
+      </c>
+      <c r="H75">
+        <v>122.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K75">
+        <v>4.14</v>
+      </c>
+      <c r="L75">
+        <v>5.22</v>
+      </c>
+      <c r="M75">
+        <v>27.7872456</v>
+      </c>
+      <c r="N75">
+        <v>-22.5672456</v>
+      </c>
+      <c r="O75">
+        <v>-5.6418114</v>
+      </c>
+      <c r="P75">
+        <v>-16.9254342</v>
+      </c>
+      <c r="Q75">
+        <v>-12.7854342</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2121347093152826</v>
+      </c>
+      <c r="T75">
+        <v>2.34722849960955</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04696399271757975</v>
+      </c>
+      <c r="W75">
+        <v>0.227584998539042</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.187855970870319</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2254134204486269</v>
+      </c>
+      <c r="C76">
+        <v>-57.02898540798597</v>
+      </c>
+      <c r="D76">
+        <v>35.62701459201403</v>
+      </c>
+      <c r="E76">
+        <v>80.756</v>
+      </c>
+      <c r="F76">
+        <v>117.956</v>
+      </c>
+      <c r="G76">
+        <v>25.3</v>
+      </c>
+      <c r="H76">
+        <v>122.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K76">
+        <v>4.14</v>
+      </c>
+      <c r="L76">
+        <v>5.22</v>
+      </c>
+      <c r="M76">
+        <v>28.1678928</v>
+      </c>
+      <c r="N76">
+        <v>-22.9478928</v>
+      </c>
+      <c r="O76">
+        <v>-5.7369732</v>
+      </c>
+      <c r="P76">
+        <v>-17.2109196</v>
+      </c>
+      <c r="Q76">
+        <v>-13.0709196</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2188014289043319</v>
+      </c>
+      <c r="T76">
+        <v>2.437506518825302</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04632934416734218</v>
+      </c>
+      <c r="W76">
+        <v>0.2277365526128387</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1853173766693688</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2274134204486269</v>
+      </c>
+      <c r="C77">
+        <v>-59.00076355873765</v>
+      </c>
+      <c r="D77">
+        <v>35.24923644126236</v>
+      </c>
+      <c r="E77">
+        <v>82.35000000000001</v>
+      </c>
+      <c r="F77">
+        <v>119.55</v>
+      </c>
+      <c r="G77">
+        <v>25.3</v>
+      </c>
+      <c r="H77">
+        <v>122.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K77">
+        <v>4.14</v>
+      </c>
+      <c r="L77">
+        <v>5.22</v>
+      </c>
+      <c r="M77">
+        <v>28.54854</v>
+      </c>
+      <c r="N77">
+        <v>-23.32854</v>
+      </c>
+      <c r="O77">
+        <v>-5.832135000000001</v>
+      </c>
+      <c r="P77">
+        <v>-17.496405</v>
+      </c>
+      <c r="Q77">
+        <v>-13.356405</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2260014860605052</v>
+      </c>
+      <c r="T77">
+        <v>2.535006779578314</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04571161957844429</v>
+      </c>
+      <c r="W77">
+        <v>0.2278840652446675</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1828464783137771</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2294134204486269</v>
+      </c>
+      <c r="C78">
+        <v>-60.9646140798426</v>
+      </c>
+      <c r="D78">
+        <v>34.8793859201574</v>
+      </c>
+      <c r="E78">
+        <v>83.944</v>
+      </c>
+      <c r="F78">
+        <v>121.144</v>
+      </c>
+      <c r="G78">
+        <v>25.3</v>
+      </c>
+      <c r="H78">
+        <v>122.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K78">
+        <v>4.14</v>
+      </c>
+      <c r="L78">
+        <v>5.22</v>
+      </c>
+      <c r="M78">
+        <v>28.9291872</v>
+      </c>
+      <c r="N78">
+        <v>-23.7091872</v>
+      </c>
+      <c r="O78">
+        <v>-5.927296800000001</v>
+      </c>
+      <c r="P78">
+        <v>-17.7818904</v>
+      </c>
+      <c r="Q78">
+        <v>-13.6418904</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2338015479796929</v>
+      </c>
+      <c r="T78">
+        <v>2.640632062060744</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.04511015089978055</v>
+      </c>
+      <c r="W78">
+        <v>0.2280276959651324</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1804406035991222</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2314134204486269</v>
+      </c>
+      <c r="C79">
+        <v>-62.920783920749</v>
+      </c>
+      <c r="D79">
+        <v>34.51721607925101</v>
+      </c>
+      <c r="E79">
+        <v>85.53800000000001</v>
+      </c>
+      <c r="F79">
+        <v>122.738</v>
+      </c>
+      <c r="G79">
+        <v>25.3</v>
+      </c>
+      <c r="H79">
+        <v>122.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K79">
+        <v>4.14</v>
+      </c>
+      <c r="L79">
+        <v>5.22</v>
+      </c>
+      <c r="M79">
+        <v>29.3098344</v>
+      </c>
+      <c r="N79">
+        <v>-24.0898344</v>
+      </c>
+      <c r="O79">
+        <v>-6.022458600000001</v>
+      </c>
+      <c r="P79">
+        <v>-18.0673758</v>
+      </c>
+      <c r="Q79">
+        <v>-13.9273758</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.242279876152723</v>
+      </c>
+      <c r="T79">
+        <v>2.755442151715559</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04452430478419898</v>
+      </c>
+      <c r="W79">
+        <v>0.2281675960175333</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1780972191367959</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.233413420448627</v>
+      </c>
+      <c r="C80">
+        <v>-64.86950987952081</v>
+      </c>
+      <c r="D80">
+        <v>34.1624901204792</v>
+      </c>
+      <c r="E80">
+        <v>87.13200000000001</v>
+      </c>
+      <c r="F80">
+        <v>124.332</v>
+      </c>
+      <c r="G80">
+        <v>25.3</v>
+      </c>
+      <c r="H80">
+        <v>122.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K80">
+        <v>4.14</v>
+      </c>
+      <c r="L80">
+        <v>5.22</v>
+      </c>
+      <c r="M80">
+        <v>29.6904816</v>
+      </c>
+      <c r="N80">
+        <v>-24.4704816</v>
+      </c>
+      <c r="O80">
+        <v>-6.117620400000001</v>
+      </c>
+      <c r="P80">
+        <v>-18.3528612</v>
+      </c>
+      <c r="Q80">
+        <v>-14.2128612</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2515289614323923</v>
+      </c>
+      <c r="T80">
+        <v>2.880689522248085</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04395348036388873</v>
+      </c>
+      <c r="W80">
+        <v>0.2283039088891034</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.175813921455555</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.235413420448627</v>
+      </c>
+      <c r="C81">
+        <v>-66.81101911914982</v>
+      </c>
+      <c r="D81">
+        <v>33.81498088085019</v>
+      </c>
+      <c r="E81">
+        <v>88.72600000000001</v>
+      </c>
+      <c r="F81">
+        <v>125.926</v>
+      </c>
+      <c r="G81">
+        <v>25.3</v>
+      </c>
+      <c r="H81">
+        <v>122.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K81">
+        <v>4.14</v>
+      </c>
+      <c r="L81">
+        <v>5.22</v>
+      </c>
+      <c r="M81">
+        <v>30.0711288</v>
+      </c>
+      <c r="N81">
+        <v>-24.85112880000001</v>
+      </c>
+      <c r="O81">
+        <v>-6.212782200000001</v>
+      </c>
+      <c r="P81">
+        <v>-18.63834660000001</v>
+      </c>
+      <c r="Q81">
+        <v>-14.4983466</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2616589119767919</v>
+      </c>
+      <c r="T81">
+        <v>3.017865213783708</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04339710719472559</v>
+      </c>
+      <c r="W81">
+        <v>0.2284367708018996</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1735884287789023</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2374134204486269</v>
+      </c>
+      <c r="C82">
+        <v>-68.74552965267235</v>
+      </c>
+      <c r="D82">
+        <v>33.47447034732766</v>
+      </c>
+      <c r="E82">
+        <v>90.32000000000001</v>
+      </c>
+      <c r="F82">
+        <v>127.52</v>
+      </c>
+      <c r="G82">
+        <v>25.3</v>
+      </c>
+      <c r="H82">
+        <v>122.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K82">
+        <v>4.14</v>
+      </c>
+      <c r="L82">
+        <v>5.22</v>
+      </c>
+      <c r="M82">
+        <v>30.451776</v>
+      </c>
+      <c r="N82">
+        <v>-25.231776</v>
+      </c>
+      <c r="O82">
+        <v>-6.307944000000001</v>
+      </c>
+      <c r="P82">
+        <v>-18.923832</v>
+      </c>
+      <c r="Q82">
+        <v>-14.783832</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2728018575756315</v>
+      </c>
+      <c r="T82">
+        <v>3.168758474472893</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04285464335479152</v>
+      </c>
+      <c r="W82">
+        <v>0.2285663111668758</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.171418573419166</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.239413420448627</v>
+      </c>
+      <c r="C83">
+        <v>-70.67325079926832</v>
+      </c>
+      <c r="D83">
+        <v>33.14074920073168</v>
+      </c>
+      <c r="E83">
+        <v>91.914</v>
+      </c>
+      <c r="F83">
+        <v>129.114</v>
+      </c>
+      <c r="G83">
+        <v>25.3</v>
+      </c>
+      <c r="H83">
+        <v>122.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K83">
+        <v>4.14</v>
+      </c>
+      <c r="L83">
+        <v>5.22</v>
+      </c>
+      <c r="M83">
+        <v>30.8324232</v>
+      </c>
+      <c r="N83">
+        <v>-25.6124232</v>
+      </c>
+      <c r="O83">
+        <v>-6.403105800000001</v>
+      </c>
+      <c r="P83">
+        <v>-19.2093174</v>
+      </c>
+      <c r="Q83">
+        <v>-15.0693174</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2851177448164542</v>
+      </c>
+      <c r="T83">
+        <v>3.335535236287257</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04232557368374471</v>
+      </c>
+      <c r="W83">
+        <v>0.2286926530043218</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1693022947349788</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.241413420448627</v>
+      </c>
+      <c r="C84">
+        <v>-72.59438361334702</v>
+      </c>
+      <c r="D84">
+        <v>32.81361638665301</v>
+      </c>
+      <c r="E84">
+        <v>93.50800000000002</v>
+      </c>
+      <c r="F84">
+        <v>130.708</v>
+      </c>
+      <c r="G84">
+        <v>25.3</v>
+      </c>
+      <c r="H84">
+        <v>122.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K84">
+        <v>4.14</v>
+      </c>
+      <c r="L84">
+        <v>5.22</v>
+      </c>
+      <c r="M84">
+        <v>31.21307040000001</v>
+      </c>
+      <c r="N84">
+        <v>-25.99307040000001</v>
+      </c>
+      <c r="O84">
+        <v>-6.498267600000002</v>
+      </c>
+      <c r="P84">
+        <v>-19.49480280000001</v>
+      </c>
+      <c r="Q84">
+        <v>-15.35480280000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.298802063972924</v>
+      </c>
+      <c r="T84">
+        <v>3.520842749414327</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04180940815101611</v>
+      </c>
+      <c r="W84">
+        <v>0.2288159133335374</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1672376326040644</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.243413420448627</v>
+      </c>
+      <c r="C85">
+        <v>-74.50912128846829</v>
+      </c>
+      <c r="D85">
+        <v>32.49287871153172</v>
+      </c>
+      <c r="E85">
+        <v>95.10200000000002</v>
+      </c>
+      <c r="F85">
+        <v>132.302</v>
+      </c>
+      <c r="G85">
+        <v>25.3</v>
+      </c>
+      <c r="H85">
+        <v>122.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K85">
+        <v>4.14</v>
+      </c>
+      <c r="L85">
+        <v>5.22</v>
+      </c>
+      <c r="M85">
+        <v>31.59371760000001</v>
+      </c>
+      <c r="N85">
+        <v>-26.37371760000001</v>
+      </c>
+      <c r="O85">
+        <v>-6.593429400000002</v>
+      </c>
+      <c r="P85">
+        <v>-19.7802882</v>
+      </c>
+      <c r="Q85">
+        <v>-15.6402882</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3140963030301548</v>
+      </c>
+      <c r="T85">
+        <v>3.727951146438699</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.04130568034196772</v>
+      </c>
+      <c r="W85">
+        <v>0.2289362035343381</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1652227213678709</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.245413420448627</v>
+      </c>
+      <c r="C86">
+        <v>-76.41764953780442</v>
+      </c>
+      <c r="D86">
+        <v>32.17835046219557</v>
+      </c>
+      <c r="E86">
+        <v>96.69599999999998</v>
+      </c>
+      <c r="F86">
+        <v>133.896</v>
+      </c>
+      <c r="G86">
+        <v>25.3</v>
+      </c>
+      <c r="H86">
+        <v>122.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K86">
+        <v>4.14</v>
+      </c>
+      <c r="L86">
+        <v>5.22</v>
+      </c>
+      <c r="M86">
+        <v>31.9743648</v>
+      </c>
+      <c r="N86">
+        <v>-26.7543648</v>
+      </c>
+      <c r="O86">
+        <v>-6.6885912</v>
+      </c>
+      <c r="P86">
+        <v>-20.0657736</v>
+      </c>
+      <c r="Q86">
+        <v>-15.9257736</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3313023219695393</v>
+      </c>
+      <c r="T86">
+        <v>3.960948093091115</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0408139460521824</v>
+      </c>
+      <c r="W86">
+        <v>0.2290536296827389</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1632557842087295</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2474134204486269</v>
+      </c>
+      <c r="C87">
+        <v>-78.32014695271663</v>
+      </c>
+      <c r="D87">
+        <v>31.86985304728338</v>
+      </c>
+      <c r="E87">
+        <v>98.29000000000001</v>
+      </c>
+      <c r="F87">
+        <v>135.49</v>
+      </c>
+      <c r="G87">
+        <v>25.3</v>
+      </c>
+      <c r="H87">
+        <v>122.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K87">
+        <v>4.14</v>
+      </c>
+      <c r="L87">
+        <v>5.22</v>
+      </c>
+      <c r="M87">
+        <v>32.355012</v>
+      </c>
+      <c r="N87">
+        <v>-27.135012</v>
+      </c>
+      <c r="O87">
+        <v>-6.783753000000001</v>
+      </c>
+      <c r="P87">
+        <v>-20.351259</v>
+      </c>
+      <c r="Q87">
+        <v>-16.211259</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3508024767675086</v>
+      </c>
+      <c r="T87">
+        <v>4.22501129929719</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04033378198098025</v>
+      </c>
+      <c r="W87">
+        <v>0.2291682928629419</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.161335127923921</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2494134204486269</v>
+      </c>
+      <c r="C88">
+        <v>-80.21678534090097</v>
+      </c>
+      <c r="D88">
+        <v>31.56721465909903</v>
+      </c>
+      <c r="E88">
+        <v>99.884</v>
+      </c>
+      <c r="F88">
+        <v>137.084</v>
+      </c>
+      <c r="G88">
+        <v>25.3</v>
+      </c>
+      <c r="H88">
+        <v>122.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K88">
+        <v>4.14</v>
+      </c>
+      <c r="L88">
+        <v>5.22</v>
+      </c>
+      <c r="M88">
+        <v>32.7356592</v>
+      </c>
+      <c r="N88">
+        <v>-27.5156592</v>
+      </c>
+      <c r="O88">
+        <v>-6.8789148</v>
+      </c>
+      <c r="P88">
+        <v>-20.6367444</v>
+      </c>
+      <c r="Q88">
+        <v>-16.4967444</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3730883679651878</v>
+      </c>
+      <c r="T88">
+        <v>4.526797820675561</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03986478451608513</v>
+      </c>
+      <c r="W88">
+        <v>0.2292802894575589</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1594591380643405</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2514134204486269</v>
+      </c>
+      <c r="C89">
+        <v>-82.10773004544964</v>
+      </c>
+      <c r="D89">
+        <v>31.27026995455036</v>
+      </c>
+      <c r="E89">
+        <v>101.478</v>
+      </c>
+      <c r="F89">
+        <v>138.678</v>
+      </c>
+      <c r="G89">
+        <v>25.3</v>
+      </c>
+      <c r="H89">
+        <v>122.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K89">
+        <v>4.14</v>
+      </c>
+      <c r="L89">
+        <v>5.22</v>
+      </c>
+      <c r="M89">
+        <v>33.1163064</v>
+      </c>
+      <c r="N89">
+        <v>-27.8963064</v>
+      </c>
+      <c r="O89">
+        <v>-6.9740766</v>
+      </c>
+      <c r="P89">
+        <v>-20.9222298</v>
+      </c>
+      <c r="Q89">
+        <v>-16.7822298</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3988028578086638</v>
+      </c>
+      <c r="T89">
+        <v>4.875013037650604</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03940656860210714</v>
+      </c>
+      <c r="W89">
+        <v>0.2293897114178168</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1576262744084286</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2534134204486269</v>
+      </c>
+      <c r="C90">
+        <v>-83.99314024607162</v>
+      </c>
+      <c r="D90">
+        <v>30.97885975392839</v>
+      </c>
+      <c r="E90">
+        <v>103.072</v>
+      </c>
+      <c r="F90">
+        <v>140.272</v>
+      </c>
+      <c r="G90">
+        <v>25.3</v>
+      </c>
+      <c r="H90">
+        <v>122.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K90">
+        <v>4.14</v>
+      </c>
+      <c r="L90">
+        <v>5.22</v>
+      </c>
+      <c r="M90">
+        <v>33.4969536</v>
+      </c>
+      <c r="N90">
+        <v>-28.27695360000001</v>
+      </c>
+      <c r="O90">
+        <v>-7.069238400000001</v>
+      </c>
+      <c r="P90">
+        <v>-21.2077152</v>
+      </c>
+      <c r="Q90">
+        <v>-17.0677152</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4288030959593858</v>
+      </c>
+      <c r="T90">
+        <v>5.281264124121487</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.0389587666861741</v>
+      </c>
+      <c r="W90">
+        <v>0.2294966465153416</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1558350667446964</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2554134204486269</v>
+      </c>
+      <c r="C91">
+        <v>-85.87316924362651</v>
+      </c>
+      <c r="D91">
+        <v>30.6928307563735</v>
+      </c>
+      <c r="E91">
+        <v>104.666</v>
+      </c>
+      <c r="F91">
+        <v>141.866</v>
+      </c>
+      <c r="G91">
+        <v>25.3</v>
+      </c>
+      <c r="H91">
+        <v>122.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K91">
+        <v>4.14</v>
+      </c>
+      <c r="L91">
+        <v>5.22</v>
+      </c>
+      <c r="M91">
+        <v>33.8776008</v>
+      </c>
+      <c r="N91">
+        <v>-28.6576008</v>
+      </c>
+      <c r="O91">
+        <v>-7.164400200000001</v>
+      </c>
+      <c r="P91">
+        <v>-21.4932006</v>
+      </c>
+      <c r="Q91">
+        <v>-17.3532006</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4642579228647845</v>
+      </c>
+      <c r="T91">
+        <v>5.761379044496169</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03852102773464406</v>
+      </c>
+      <c r="W91">
+        <v>0.229601178576967</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1540841109385762</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2574134204486269</v>
+      </c>
+      <c r="C92">
+        <v>-87.74796472903986</v>
+      </c>
+      <c r="D92">
+        <v>30.41203527096015</v>
+      </c>
+      <c r="E92">
+        <v>106.26</v>
+      </c>
+      <c r="F92">
+        <v>143.46</v>
+      </c>
+      <c r="G92">
+        <v>25.3</v>
+      </c>
+      <c r="H92">
+        <v>122.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K92">
+        <v>4.14</v>
+      </c>
+      <c r="L92">
+        <v>5.22</v>
+      </c>
+      <c r="M92">
+        <v>34.258248</v>
+      </c>
+      <c r="N92">
+        <v>-29.038248</v>
+      </c>
+      <c r="O92">
+        <v>-7.259562000000001</v>
+      </c>
+      <c r="P92">
+        <v>-21.778686</v>
+      </c>
+      <c r="Q92">
+        <v>-17.638686</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5068037151512631</v>
+      </c>
+      <c r="T92">
+        <v>6.337516948945788</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03809301631537024</v>
+      </c>
+      <c r="W92">
+        <v>0.2297033877038896</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1523720652614809</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.259413420448627</v>
+      </c>
+      <c r="C93">
+        <v>-89.61766903759113</v>
+      </c>
+      <c r="D93">
+        <v>30.13633096240887</v>
+      </c>
+      <c r="E93">
+        <v>107.854</v>
+      </c>
+      <c r="F93">
+        <v>145.054</v>
+      </c>
+      <c r="G93">
+        <v>25.3</v>
+      </c>
+      <c r="H93">
+        <v>122.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K93">
+        <v>4.14</v>
+      </c>
+      <c r="L93">
+        <v>5.22</v>
+      </c>
+      <c r="M93">
+        <v>34.6388952</v>
+      </c>
+      <c r="N93">
+        <v>-29.4188952</v>
+      </c>
+      <c r="O93">
+        <v>-7.3547238</v>
+      </c>
+      <c r="P93">
+        <v>-22.0641714</v>
+      </c>
+      <c r="Q93">
+        <v>-17.9241714</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.558804127945848</v>
+      </c>
+      <c r="T93">
+        <v>7.041685498828653</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03767441174047606</v>
+      </c>
+      <c r="W93">
+        <v>0.2298033504763743</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1506976469619042</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.261413420448627</v>
+      </c>
+      <c r="C94">
+        <v>-91.48241938949425</v>
+      </c>
+      <c r="D94">
+        <v>29.86558061050577</v>
+      </c>
+      <c r="E94">
+        <v>109.448</v>
+      </c>
+      <c r="F94">
+        <v>146.648</v>
+      </c>
+      <c r="G94">
+        <v>25.3</v>
+      </c>
+      <c r="H94">
+        <v>122.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K94">
+        <v>4.14</v>
+      </c>
+      <c r="L94">
+        <v>5.22</v>
+      </c>
+      <c r="M94">
+        <v>35.01954240000001</v>
+      </c>
+      <c r="N94">
+        <v>-29.79954240000001</v>
+      </c>
+      <c r="O94">
+        <v>-7.449885600000002</v>
+      </c>
+      <c r="P94">
+        <v>-22.34965680000001</v>
+      </c>
+      <c r="Q94">
+        <v>-18.2096568</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.623804643939079</v>
+      </c>
+      <c r="T94">
+        <v>7.921896186182237</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0372649072650361</v>
+      </c>
+      <c r="W94">
+        <v>0.2299011401451094</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1490596290601444</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2634134204486269</v>
+      </c>
+      <c r="C95">
+        <v>-93.34234811762505</v>
+      </c>
+      <c r="D95">
+        <v>29.59965188237497</v>
+      </c>
+      <c r="E95">
+        <v>111.042</v>
+      </c>
+      <c r="F95">
+        <v>148.242</v>
+      </c>
+      <c r="G95">
+        <v>25.3</v>
+      </c>
+      <c r="H95">
+        <v>122.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K95">
+        <v>4.14</v>
+      </c>
+      <c r="L95">
+        <v>5.22</v>
+      </c>
+      <c r="M95">
+        <v>35.4001896</v>
+      </c>
+      <c r="N95">
+        <v>-30.18018960000001</v>
+      </c>
+      <c r="O95">
+        <v>-7.545047400000001</v>
+      </c>
+      <c r="P95">
+        <v>-22.6351422</v>
+      </c>
+      <c r="Q95">
+        <v>-18.4951422</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.707376735930376</v>
+      </c>
+      <c r="T95">
+        <v>9.053595641351128</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03686420933745507</v>
+      </c>
+      <c r="W95">
+        <v>0.2299968268102157</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1474568373498203</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2654134204486269</v>
+      </c>
+      <c r="C96">
+        <v>-95.19758288318991</v>
+      </c>
+      <c r="D96">
+        <v>29.33841711681011</v>
+      </c>
+      <c r="E96">
+        <v>112.636</v>
+      </c>
+      <c r="F96">
+        <v>149.836</v>
+      </c>
+      <c r="G96">
+        <v>25.3</v>
+      </c>
+      <c r="H96">
+        <v>122.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K96">
+        <v>4.14</v>
+      </c>
+      <c r="L96">
+        <v>5.22</v>
+      </c>
+      <c r="M96">
+        <v>35.7808368</v>
+      </c>
+      <c r="N96">
+        <v>-30.5608368</v>
+      </c>
+      <c r="O96">
+        <v>-7.640209200000001</v>
+      </c>
+      <c r="P96">
+        <v>-22.9206276</v>
+      </c>
+      <c r="Q96">
+        <v>-18.7806276</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8188061919187721</v>
+      </c>
+      <c r="T96">
+        <v>10.56252824824298</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.03647203689769491</v>
+      </c>
+      <c r="W96">
+        <v>0.2300904775888304</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1458881475907796</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2674134204486269</v>
+      </c>
+      <c r="C97">
+        <v>-97.04824688007369</v>
+      </c>
+      <c r="D97">
+        <v>29.08175311992631</v>
+      </c>
+      <c r="E97">
+        <v>114.23</v>
+      </c>
+      <c r="F97">
+        <v>151.43</v>
+      </c>
+      <c r="G97">
+        <v>25.3</v>
+      </c>
+      <c r="H97">
+        <v>122.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K97">
+        <v>4.14</v>
+      </c>
+      <c r="L97">
+        <v>5.22</v>
+      </c>
+      <c r="M97">
+        <v>36.161484</v>
+      </c>
+      <c r="N97">
+        <v>-30.941484</v>
+      </c>
+      <c r="O97">
+        <v>-7.735371000000001</v>
+      </c>
+      <c r="P97">
+        <v>-23.206113</v>
+      </c>
+      <c r="Q97">
+        <v>-19.066113</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9748074303025271</v>
+      </c>
+      <c r="T97">
+        <v>12.67503389789159</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03608812071982444</v>
+      </c>
+      <c r="W97">
+        <v>0.2301821567721059</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1443524828792977</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2694134204486269</v>
+      </c>
+      <c r="C98">
+        <v>-98.89445902855448</v>
+      </c>
+      <c r="D98">
+        <v>28.82954097144551</v>
+      </c>
+      <c r="E98">
+        <v>115.824</v>
+      </c>
+      <c r="F98">
+        <v>153.024</v>
+      </c>
+      <c r="G98">
+        <v>25.3</v>
+      </c>
+      <c r="H98">
+        <v>122.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K98">
+        <v>4.14</v>
+      </c>
+      <c r="L98">
+        <v>5.22</v>
+      </c>
+      <c r="M98">
+        <v>36.5421312</v>
+      </c>
+      <c r="N98">
+        <v>-31.3221312</v>
+      </c>
+      <c r="O98">
+        <v>-7.8305328</v>
+      </c>
+      <c r="P98">
+        <v>-23.4915984</v>
+      </c>
+      <c r="Q98">
+        <v>-19.3515984</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.208809287878156</v>
+      </c>
+      <c r="T98">
+        <v>15.84379237236445</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.0357122027956596</v>
+      </c>
+      <c r="W98">
+        <v>0.2302719259723965</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1428488111826384</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2714134204486269</v>
+      </c>
+      <c r="C99">
+        <v>-100.736334159025</v>
+      </c>
+      <c r="D99">
+        <v>28.58166584097502</v>
+      </c>
+      <c r="E99">
+        <v>117.418</v>
+      </c>
+      <c r="F99">
+        <v>154.618</v>
+      </c>
+      <c r="G99">
+        <v>25.3</v>
+      </c>
+      <c r="H99">
+        <v>122.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K99">
+        <v>4.14</v>
+      </c>
+      <c r="L99">
+        <v>5.22</v>
+      </c>
+      <c r="M99">
+        <v>36.9227784</v>
+      </c>
+      <c r="N99">
+        <v>-31.7027784</v>
+      </c>
+      <c r="O99">
+        <v>-7.9256946</v>
+      </c>
+      <c r="P99">
+        <v>-23.7770838</v>
+      </c>
+      <c r="Q99">
+        <v>-19.6370838</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.598812383837542</v>
+      </c>
+      <c r="T99">
+        <v>21.12505649648594</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03534403575652909</v>
+      </c>
+      <c r="W99">
+        <v>0.2303598442613408</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1413761430261163</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2734134204486269</v>
+      </c>
+      <c r="C100">
+        <v>-102.5739831863169</v>
+      </c>
+      <c r="D100">
+        <v>28.33801681368305</v>
+      </c>
+      <c r="E100">
+        <v>119.012</v>
+      </c>
+      <c r="F100">
+        <v>156.212</v>
+      </c>
+      <c r="G100">
+        <v>25.3</v>
+      </c>
+      <c r="H100">
+        <v>122.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K100">
+        <v>4.14</v>
+      </c>
+      <c r="L100">
+        <v>5.22</v>
+      </c>
+      <c r="M100">
+        <v>37.3034256</v>
+      </c>
+      <c r="N100">
+        <v>-32.0834256</v>
+      </c>
+      <c r="O100">
+        <v>-8.0208564</v>
+      </c>
+      <c r="P100">
+        <v>-24.0625692</v>
+      </c>
+      <c r="Q100">
+        <v>-19.9225692</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.378818575756313</v>
+      </c>
+      <c r="T100">
+        <v>31.6875847447289</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03498338233044206</v>
+      </c>
+      <c r="W100">
+        <v>0.2304459682994904</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1399335293217682</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2754134204486269</v>
+      </c>
+      <c r="C101">
+        <v>-104.4075132751847</v>
+      </c>
+      <c r="D101">
+        <v>28.09848672481528</v>
+      </c>
+      <c r="E101">
+        <v>120.606</v>
+      </c>
+      <c r="F101">
+        <v>157.806</v>
+      </c>
+      <c r="G101">
+        <v>25.3</v>
+      </c>
+      <c r="H101">
+        <v>122.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K101">
+        <v>4.14</v>
+      </c>
+      <c r="L101">
+        <v>5.22</v>
+      </c>
+      <c r="M101">
+        <v>37.6840728</v>
+      </c>
+      <c r="N101">
+        <v>-32.4640728</v>
+      </c>
+      <c r="O101">
+        <v>-8.116018200000001</v>
+      </c>
+      <c r="P101">
+        <v>-24.3480546</v>
+      </c>
+      <c r="Q101">
+        <v>-20.2080546</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.718837151512626</v>
+      </c>
+      <c r="T101">
+        <v>63.3751694894578</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03463001483215476</v>
+      </c>
+      <c r="W101">
+        <v>0.2305303524580815</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.138520059328619</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/philippines/philippines_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_beverage_soft.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09089934325511963</v>
+        <v>0.09070584489698183</v>
       </c>
       <c r="C2">
-        <v>165.632651696846</v>
+        <v>164.6393589259454</v>
       </c>
       <c r="D2">
-        <v>153.332651696846</v>
+        <v>153.9933589259454</v>
       </c>
       <c r="E2">
-        <v>-27.1</v>
+        <v>-25.446</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.654</v>
       </c>
       <c r="G2">
         <v>12.3</v>
@@ -1439,28 +1439,28 @@
         <v>11.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0831962</v>
       </c>
       <c r="N2">
-        <v>11.6</v>
+        <v>11.5168038</v>
       </c>
       <c r="O2">
-        <v>2.9</v>
+        <v>2.87920095</v>
       </c>
       <c r="P2">
-        <v>8.699999999999999</v>
+        <v>8.63760285</v>
       </c>
       <c r="Q2">
-        <v>5.43</v>
+        <v>5.367602850000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09089934325511963</v>
+        <v>0.0912410049464463</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6612219901513506</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>139.4294450948481</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09070584489698183</v>
+        <v>0.09051234653884403</v>
       </c>
       <c r="C3">
-        <v>164.6393589259454</v>
+        <v>163.651784743933</v>
       </c>
       <c r="D3">
-        <v>153.9933589259454</v>
+        <v>154.659784743933</v>
       </c>
       <c r="E3">
-        <v>-25.446</v>
+        <v>-23.792</v>
       </c>
       <c r="F3">
-        <v>1.654</v>
+        <v>3.308</v>
       </c>
       <c r="G3">
         <v>12.3</v>
@@ -1521,28 +1521,28 @@
         <v>11.6</v>
       </c>
       <c r="M3">
-        <v>0.0831962</v>
+        <v>0.1663924</v>
       </c>
       <c r="N3">
-        <v>11.5168038</v>
+        <v>11.4336076</v>
       </c>
       <c r="O3">
-        <v>2.87920095</v>
+        <v>2.8584019</v>
       </c>
       <c r="P3">
-        <v>8.63760285</v>
+        <v>8.5752057</v>
       </c>
       <c r="Q3">
-        <v>5.367602850000001</v>
+        <v>5.3052057</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0912410049464463</v>
+        <v>0.09158963932535105</v>
       </c>
       <c r="T3">
-        <v>0.6612219901513506</v>
+        <v>0.6662950451624858</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>139.4294450948481</v>
+        <v>69.71472254742405</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09051234653884403</v>
+        <v>0.09031884818070623</v>
       </c>
       <c r="C4">
-        <v>163.651784743933</v>
+        <v>162.6700037172637</v>
       </c>
       <c r="D4">
-        <v>154.659784743933</v>
+        <v>155.3320037172637</v>
       </c>
       <c r="E4">
-        <v>-23.792</v>
+        <v>-22.138</v>
       </c>
       <c r="F4">
-        <v>3.308</v>
+        <v>4.962</v>
       </c>
       <c r="G4">
         <v>12.3</v>
@@ -1603,28 +1603,28 @@
         <v>11.6</v>
       </c>
       <c r="M4">
-        <v>0.1663924</v>
+        <v>0.2495886</v>
       </c>
       <c r="N4">
-        <v>11.4336076</v>
+        <v>11.3504114</v>
       </c>
       <c r="O4">
-        <v>2.8584019</v>
+        <v>2.83760285</v>
       </c>
       <c r="P4">
-        <v>8.5752057</v>
+        <v>8.512808550000001</v>
       </c>
       <c r="Q4">
-        <v>5.3052057</v>
+        <v>5.242808550000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09158963932535105</v>
+        <v>0.09194546204196519</v>
       </c>
       <c r="T4">
-        <v>0.6662950451624858</v>
+        <v>0.6714726992460154</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.71472254742405</v>
+        <v>46.4764816982827</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09031884818070623</v>
+        <v>0.09012534982256842</v>
       </c>
       <c r="C5">
-        <v>162.6700037172637</v>
+        <v>161.694091714445</v>
       </c>
       <c r="D5">
-        <v>155.3320037172637</v>
+        <v>156.010091714445</v>
       </c>
       <c r="E5">
-        <v>-22.138</v>
+        <v>-20.484</v>
       </c>
       <c r="F5">
-        <v>4.962</v>
+        <v>6.616000000000001</v>
       </c>
       <c r="G5">
         <v>12.3</v>
@@ -1685,28 +1685,28 @@
         <v>11.6</v>
       </c>
       <c r="M5">
-        <v>0.2495886</v>
+        <v>0.3327848</v>
       </c>
       <c r="N5">
-        <v>11.3504114</v>
+        <v>11.2672152</v>
       </c>
       <c r="O5">
-        <v>2.83760285</v>
+        <v>2.8168038</v>
       </c>
       <c r="P5">
-        <v>8.512808550000001</v>
+        <v>8.4504114</v>
       </c>
       <c r="Q5">
-        <v>5.242808550000001</v>
+        <v>5.180411400000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09194546204196519</v>
+        <v>0.09230869773184211</v>
       </c>
       <c r="T5">
-        <v>0.6714726992460154</v>
+        <v>0.6767582211229519</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.4764816982827</v>
+        <v>34.85736127371202</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09012534982256842</v>
+        <v>0.08993185146443063</v>
       </c>
       <c r="C6">
-        <v>161.694091714445</v>
+        <v>160.724125934582</v>
       </c>
       <c r="D6">
-        <v>156.010091714445</v>
+        <v>156.694125934582</v>
       </c>
       <c r="E6">
-        <v>-20.484</v>
+        <v>-18.83</v>
       </c>
       <c r="F6">
-        <v>6.616000000000001</v>
+        <v>8.270000000000001</v>
       </c>
       <c r="G6">
         <v>12.3</v>
@@ -1767,28 +1767,28 @@
         <v>11.6</v>
       </c>
       <c r="M6">
-        <v>0.3327848</v>
+        <v>0.415981</v>
       </c>
       <c r="N6">
-        <v>11.2672152</v>
+        <v>11.184019</v>
       </c>
       <c r="O6">
-        <v>2.8168038</v>
+        <v>2.79600475</v>
       </c>
       <c r="P6">
-        <v>8.4504114</v>
+        <v>8.388014249999999</v>
       </c>
       <c r="Q6">
-        <v>5.180411400000001</v>
+        <v>5.11801425</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09230869773184211</v>
+        <v>0.09267958048887434</v>
       </c>
       <c r="T6">
-        <v>0.6767582211229519</v>
+        <v>0.6821550171446661</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.85736127371202</v>
+        <v>27.88588901896961</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08993185146443063</v>
+        <v>0.08973835310629283</v>
       </c>
       <c r="C7">
-        <v>160.724125934582</v>
+        <v>159.7601849366759</v>
       </c>
       <c r="D7">
-        <v>156.694125934582</v>
+        <v>157.3841849366759</v>
       </c>
       <c r="E7">
-        <v>-18.83</v>
+        <v>-17.176</v>
       </c>
       <c r="F7">
-        <v>8.270000000000001</v>
+        <v>9.924000000000001</v>
       </c>
       <c r="G7">
         <v>12.3</v>
@@ -1849,28 +1849,28 @@
         <v>11.6</v>
       </c>
       <c r="M7">
-        <v>0.415981</v>
+        <v>0.4991772</v>
       </c>
       <c r="N7">
-        <v>11.184019</v>
+        <v>11.1008228</v>
       </c>
       <c r="O7">
-        <v>2.79600475</v>
+        <v>2.7752057</v>
       </c>
       <c r="P7">
-        <v>8.388014249999999</v>
+        <v>8.325617099999999</v>
       </c>
       <c r="Q7">
-        <v>5.11801425</v>
+        <v>5.055617099999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09267958048887434</v>
+        <v>0.09305835436839663</v>
       </c>
       <c r="T7">
-        <v>0.6821550171446661</v>
+        <v>0.6876666386136507</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.88588901896961</v>
+        <v>23.23824084914135</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08973835310629283</v>
+        <v>0.08954485474815503</v>
       </c>
       <c r="C8">
-        <v>159.7601849366759</v>
+        <v>158.8023486697006</v>
       </c>
       <c r="D8">
-        <v>157.3841849366759</v>
+        <v>158.0803486697006</v>
       </c>
       <c r="E8">
-        <v>-17.176</v>
+        <v>-15.522</v>
       </c>
       <c r="F8">
-        <v>9.923999999999999</v>
+        <v>11.578</v>
       </c>
       <c r="G8">
         <v>12.3</v>
@@ -1931,28 +1931,28 @@
         <v>11.6</v>
       </c>
       <c r="M8">
-        <v>0.4991771999999999</v>
+        <v>0.5823733999999999</v>
       </c>
       <c r="N8">
-        <v>11.1008228</v>
+        <v>11.0176266</v>
       </c>
       <c r="O8">
-        <v>2.7752057</v>
+        <v>2.75440665</v>
       </c>
       <c r="P8">
-        <v>8.325617099999999</v>
+        <v>8.26321995</v>
       </c>
       <c r="Q8">
-        <v>5.055617099999999</v>
+        <v>4.99321995</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09305835436839663</v>
+        <v>0.09344527392274735</v>
       </c>
       <c r="T8">
-        <v>0.6876666386136507</v>
+        <v>0.693296789576592</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.23824084914135</v>
+        <v>19.91849215640687</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08954485474815502</v>
+        <v>0.08935135639001726</v>
       </c>
       <c r="C9">
-        <v>158.8023486697007</v>
+        <v>157.8506985034809</v>
       </c>
       <c r="D9">
-        <v>158.0803486697007</v>
+        <v>158.7826985034809</v>
       </c>
       <c r="E9">
-        <v>-15.522</v>
+        <v>-13.868</v>
       </c>
       <c r="F9">
-        <v>11.578</v>
+        <v>13.232</v>
       </c>
       <c r="G9">
         <v>12.3</v>
@@ -2013,28 +2013,28 @@
         <v>11.6</v>
       </c>
       <c r="M9">
-        <v>0.5823734</v>
+        <v>0.6655696</v>
       </c>
       <c r="N9">
-        <v>11.0176266</v>
+        <v>10.9344304</v>
       </c>
       <c r="O9">
-        <v>2.75440665</v>
+        <v>2.7336076</v>
       </c>
       <c r="P9">
-        <v>8.26321995</v>
+        <v>8.200822800000001</v>
       </c>
       <c r="Q9">
-        <v>4.99321995</v>
+        <v>4.930822800000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09344527392274735</v>
+        <v>0.09384060477175787</v>
       </c>
       <c r="T9">
-        <v>0.693296789576592</v>
+        <v>0.6990493351256842</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.91849215640687</v>
+        <v>17.42868063685601</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08935135639001726</v>
+        <v>0.08915785803187945</v>
       </c>
       <c r="C10">
-        <v>157.8506985034809</v>
+        <v>156.9053172603975</v>
       </c>
       <c r="D10">
-        <v>158.7826985034809</v>
+        <v>159.4913172603975</v>
       </c>
       <c r="E10">
-        <v>-13.868</v>
+        <v>-12.214</v>
       </c>
       <c r="F10">
-        <v>13.232</v>
+        <v>14.886</v>
       </c>
       <c r="G10">
         <v>12.3</v>
@@ -2095,28 +2095,28 @@
         <v>11.6</v>
       </c>
       <c r="M10">
-        <v>0.6655696</v>
+        <v>0.7487657999999999</v>
       </c>
       <c r="N10">
-        <v>10.9344304</v>
+        <v>10.8512342</v>
       </c>
       <c r="O10">
-        <v>2.7336076</v>
+        <v>2.71280855</v>
       </c>
       <c r="P10">
-        <v>8.200822800000001</v>
+        <v>8.13842565</v>
       </c>
       <c r="Q10">
-        <v>4.930822800000001</v>
+        <v>4.868425650000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09384060477175787</v>
+        <v>0.09424462421085653</v>
       </c>
       <c r="T10">
-        <v>0.6990493351256842</v>
+        <v>0.7049283102472839</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.42868063685601</v>
+        <v>15.49216056609423</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08915785803187945</v>
+        <v>0.08896435967374162</v>
       </c>
       <c r="C11">
-        <v>156.9053172603975</v>
+        <v>155.9662892479444</v>
       </c>
       <c r="D11">
-        <v>159.4913172603975</v>
+        <v>160.2062892479444</v>
       </c>
       <c r="E11">
-        <v>-12.214</v>
+        <v>-10.56</v>
       </c>
       <c r="F11">
-        <v>14.886</v>
+        <v>16.54</v>
       </c>
       <c r="G11">
         <v>12.3</v>
@@ -2177,28 +2177,28 @@
         <v>11.6</v>
       </c>
       <c r="M11">
-        <v>0.7487657999999999</v>
+        <v>0.8319619999999999</v>
       </c>
       <c r="N11">
-        <v>10.8512342</v>
+        <v>10.768038</v>
       </c>
       <c r="O11">
-        <v>2.71280855</v>
+        <v>2.6920095</v>
       </c>
       <c r="P11">
-        <v>8.13842565</v>
+        <v>8.0760285</v>
       </c>
       <c r="Q11">
-        <v>4.868425650000001</v>
+        <v>4.8060285</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09424462421085653</v>
+        <v>0.09465762185971292</v>
       </c>
       <c r="T11">
-        <v>0.7049283102472839</v>
+        <v>0.7109379292604747</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.49216056609423</v>
+        <v>13.94294450948481</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08896435967374162</v>
+        <v>0.08889461131560385</v>
       </c>
       <c r="C12">
-        <v>155.9662892479444</v>
+        <v>154.5715821223262</v>
       </c>
       <c r="D12">
-        <v>160.2062892479444</v>
+        <v>160.4655821223262</v>
       </c>
       <c r="E12">
-        <v>-10.56</v>
+        <v>-8.906000000000002</v>
       </c>
       <c r="F12">
-        <v>16.54</v>
+        <v>18.194</v>
       </c>
       <c r="G12">
         <v>12.3</v>
@@ -2259,45 +2259,45 @@
         <v>11.6</v>
       </c>
       <c r="M12">
-        <v>0.8319620000000001</v>
+        <v>0.9424491999999999</v>
       </c>
       <c r="N12">
-        <v>10.768038</v>
+        <v>10.6575508</v>
       </c>
       <c r="O12">
-        <v>2.6920095</v>
+        <v>2.6643877</v>
       </c>
       <c r="P12">
-        <v>8.0760285</v>
+        <v>7.993163099999999</v>
       </c>
       <c r="Q12">
-        <v>4.8060285</v>
+        <v>4.7231631</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09465762185971292</v>
+        <v>0.09507990035461106</v>
       </c>
       <c r="T12">
-        <v>0.7109379292604747</v>
+        <v>0.7170825958919396</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.94294450948481</v>
+        <v>12.30835571827108</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08889461131560385</v>
+        <v>0.08871236295746604</v>
       </c>
       <c r="C13">
-        <v>154.5715821223262</v>
+        <v>153.5990777768164</v>
       </c>
       <c r="D13">
-        <v>160.4655821223262</v>
+        <v>161.1470777768164</v>
       </c>
       <c r="E13">
-        <v>-8.906000000000002</v>
+        <v>-7.252000000000002</v>
       </c>
       <c r="F13">
-        <v>18.194</v>
+        <v>19.848</v>
       </c>
       <c r="G13">
         <v>12.3</v>
@@ -2341,28 +2341,28 @@
         <v>11.6</v>
       </c>
       <c r="M13">
-        <v>0.9424491999999999</v>
+        <v>1.0281264</v>
       </c>
       <c r="N13">
-        <v>10.6575508</v>
+        <v>10.5718736</v>
       </c>
       <c r="O13">
-        <v>2.6643877</v>
+        <v>2.6429684</v>
       </c>
       <c r="P13">
-        <v>7.993163099999999</v>
+        <v>7.9289052</v>
       </c>
       <c r="Q13">
-        <v>4.7231631</v>
+        <v>4.6589052</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09507990035461106</v>
+        <v>0.09551177608802959</v>
       </c>
       <c r="T13">
-        <v>0.7170825958919396</v>
+        <v>0.7233669140377558</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.30835571827108</v>
+        <v>11.28265940841515</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08871236295746604</v>
+        <v>0.08853011459932823</v>
       </c>
       <c r="C14">
-        <v>153.5990777768164</v>
+        <v>152.6323867302072</v>
       </c>
       <c r="D14">
-        <v>161.1470777768164</v>
+        <v>161.8343867302072</v>
       </c>
       <c r="E14">
-        <v>-7.252000000000002</v>
+        <v>-5.597999999999999</v>
       </c>
       <c r="F14">
-        <v>19.848</v>
+        <v>21.502</v>
       </c>
       <c r="G14">
         <v>12.3</v>
@@ -2423,28 +2423,28 @@
         <v>11.6</v>
       </c>
       <c r="M14">
-        <v>1.0281264</v>
+        <v>1.1138036</v>
       </c>
       <c r="N14">
-        <v>10.5718736</v>
+        <v>10.4861964</v>
       </c>
       <c r="O14">
-        <v>2.6429684</v>
+        <v>2.6215491</v>
       </c>
       <c r="P14">
-        <v>7.9289052</v>
+        <v>7.8646473</v>
       </c>
       <c r="Q14">
-        <v>4.6589052</v>
+        <v>4.5946473</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09551177608802959</v>
+        <v>0.09595357999922785</v>
       </c>
       <c r="T14">
-        <v>0.7233669140377558</v>
+        <v>0.7297956992673839</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.28265940841515</v>
+        <v>10.41476253084475</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08853011459932823</v>
+        <v>0.08852636624119044</v>
       </c>
       <c r="C15">
-        <v>152.6323867302072</v>
+        <v>150.992584362579</v>
       </c>
       <c r="D15">
-        <v>161.8343867302072</v>
+        <v>161.848584362579</v>
       </c>
       <c r="E15">
-        <v>-5.597999999999999</v>
+        <v>-3.943999999999999</v>
       </c>
       <c r="F15">
-        <v>21.502</v>
+        <v>23.156</v>
       </c>
       <c r="G15">
         <v>12.3</v>
@@ -2505,45 +2505,45 @@
         <v>11.6</v>
       </c>
       <c r="M15">
-        <v>1.1138036</v>
+        <v>1.238846</v>
       </c>
       <c r="N15">
-        <v>10.4861964</v>
+        <v>10.361154</v>
       </c>
       <c r="O15">
-        <v>2.6215491</v>
+        <v>2.5902885</v>
       </c>
       <c r="P15">
-        <v>7.8646473</v>
+        <v>7.770865499999999</v>
       </c>
       <c r="Q15">
-        <v>4.5946473</v>
+        <v>4.5008655</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09595357999922785</v>
+        <v>0.09640565841998888</v>
       </c>
       <c r="T15">
-        <v>0.7297956992673839</v>
+        <v>0.7363739911302591</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.41476253084475</v>
+        <v>9.363552854834255</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08852636624119044</v>
+        <v>0.08835686788305264</v>
       </c>
       <c r="C16">
-        <v>150.992584362579</v>
+        <v>149.9832057992827</v>
       </c>
       <c r="D16">
-        <v>161.848584362579</v>
+        <v>162.4932057992827</v>
       </c>
       <c r="E16">
-        <v>-3.943999999999999</v>
+        <v>-2.289999999999996</v>
       </c>
       <c r="F16">
-        <v>23.156</v>
+        <v>24.81000000000001</v>
       </c>
       <c r="G16">
         <v>12.3</v>
@@ -2587,28 +2587,28 @@
         <v>11.6</v>
       </c>
       <c r="M16">
-        <v>1.238846</v>
+        <v>1.327335</v>
       </c>
       <c r="N16">
-        <v>10.361154</v>
+        <v>10.272665</v>
       </c>
       <c r="O16">
-        <v>2.5902885</v>
+        <v>2.56816625</v>
       </c>
       <c r="P16">
-        <v>7.770865499999999</v>
+        <v>7.70449875</v>
       </c>
       <c r="Q16">
-        <v>4.5008655</v>
+        <v>4.43449875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09640565841998888</v>
+        <v>0.09686837398006193</v>
       </c>
       <c r="T16">
-        <v>0.7363739911302591</v>
+        <v>0.7431070663310845</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.363552854834255</v>
+        <v>8.739315997845305</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08835686788305264</v>
+        <v>0.08818736952491484</v>
       </c>
       <c r="C17">
-        <v>149.9832057992827</v>
+        <v>148.978982652629</v>
       </c>
       <c r="D17">
-        <v>162.4932057992827</v>
+        <v>163.142982652629</v>
       </c>
       <c r="E17">
-        <v>-2.290000000000003</v>
+        <v>-0.6359999999999992</v>
       </c>
       <c r="F17">
-        <v>24.81</v>
+        <v>26.464</v>
       </c>
       <c r="G17">
         <v>12.3</v>
@@ -2669,28 +2669,28 @@
         <v>11.6</v>
       </c>
       <c r="M17">
-        <v>1.327335</v>
+        <v>1.415824</v>
       </c>
       <c r="N17">
-        <v>10.272665</v>
+        <v>10.184176</v>
       </c>
       <c r="O17">
-        <v>2.56816625</v>
+        <v>2.546044</v>
       </c>
       <c r="P17">
-        <v>7.70449875</v>
+        <v>7.638131999999999</v>
       </c>
       <c r="Q17">
-        <v>4.43449875</v>
+        <v>4.368131999999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09686837398006193</v>
+        <v>0.09734210657727957</v>
       </c>
       <c r="T17">
-        <v>0.7431070663310845</v>
+        <v>0.7500004528462151</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.739315997845306</v>
+        <v>8.193108747979974</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08818736952491484</v>
+        <v>0.08801787116677705</v>
       </c>
       <c r="C18">
-        <v>148.978982652629</v>
+        <v>147.9799770172687</v>
       </c>
       <c r="D18">
-        <v>163.142982652629</v>
+        <v>163.7979770172687</v>
       </c>
       <c r="E18">
-        <v>-0.6359999999999992</v>
+        <v>1.018000000000001</v>
       </c>
       <c r="F18">
-        <v>26.464</v>
+        <v>28.118</v>
       </c>
       <c r="G18">
         <v>12.3</v>
@@ -2751,28 +2751,28 @@
         <v>11.6</v>
       </c>
       <c r="M18">
-        <v>1.415824</v>
+        <v>1.504313</v>
       </c>
       <c r="N18">
-        <v>10.184176</v>
+        <v>10.095687</v>
       </c>
       <c r="O18">
-        <v>2.546044</v>
+        <v>2.52392175</v>
       </c>
       <c r="P18">
-        <v>7.638131999999999</v>
+        <v>7.57176525</v>
       </c>
       <c r="Q18">
-        <v>4.368131999999999</v>
+        <v>4.301765250000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09734210657727957</v>
+        <v>0.09782725441780368</v>
       </c>
       <c r="T18">
-        <v>0.7500004528462151</v>
+        <v>0.7570599450605057</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.193108747979974</v>
+        <v>7.711161174569388</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08801787116677705</v>
+        <v>0.08795637280863924</v>
       </c>
       <c r="C19">
-        <v>147.9799770172687</v>
+        <v>146.5649279986205</v>
       </c>
       <c r="D19">
-        <v>163.7979770172687</v>
+        <v>164.0369279986205</v>
       </c>
       <c r="E19">
-        <v>1.018000000000001</v>
+        <v>2.672000000000004</v>
       </c>
       <c r="F19">
-        <v>28.118</v>
+        <v>29.77200000000001</v>
       </c>
       <c r="G19">
         <v>12.3</v>
@@ -2833,45 +2833,45 @@
         <v>11.6</v>
       </c>
       <c r="M19">
-        <v>1.504313</v>
+        <v>1.6166196</v>
       </c>
       <c r="N19">
-        <v>10.095687</v>
+        <v>9.9833804</v>
       </c>
       <c r="O19">
-        <v>2.52392175</v>
+        <v>2.4958451</v>
       </c>
       <c r="P19">
-        <v>7.57176525</v>
+        <v>7.487535299999999</v>
       </c>
       <c r="Q19">
-        <v>4.301765250000001</v>
+        <v>4.2175353</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09782725441780368</v>
+        <v>0.09832423513248688</v>
       </c>
       <c r="T19">
-        <v>0.7570599450605057</v>
+        <v>0.7642916200117299</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.711161174569388</v>
+        <v>7.175466634203865</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08795637280863924</v>
+        <v>0.08779287445050146</v>
       </c>
       <c r="C20">
-        <v>146.5649279986205</v>
+        <v>145.5496022678314</v>
       </c>
       <c r="D20">
-        <v>164.0369279986205</v>
+        <v>164.6756022678314</v>
       </c>
       <c r="E20">
-        <v>2.671999999999997</v>
+        <v>4.326000000000001</v>
       </c>
       <c r="F20">
-        <v>29.772</v>
+        <v>31.426</v>
       </c>
       <c r="G20">
         <v>12.3</v>
@@ -2915,28 +2915,28 @@
         <v>11.6</v>
       </c>
       <c r="M20">
-        <v>1.6166196</v>
+        <v>1.7064318</v>
       </c>
       <c r="N20">
-        <v>9.9833804</v>
+        <v>9.893568199999999</v>
       </c>
       <c r="O20">
-        <v>2.4958451</v>
+        <v>2.47339205</v>
       </c>
       <c r="P20">
-        <v>7.487535299999999</v>
+        <v>7.42017615</v>
       </c>
       <c r="Q20">
-        <v>4.2175353</v>
+        <v>4.15017615</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09832423513248688</v>
+        <v>0.09883348697592773</v>
       </c>
       <c r="T20">
-        <v>0.7642916200117299</v>
+        <v>0.7717018548382932</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.175466634203866</v>
+        <v>6.797810495561556</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08779287445050146</v>
+        <v>0.08762937609236365</v>
       </c>
       <c r="C21">
-        <v>145.5496022678314</v>
+        <v>144.539269305482</v>
       </c>
       <c r="D21">
-        <v>164.6756022678314</v>
+        <v>165.319269305482</v>
       </c>
       <c r="E21">
-        <v>4.326000000000001</v>
+        <v>5.980000000000004</v>
       </c>
       <c r="F21">
-        <v>31.426</v>
+        <v>33.08000000000001</v>
       </c>
       <c r="G21">
         <v>12.3</v>
@@ -2997,28 +2997,28 @@
         <v>11.6</v>
       </c>
       <c r="M21">
-        <v>1.7064318</v>
+        <v>1.796244</v>
       </c>
       <c r="N21">
-        <v>9.893568199999999</v>
+        <v>9.803756</v>
       </c>
       <c r="O21">
-        <v>2.47339205</v>
+        <v>2.450939</v>
       </c>
       <c r="P21">
-        <v>7.42017615</v>
+        <v>7.352817</v>
       </c>
       <c r="Q21">
-        <v>4.15017615</v>
+        <v>4.082817</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09883348697592773</v>
+        <v>0.09935547011545456</v>
       </c>
       <c r="T21">
-        <v>0.7717018548382932</v>
+        <v>0.7792973455355204</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.797810495561556</v>
+        <v>6.457919970783478</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08762937609236365</v>
+        <v>0.08746587773422584</v>
       </c>
       <c r="C22">
-        <v>144.539269305482</v>
+        <v>143.533987886965</v>
       </c>
       <c r="D22">
-        <v>165.319269305482</v>
+        <v>165.9679878869649</v>
       </c>
       <c r="E22">
-        <v>5.980000000000004</v>
+        <v>7.634</v>
       </c>
       <c r="F22">
-        <v>33.08000000000001</v>
+        <v>34.734</v>
       </c>
       <c r="G22">
         <v>12.3</v>
@@ -3079,28 +3079,28 @@
         <v>11.6</v>
       </c>
       <c r="M22">
-        <v>1.796244</v>
+        <v>1.8860562</v>
       </c>
       <c r="N22">
-        <v>9.803756</v>
+        <v>9.713943799999999</v>
       </c>
       <c r="O22">
-        <v>2.450939</v>
+        <v>2.42848595</v>
       </c>
       <c r="P22">
-        <v>7.352817</v>
+        <v>7.285457849999999</v>
       </c>
       <c r="Q22">
-        <v>4.082817</v>
+        <v>4.01545785</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09935547011545456</v>
+        <v>0.09989066801800739</v>
       </c>
       <c r="T22">
-        <v>0.7792973455355204</v>
+        <v>0.7870851271364749</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.457919970783478</v>
+        <v>6.150399972174742</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08746587773422584</v>
+        <v>0.08746737937608803</v>
       </c>
       <c r="C23">
-        <v>143.533987886965</v>
+        <v>141.8740066017936</v>
       </c>
       <c r="D23">
-        <v>165.9679878869649</v>
+        <v>165.9620066017935</v>
       </c>
       <c r="E23">
-        <v>7.634</v>
+        <v>9.287999999999997</v>
       </c>
       <c r="F23">
-        <v>34.734</v>
+        <v>36.388</v>
       </c>
       <c r="G23">
         <v>12.3</v>
@@ -3161,45 +3161,45 @@
         <v>11.6</v>
       </c>
       <c r="M23">
-        <v>1.8860562</v>
+        <v>2.0122564</v>
       </c>
       <c r="N23">
-        <v>9.713943799999999</v>
+        <v>9.5877436</v>
       </c>
       <c r="O23">
-        <v>2.42848595</v>
+        <v>2.3969359</v>
       </c>
       <c r="P23">
-        <v>7.285457849999999</v>
+        <v>7.1908077</v>
       </c>
       <c r="Q23">
-        <v>4.01545785</v>
+        <v>3.9208077</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09989066801800739</v>
+        <v>0.1004395889437026</v>
       </c>
       <c r="T23">
-        <v>0.7870851271364749</v>
+        <v>0.7950725954451463</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.150399972174742</v>
+        <v>5.764672931342148</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08746737937608803</v>
+        <v>0.08731138101795025</v>
       </c>
       <c r="C24">
-        <v>141.8740066017936</v>
+        <v>140.8436861785327</v>
       </c>
       <c r="D24">
-        <v>165.9620066017935</v>
+        <v>166.5856861785327</v>
       </c>
       <c r="E24">
-        <v>9.287999999999997</v>
+        <v>10.942</v>
       </c>
       <c r="F24">
-        <v>36.388</v>
+        <v>38.042</v>
       </c>
       <c r="G24">
         <v>12.3</v>
@@ -3243,28 +3243,28 @@
         <v>11.6</v>
       </c>
       <c r="M24">
-        <v>2.0122564</v>
+        <v>2.1037226</v>
       </c>
       <c r="N24">
-        <v>9.5877436</v>
+        <v>9.4962774</v>
       </c>
       <c r="O24">
-        <v>2.3969359</v>
+        <v>2.37406935</v>
       </c>
       <c r="P24">
-        <v>7.1908077</v>
+        <v>7.12220805</v>
       </c>
       <c r="Q24">
-        <v>3.9208077</v>
+        <v>3.852208050000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1004395889437026</v>
+        <v>0.1010027675557795</v>
       </c>
       <c r="T24">
-        <v>0.7950725954451463</v>
+        <v>0.8032675304631338</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.764672931342148</v>
+        <v>5.514034977805534</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08731138101795025</v>
+        <v>0.08715538265981244</v>
       </c>
       <c r="C25">
-        <v>140.8436861785327</v>
+        <v>139.8180709705893</v>
       </c>
       <c r="D25">
-        <v>166.5856861785327</v>
+        <v>167.2140709705893</v>
       </c>
       <c r="E25">
-        <v>10.942</v>
+        <v>12.596</v>
       </c>
       <c r="F25">
-        <v>38.042</v>
+        <v>39.69600000000001</v>
       </c>
       <c r="G25">
         <v>12.3</v>
@@ -3325,28 +3325,28 @@
         <v>11.6</v>
       </c>
       <c r="M25">
-        <v>2.1037226</v>
+        <v>2.1951888</v>
       </c>
       <c r="N25">
-        <v>9.4962774</v>
+        <v>9.404811199999999</v>
       </c>
       <c r="O25">
-        <v>2.37406935</v>
+        <v>2.3512028</v>
       </c>
       <c r="P25">
-        <v>7.12220805</v>
+        <v>7.0536084</v>
       </c>
       <c r="Q25">
-        <v>3.852208050000001</v>
+        <v>3.7836084</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1010027675557795</v>
+        <v>0.101580766657648</v>
       </c>
       <c r="T25">
-        <v>0.8032675304631338</v>
+        <v>0.8116781216658052</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.514034977805534</v>
+        <v>5.284283520396968</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08715538265981244</v>
+        <v>0.08699938430167464</v>
       </c>
       <c r="C26">
-        <v>139.8180709705893</v>
+        <v>138.7972144257912</v>
       </c>
       <c r="D26">
-        <v>167.2140709705893</v>
+        <v>167.8472144257912</v>
       </c>
       <c r="E26">
-        <v>12.596</v>
+        <v>14.25</v>
       </c>
       <c r="F26">
-        <v>39.696</v>
+        <v>41.35</v>
       </c>
       <c r="G26">
         <v>12.3</v>
@@ -3407,28 +3407,28 @@
         <v>11.6</v>
       </c>
       <c r="M26">
-        <v>2.1951888</v>
+        <v>2.286655</v>
       </c>
       <c r="N26">
-        <v>9.404811199999999</v>
+        <v>9.313345</v>
       </c>
       <c r="O26">
-        <v>2.3512028</v>
+        <v>2.32833625</v>
       </c>
       <c r="P26">
-        <v>7.0536084</v>
+        <v>6.98500875</v>
       </c>
       <c r="Q26">
-        <v>3.7836084</v>
+        <v>3.715008750000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.101580766657648</v>
+        <v>0.1021741790688995</v>
       </c>
       <c r="T26">
-        <v>0.8116781216658052</v>
+        <v>0.8203129953005478</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.284283520396969</v>
+        <v>5.072912179581091</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08699938430167464</v>
+        <v>0.08684338594353685</v>
       </c>
       <c r="C27">
-        <v>138.7972144257912</v>
+        <v>137.7811708045472</v>
       </c>
       <c r="D27">
-        <v>167.8472144257912</v>
+        <v>168.4851708045472</v>
       </c>
       <c r="E27">
-        <v>14.25</v>
+        <v>15.904</v>
       </c>
       <c r="F27">
-        <v>41.35</v>
+        <v>43.004</v>
       </c>
       <c r="G27">
         <v>12.3</v>
@@ -3489,28 +3489,28 @@
         <v>11.6</v>
       </c>
       <c r="M27">
-        <v>2.286655</v>
+        <v>2.3781212</v>
       </c>
       <c r="N27">
-        <v>9.313345</v>
+        <v>9.221878799999999</v>
       </c>
       <c r="O27">
-        <v>2.32833625</v>
+        <v>2.3054697</v>
       </c>
       <c r="P27">
-        <v>6.98500875</v>
+        <v>6.916409099999999</v>
       </c>
       <c r="Q27">
-        <v>3.715008750000001</v>
+        <v>3.6464091</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1021741790688995</v>
+        <v>0.1027836296534282</v>
       </c>
       <c r="T27">
-        <v>0.8203129953005478</v>
+        <v>0.8291812438983917</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.072912179581091</v>
+        <v>4.877800172674125</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08684338594353685</v>
+        <v>0.08668738758539904</v>
       </c>
       <c r="C28">
-        <v>137.7811708045472</v>
+        <v>136.7699951953494</v>
       </c>
       <c r="D28">
-        <v>168.4851708045472</v>
+        <v>169.1279951953494</v>
       </c>
       <c r="E28">
-        <v>15.904</v>
+        <v>17.558</v>
       </c>
       <c r="F28">
-        <v>43.004</v>
+        <v>44.658</v>
       </c>
       <c r="G28">
         <v>12.3</v>
@@ -3571,28 +3571,28 @@
         <v>11.6</v>
       </c>
       <c r="M28">
-        <v>2.3781212</v>
+        <v>2.4695874</v>
       </c>
       <c r="N28">
-        <v>9.221878799999999</v>
+        <v>9.1304126</v>
       </c>
       <c r="O28">
-        <v>2.3054697</v>
+        <v>2.28260315</v>
       </c>
       <c r="P28">
-        <v>6.916409099999999</v>
+        <v>6.84780945</v>
       </c>
       <c r="Q28">
-        <v>3.6464091</v>
+        <v>3.57780945</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1027836296534282</v>
+        <v>0.1034097775142453</v>
       </c>
       <c r="T28">
-        <v>0.8291812438983917</v>
+        <v>0.8382924582112448</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.877800172674125</v>
+        <v>4.697140907019529</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08668738758539904</v>
+        <v>0.08653138922726125</v>
       </c>
       <c r="C29">
-        <v>136.7699951953494</v>
+        <v>135.7637435306297</v>
       </c>
       <c r="D29">
-        <v>169.1279951953494</v>
+        <v>169.7757435306297</v>
       </c>
       <c r="E29">
-        <v>17.558</v>
+        <v>19.212</v>
       </c>
       <c r="F29">
-        <v>44.658</v>
+        <v>46.312</v>
       </c>
       <c r="G29">
         <v>12.3</v>
@@ -3653,28 +3653,28 @@
         <v>11.6</v>
       </c>
       <c r="M29">
-        <v>2.4695874</v>
+        <v>2.5610536</v>
       </c>
       <c r="N29">
-        <v>9.1304126</v>
+        <v>9.0389464</v>
       </c>
       <c r="O29">
-        <v>2.28260315</v>
+        <v>2.2597366</v>
       </c>
       <c r="P29">
-        <v>6.84780945</v>
+        <v>6.7792098</v>
       </c>
       <c r="Q29">
-        <v>3.57780945</v>
+        <v>3.509209800000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1034097775142453</v>
+        <v>0.1040533183711962</v>
       </c>
       <c r="T29">
-        <v>0.8382924582112448</v>
+        <v>0.8476567618105662</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.697140907019529</v>
+        <v>4.529385874625975</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08653138922726125</v>
+        <v>0.08691914086912345</v>
       </c>
       <c r="C30">
-        <v>135.7637435306297</v>
+        <v>132.5087659345289</v>
       </c>
       <c r="D30">
-        <v>169.7757435306297</v>
+        <v>168.1747659345289</v>
       </c>
       <c r="E30">
-        <v>19.212</v>
+        <v>20.86600000000001</v>
       </c>
       <c r="F30">
-        <v>46.312</v>
+        <v>47.96600000000001</v>
       </c>
       <c r="G30">
         <v>12.3</v>
@@ -3735,45 +3735,45 @@
         <v>11.6</v>
       </c>
       <c r="M30">
-        <v>2.5610536</v>
+        <v>2.772434800000001</v>
       </c>
       <c r="N30">
-        <v>9.0389464</v>
+        <v>8.827565199999999</v>
       </c>
       <c r="O30">
-        <v>2.2597366</v>
+        <v>2.2068913</v>
       </c>
       <c r="P30">
-        <v>6.7792098</v>
+        <v>6.620673899999999</v>
       </c>
       <c r="Q30">
-        <v>3.509209800000001</v>
+        <v>3.350673899999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1040533183711962</v>
+        <v>0.1047149871396105</v>
       </c>
       <c r="T30">
-        <v>0.8476567618105662</v>
+        <v>0.8572848486098682</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.529385874625975</v>
+        <v>4.184047898980346</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08691914086912345</v>
+        <v>0.08678189251098566</v>
       </c>
       <c r="C31">
-        <v>132.5087659345289</v>
+        <v>131.41798322613</v>
       </c>
       <c r="D31">
-        <v>168.1747659345289</v>
+        <v>168.73798322613</v>
       </c>
       <c r="E31">
-        <v>20.866</v>
+        <v>22.52</v>
       </c>
       <c r="F31">
-        <v>47.966</v>
+        <v>49.62</v>
       </c>
       <c r="G31">
         <v>12.3</v>
@@ -3817,28 +3817,28 @@
         <v>11.6</v>
       </c>
       <c r="M31">
-        <v>2.7724348</v>
+        <v>2.868036</v>
       </c>
       <c r="N31">
-        <v>8.827565199999999</v>
+        <v>8.731964</v>
       </c>
       <c r="O31">
-        <v>2.2068913</v>
+        <v>2.182991</v>
       </c>
       <c r="P31">
-        <v>6.620673899999999</v>
+        <v>6.548973</v>
       </c>
       <c r="Q31">
-        <v>3.350673899999999</v>
+        <v>3.278973000000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1047149871396105</v>
+        <v>0.1053955607299795</v>
       </c>
       <c r="T31">
-        <v>0.8572848486098682</v>
+        <v>0.8671880236034363</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.184047898980348</v>
+        <v>4.044579635681003</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08678189251098566</v>
+        <v>0.08745839415284784</v>
       </c>
       <c r="C32">
-        <v>131.41798322613</v>
+        <v>127.0238026450408</v>
       </c>
       <c r="D32">
-        <v>168.73798322613</v>
+        <v>165.9978026450408</v>
       </c>
       <c r="E32">
-        <v>22.52</v>
+        <v>24.174</v>
       </c>
       <c r="F32">
-        <v>49.62</v>
+        <v>51.274</v>
       </c>
       <c r="G32">
         <v>12.3</v>
@@ -3899,45 +3899,45 @@
         <v>11.6</v>
       </c>
       <c r="M32">
-        <v>2.868036</v>
+        <v>3.1430962</v>
       </c>
       <c r="N32">
-        <v>8.731964</v>
+        <v>8.456903799999999</v>
       </c>
       <c r="O32">
-        <v>2.182991</v>
+        <v>2.11422595</v>
       </c>
       <c r="P32">
-        <v>6.548973</v>
+        <v>6.342677849999999</v>
       </c>
       <c r="Q32">
-        <v>3.278973000000001</v>
+        <v>3.07267785</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1053955607299795</v>
+        <v>0.1060958610910838</v>
       </c>
       <c r="T32">
-        <v>0.8671880236034363</v>
+        <v>0.8773782471475424</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.044579635681003</v>
+        <v>3.690628368294931</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08745839415284784</v>
+        <v>0.08734739579471006</v>
       </c>
       <c r="C33">
-        <v>127.0238026450408</v>
+        <v>125.813283715169</v>
       </c>
       <c r="D33">
-        <v>165.9978026450408</v>
+        <v>166.441283715169</v>
       </c>
       <c r="E33">
-        <v>24.174</v>
+        <v>25.828</v>
       </c>
       <c r="F33">
-        <v>51.274</v>
+        <v>52.928</v>
       </c>
       <c r="G33">
         <v>12.3</v>
@@ -3981,28 +3981,28 @@
         <v>11.6</v>
       </c>
       <c r="M33">
-        <v>3.1430962</v>
+        <v>3.2444864</v>
       </c>
       <c r="N33">
-        <v>8.456903799999999</v>
+        <v>8.355513599999998</v>
       </c>
       <c r="O33">
-        <v>2.11422595</v>
+        <v>2.0888784</v>
       </c>
       <c r="P33">
-        <v>6.342677849999999</v>
+        <v>6.266635199999999</v>
       </c>
       <c r="Q33">
-        <v>3.07267785</v>
+        <v>2.996635199999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1060958610910838</v>
+        <v>0.1068167585216324</v>
       </c>
       <c r="T33">
-        <v>0.8773782471475424</v>
+        <v>0.8878681831488282</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.690628368294931</v>
+        <v>3.575296231785714</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08734739579471006</v>
+        <v>0.08792939743657227</v>
       </c>
       <c r="C34">
-        <v>125.813283715169</v>
+        <v>121.859960527798</v>
       </c>
       <c r="D34">
-        <v>166.441283715169</v>
+        <v>164.1419605277979</v>
       </c>
       <c r="E34">
-        <v>25.828</v>
+        <v>27.48200000000001</v>
       </c>
       <c r="F34">
-        <v>52.928</v>
+        <v>54.58200000000001</v>
       </c>
       <c r="G34">
         <v>12.3</v>
@@ -4063,45 +4063,45 @@
         <v>11.6</v>
       </c>
       <c r="M34">
-        <v>3.2444864</v>
+        <v>3.498706200000001</v>
       </c>
       <c r="N34">
-        <v>8.355513599999998</v>
+        <v>8.101293799999999</v>
       </c>
       <c r="O34">
-        <v>2.0888784</v>
+        <v>2.02532345</v>
       </c>
       <c r="P34">
-        <v>6.266635199999999</v>
+        <v>6.075970349999999</v>
       </c>
       <c r="Q34">
-        <v>2.996635199999999</v>
+        <v>2.805970349999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1068167585216324</v>
+        <v>0.1075591752784661</v>
       </c>
       <c r="T34">
-        <v>0.8878681831488282</v>
+        <v>0.8986712515680629</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.575296231785714</v>
+        <v>3.315511316726165</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08792939743657227</v>
+        <v>0.08783939907843445</v>
       </c>
       <c r="C35">
-        <v>121.859960527798</v>
+        <v>120.5573572478477</v>
       </c>
       <c r="D35">
-        <v>164.1419605277979</v>
+        <v>164.4933572478477</v>
       </c>
       <c r="E35">
-        <v>27.48200000000001</v>
+        <v>29.136</v>
       </c>
       <c r="F35">
-        <v>54.58200000000001</v>
+        <v>56.236</v>
       </c>
       <c r="G35">
         <v>12.3</v>
@@ -4145,28 +4145,28 @@
         <v>11.6</v>
       </c>
       <c r="M35">
-        <v>3.498706200000001</v>
+        <v>3.6047276</v>
       </c>
       <c r="N35">
-        <v>8.101293799999999</v>
+        <v>7.995272399999999</v>
       </c>
       <c r="O35">
-        <v>2.02532345</v>
+        <v>1.9988181</v>
       </c>
       <c r="P35">
-        <v>6.075970349999999</v>
+        <v>5.9964543</v>
       </c>
       <c r="Q35">
-        <v>2.805970349999999</v>
+        <v>2.7264543</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1075591752784661</v>
+        <v>0.1083240895127795</v>
       </c>
       <c r="T35">
-        <v>0.8986712515680629</v>
+        <v>0.9098016856969713</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.315511316726165</v>
+        <v>3.217996277998925</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08783939907843445</v>
+        <v>0.08774940072029665</v>
       </c>
       <c r="C36">
-        <v>120.5573572478477</v>
+        <v>119.2562617428509</v>
       </c>
       <c r="D36">
-        <v>164.4933572478477</v>
+        <v>164.8462617428509</v>
       </c>
       <c r="E36">
-        <v>29.136</v>
+        <v>30.79000000000001</v>
       </c>
       <c r="F36">
-        <v>56.236</v>
+        <v>57.89000000000001</v>
       </c>
       <c r="G36">
         <v>12.3</v>
@@ -4227,28 +4227,28 @@
         <v>11.6</v>
       </c>
       <c r="M36">
-        <v>3.6047276</v>
+        <v>3.710749000000001</v>
       </c>
       <c r="N36">
-        <v>7.995272399999999</v>
+        <v>7.889250999999999</v>
       </c>
       <c r="O36">
-        <v>1.9988181</v>
+        <v>1.97231275</v>
       </c>
       <c r="P36">
-        <v>5.9964543</v>
+        <v>5.916938249999999</v>
       </c>
       <c r="Q36">
-        <v>2.7264543</v>
+        <v>2.64693825</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1083240895127795</v>
+        <v>0.1091125395696872</v>
       </c>
       <c r="T36">
-        <v>0.9098016856969713</v>
+        <v>0.9212745947221538</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.217996277998925</v>
+        <v>3.126053527198956</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08774940072029665</v>
+        <v>0.08765940236215886</v>
       </c>
       <c r="C37">
-        <v>119.2562617428509</v>
+        <v>117.9566837380254</v>
       </c>
       <c r="D37">
-        <v>164.8462617428509</v>
+        <v>165.2006837380254</v>
       </c>
       <c r="E37">
-        <v>30.79000000000001</v>
+        <v>32.44400000000001</v>
       </c>
       <c r="F37">
-        <v>57.89000000000001</v>
+        <v>59.54400000000001</v>
       </c>
       <c r="G37">
         <v>12.3</v>
@@ -4309,28 +4309,28 @@
         <v>11.6</v>
       </c>
       <c r="M37">
-        <v>3.710749000000001</v>
+        <v>3.816770400000001</v>
       </c>
       <c r="N37">
-        <v>7.889250999999999</v>
+        <v>7.783229599999999</v>
       </c>
       <c r="O37">
-        <v>1.97231275</v>
+        <v>1.9458074</v>
       </c>
       <c r="P37">
-        <v>5.916938249999999</v>
+        <v>5.837422199999999</v>
       </c>
       <c r="Q37">
-        <v>2.64693825</v>
+        <v>2.567422199999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1091125395696872</v>
+        <v>0.1099256286908732</v>
       </c>
       <c r="T37">
-        <v>0.9212745947221538</v>
+        <v>0.9331060321543732</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.126053527198956</v>
+        <v>3.039218706998984</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08765940236215887</v>
+        <v>0.08973390400402106</v>
       </c>
       <c r="C38">
-        <v>117.9566837380253</v>
+        <v>108.5021229315028</v>
       </c>
       <c r="D38">
-        <v>165.2006837380253</v>
+        <v>157.4001229315028</v>
       </c>
       <c r="E38">
-        <v>32.444</v>
+        <v>34.098</v>
       </c>
       <c r="F38">
-        <v>59.544</v>
+        <v>61.198</v>
       </c>
       <c r="G38">
         <v>12.3</v>
@@ -4391,45 +4391,45 @@
         <v>11.6</v>
       </c>
       <c r="M38">
-        <v>3.8167704</v>
+        <v>4.4001362</v>
       </c>
       <c r="N38">
-        <v>7.783229599999999</v>
+        <v>7.199863799999999</v>
       </c>
       <c r="O38">
-        <v>1.9458074</v>
+        <v>1.79996595</v>
       </c>
       <c r="P38">
-        <v>5.8374222</v>
+        <v>5.399897849999999</v>
       </c>
       <c r="Q38">
-        <v>2.5674222</v>
+        <v>2.12989785</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1099256286908732</v>
+        <v>0.1107645301651128</v>
       </c>
       <c r="T38">
-        <v>0.9331060321543732</v>
+        <v>0.945313070774917</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.039218706998985</v>
+        <v>2.636282031451662</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08973390400402106</v>
+        <v>0.08970240564588326</v>
       </c>
       <c r="C39">
-        <v>108.5021229315028</v>
+        <v>106.9610517191191</v>
       </c>
       <c r="D39">
-        <v>157.4001229315028</v>
+        <v>157.5130517191191</v>
       </c>
       <c r="E39">
-        <v>34.098</v>
+        <v>35.752</v>
       </c>
       <c r="F39">
-        <v>61.198</v>
+        <v>62.852</v>
       </c>
       <c r="G39">
         <v>12.3</v>
@@ -4473,28 +4473,28 @@
         <v>11.6</v>
       </c>
       <c r="M39">
-        <v>4.4001362</v>
+        <v>4.519058800000001</v>
       </c>
       <c r="N39">
-        <v>7.199863799999999</v>
+        <v>7.080941199999999</v>
       </c>
       <c r="O39">
-        <v>1.79996595</v>
+        <v>1.7702353</v>
       </c>
       <c r="P39">
-        <v>5.399897849999999</v>
+        <v>5.310705899999999</v>
       </c>
       <c r="Q39">
-        <v>2.12989785</v>
+        <v>2.0407059</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1107645301651128</v>
+        <v>0.1116304929772311</v>
       </c>
       <c r="T39">
-        <v>0.945313070774917</v>
+        <v>0.9579138848348333</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.636282031451662</v>
+        <v>2.566906188518724</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08970240564588326</v>
+        <v>0.08967090728774545</v>
       </c>
       <c r="C40">
-        <v>106.9610517191191</v>
+        <v>105.4201426675668</v>
       </c>
       <c r="D40">
-        <v>157.5130517191191</v>
+        <v>157.6261426675667</v>
       </c>
       <c r="E40">
-        <v>35.752</v>
+        <v>37.406</v>
       </c>
       <c r="F40">
-        <v>62.852</v>
+        <v>64.506</v>
       </c>
       <c r="G40">
         <v>12.3</v>
@@ -4555,28 +4555,28 @@
         <v>11.6</v>
       </c>
       <c r="M40">
-        <v>4.519058800000001</v>
+        <v>4.6379814</v>
       </c>
       <c r="N40">
-        <v>7.080941199999999</v>
+        <v>6.9620186</v>
       </c>
       <c r="O40">
-        <v>1.7702353</v>
+        <v>1.74050465</v>
       </c>
       <c r="P40">
-        <v>5.310705899999999</v>
+        <v>5.221513949999999</v>
       </c>
       <c r="Q40">
-        <v>2.0407059</v>
+        <v>1.95151395</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1116304929772311</v>
+        <v>0.1125248480126975</v>
       </c>
       <c r="T40">
-        <v>0.9579138848348333</v>
+        <v>0.9709278403393369</v>
       </c>
       <c r="U40">
         <v>0.07190000000000001</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.566906188518724</v>
+        <v>2.501088081120808</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08967090728774545</v>
+        <v>0.09080940892960768</v>
       </c>
       <c r="C41">
-        <v>105.4201426675668</v>
+        <v>99.77902916185293</v>
       </c>
       <c r="D41">
-        <v>157.6261426675667</v>
+        <v>153.6390291618529</v>
       </c>
       <c r="E41">
-        <v>37.406</v>
+        <v>39.06000000000001</v>
       </c>
       <c r="F41">
-        <v>64.506</v>
+        <v>66.16000000000001</v>
       </c>
       <c r="G41">
         <v>12.3</v>
@@ -4637,45 +4637,45 @@
         <v>11.6</v>
       </c>
       <c r="M41">
-        <v>4.6379814</v>
+        <v>5.014928000000001</v>
       </c>
       <c r="N41">
-        <v>6.9620186</v>
+        <v>6.585071999999998</v>
       </c>
       <c r="O41">
-        <v>1.74050465</v>
+        <v>1.646268</v>
       </c>
       <c r="P41">
-        <v>5.221513949999999</v>
+        <v>4.938803999999999</v>
       </c>
       <c r="Q41">
-        <v>1.95151395</v>
+        <v>1.668804</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1125248480126975</v>
+        <v>0.1134490148826794</v>
       </c>
       <c r="T41">
-        <v>0.9709278403393369</v>
+        <v>0.9843755943606574</v>
       </c>
       <c r="U41">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.501088081120808</v>
+        <v>2.313094026474557</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09080940892960768</v>
+        <v>0.09080716057146987</v>
       </c>
       <c r="C42">
-        <v>99.77902916185293</v>
+        <v>98.13270428636899</v>
       </c>
       <c r="D42">
-        <v>153.6390291618529</v>
+        <v>153.646704286369</v>
       </c>
       <c r="E42">
-        <v>39.06000000000001</v>
+        <v>40.71400000000001</v>
       </c>
       <c r="F42">
-        <v>66.16000000000001</v>
+        <v>67.81400000000001</v>
       </c>
       <c r="G42">
         <v>12.3</v>
@@ -4719,28 +4719,28 @@
         <v>11.6</v>
       </c>
       <c r="M42">
-        <v>5.014928000000001</v>
+        <v>5.140301200000001</v>
       </c>
       <c r="N42">
-        <v>6.585071999999998</v>
+        <v>6.459698799999999</v>
       </c>
       <c r="O42">
-        <v>1.646268</v>
+        <v>1.6149247</v>
       </c>
       <c r="P42">
-        <v>4.938803999999999</v>
+        <v>4.8447741</v>
       </c>
       <c r="Q42">
-        <v>1.668804</v>
+        <v>1.5747741</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1134490148826794</v>
+        <v>0.1144045094431693</v>
       </c>
       <c r="T42">
-        <v>0.9843755943606574</v>
+        <v>0.9982792044504972</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.313094026474557</v>
+        <v>2.256677098999568</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09080716057146987</v>
+        <v>0.09080491221333206</v>
       </c>
       <c r="C43">
-        <v>98.13270428636899</v>
+        <v>96.48638017775376</v>
       </c>
       <c r="D43">
-        <v>153.646704286369</v>
+        <v>153.6543801777538</v>
       </c>
       <c r="E43">
-        <v>40.71400000000001</v>
+        <v>42.368</v>
       </c>
       <c r="F43">
-        <v>67.81400000000001</v>
+        <v>69.468</v>
       </c>
       <c r="G43">
         <v>12.3</v>
@@ -4801,28 +4801,28 @@
         <v>11.6</v>
       </c>
       <c r="M43">
-        <v>5.140301200000001</v>
+        <v>5.265674400000001</v>
       </c>
       <c r="N43">
-        <v>6.459698799999999</v>
+        <v>6.334325599999999</v>
       </c>
       <c r="O43">
-        <v>1.6149247</v>
+        <v>1.5835814</v>
       </c>
       <c r="P43">
-        <v>4.8447741</v>
+        <v>4.750744199999999</v>
       </c>
       <c r="Q43">
-        <v>1.5747741</v>
+        <v>1.480744199999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1144045094431693</v>
+        <v>0.1153929520919518</v>
       </c>
       <c r="T43">
-        <v>0.9982792044504972</v>
+        <v>1.012662249371021</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.256677098999568</v>
+        <v>2.20294669188053</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09080491221333206</v>
+        <v>0.09080266385519425</v>
       </c>
       <c r="C44">
-        <v>96.48638017775376</v>
+        <v>94.84005683612212</v>
       </c>
       <c r="D44">
-        <v>153.6543801777538</v>
+        <v>153.6620568361221</v>
       </c>
       <c r="E44">
-        <v>42.368</v>
+        <v>44.022</v>
       </c>
       <c r="F44">
-        <v>69.468</v>
+        <v>71.122</v>
       </c>
       <c r="G44">
         <v>12.3</v>
@@ -4883,28 +4883,28 @@
         <v>11.6</v>
       </c>
       <c r="M44">
-        <v>5.265674400000001</v>
+        <v>5.3910476</v>
       </c>
       <c r="N44">
-        <v>6.334325599999999</v>
+        <v>6.208952399999999</v>
       </c>
       <c r="O44">
-        <v>1.5835814</v>
+        <v>1.5522381</v>
       </c>
       <c r="P44">
-        <v>4.750744199999999</v>
+        <v>4.656714299999999</v>
       </c>
       <c r="Q44">
-        <v>1.480744199999999</v>
+        <v>1.3867143</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1153929520919518</v>
+        <v>0.1164160769389373</v>
       </c>
       <c r="T44">
-        <v>1.012662249371021</v>
+        <v>1.02754996253437</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.20294669188053</v>
+        <v>2.151715373464705</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09080266385519425</v>
+        <v>0.09080041549705647</v>
       </c>
       <c r="C45">
-        <v>94.84005683612212</v>
+        <v>93.19373426158897</v>
       </c>
       <c r="D45">
-        <v>153.6620568361221</v>
+        <v>153.669734261589</v>
       </c>
       <c r="E45">
-        <v>44.022</v>
+        <v>45.67599999999999</v>
       </c>
       <c r="F45">
-        <v>71.122</v>
+        <v>72.776</v>
       </c>
       <c r="G45">
         <v>12.3</v>
@@ -4965,28 +4965,28 @@
         <v>11.6</v>
       </c>
       <c r="M45">
-        <v>5.3910476</v>
+        <v>5.516420800000001</v>
       </c>
       <c r="N45">
-        <v>6.208952399999999</v>
+        <v>6.083579199999999</v>
       </c>
       <c r="O45">
-        <v>1.5522381</v>
+        <v>1.5208948</v>
       </c>
       <c r="P45">
-        <v>4.656714299999999</v>
+        <v>4.562684399999999</v>
       </c>
       <c r="Q45">
-        <v>1.3867143</v>
+        <v>1.2926844</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1164160769389373</v>
+        <v>0.1174757419590294</v>
       </c>
       <c r="T45">
-        <v>1.02754996253437</v>
+        <v>1.042969379739268</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.151715373464705</v>
+        <v>2.102812751340506</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09080041549705647</v>
+        <v>0.09079816713891867</v>
       </c>
       <c r="C46">
-        <v>93.19373426158897</v>
+        <v>91.54741245426945</v>
       </c>
       <c r="D46">
-        <v>153.669734261589</v>
+        <v>153.6774124542694</v>
       </c>
       <c r="E46">
-        <v>45.67599999999999</v>
+        <v>47.33000000000001</v>
       </c>
       <c r="F46">
-        <v>72.776</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="G46">
         <v>12.3</v>
@@ -5047,28 +5047,28 @@
         <v>11.6</v>
       </c>
       <c r="M46">
-        <v>5.516420800000001</v>
+        <v>5.641794000000001</v>
       </c>
       <c r="N46">
-        <v>6.083579199999999</v>
+        <v>5.958205999999999</v>
       </c>
       <c r="O46">
-        <v>1.5208948</v>
+        <v>1.4895515</v>
       </c>
       <c r="P46">
-        <v>4.562684399999999</v>
+        <v>4.4686545</v>
       </c>
       <c r="Q46">
-        <v>1.2926844</v>
+        <v>1.1986545</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1174757419590294</v>
+        <v>0.1185739402525794</v>
       </c>
       <c r="T46">
-        <v>1.042969379739268</v>
+        <v>1.058949503024343</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.102812751340506</v>
+        <v>2.056083579088495</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09079816713891867</v>
+        <v>0.09079591878078089</v>
       </c>
       <c r="C47">
-        <v>91.54741245426945</v>
+        <v>89.90109141427843</v>
       </c>
       <c r="D47">
-        <v>153.6774124542694</v>
+        <v>153.6850914142784</v>
       </c>
       <c r="E47">
-        <v>47.33000000000001</v>
+        <v>48.984</v>
       </c>
       <c r="F47">
-        <v>74.43000000000001</v>
+        <v>76.084</v>
       </c>
       <c r="G47">
         <v>12.3</v>
@@ -5129,28 +5129,28 @@
         <v>11.6</v>
       </c>
       <c r="M47">
-        <v>5.641794000000001</v>
+        <v>5.767167200000001</v>
       </c>
       <c r="N47">
-        <v>5.958205999999999</v>
+        <v>5.832832799999998</v>
       </c>
       <c r="O47">
-        <v>1.4895515</v>
+        <v>1.4582082</v>
       </c>
       <c r="P47">
-        <v>4.4686545</v>
+        <v>4.374624599999999</v>
       </c>
       <c r="Q47">
-        <v>1.1986545</v>
+        <v>1.104624599999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1185739402525794</v>
+        <v>0.1197128125570016</v>
       </c>
       <c r="T47">
-        <v>1.058949503024343</v>
+        <v>1.075521482727385</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.056083579088495</v>
+        <v>2.011386109977876</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09079591878078089</v>
+        <v>0.09579917042264308</v>
       </c>
       <c r="C48">
-        <v>89.90109141427843</v>
+        <v>72.868332537911</v>
       </c>
       <c r="D48">
-        <v>153.6850914142784</v>
+        <v>138.306332537911</v>
       </c>
       <c r="E48">
-        <v>48.984</v>
+        <v>50.63800000000001</v>
       </c>
       <c r="F48">
-        <v>76.084</v>
+        <v>77.73800000000001</v>
       </c>
       <c r="G48">
         <v>12.3</v>
@@ -5211,45 +5211,45 @@
         <v>11.6</v>
       </c>
       <c r="M48">
-        <v>5.767167200000001</v>
+        <v>6.996420000000001</v>
       </c>
       <c r="N48">
-        <v>5.832832799999998</v>
+        <v>4.603579999999998</v>
       </c>
       <c r="O48">
-        <v>1.4582082</v>
+        <v>1.150895</v>
       </c>
       <c r="P48">
-        <v>4.374624599999999</v>
+        <v>3.452684999999999</v>
       </c>
       <c r="Q48">
-        <v>1.104624599999999</v>
+        <v>0.1826849999999993</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1197128125570016</v>
+        <v>0.1208946611747982</v>
       </c>
       <c r="T48">
-        <v>1.075521482727385</v>
+        <v>1.092718820155069</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.011386109977876</v>
+        <v>1.657990801009659</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09579917042264308</v>
+        <v>0.09590342206450528</v>
       </c>
       <c r="C49">
-        <v>72.868332537911</v>
+        <v>70.92655454485389</v>
       </c>
       <c r="D49">
-        <v>138.306332537911</v>
+        <v>138.0185545448539</v>
       </c>
       <c r="E49">
-        <v>50.63800000000001</v>
+        <v>52.29200000000001</v>
       </c>
       <c r="F49">
-        <v>77.73800000000001</v>
+        <v>79.39200000000001</v>
       </c>
       <c r="G49">
         <v>12.3</v>
@@ -5293,28 +5293,28 @@
         <v>11.6</v>
       </c>
       <c r="M49">
-        <v>6.996420000000001</v>
+        <v>7.145280000000001</v>
       </c>
       <c r="N49">
-        <v>4.603579999999998</v>
+        <v>4.454719999999999</v>
       </c>
       <c r="O49">
-        <v>1.150895</v>
+        <v>1.11368</v>
       </c>
       <c r="P49">
-        <v>3.452684999999999</v>
+        <v>3.34104</v>
       </c>
       <c r="Q49">
-        <v>0.1826849999999993</v>
+        <v>0.07103999999999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1208946611747982</v>
+        <v>0.122121965508664</v>
       </c>
       <c r="T49">
-        <v>1.092718820155069</v>
+        <v>1.110577593637665</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.657990801009659</v>
+        <v>1.623449325988624</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09590342206450526</v>
+        <v>0.09600767370636748</v>
       </c>
       <c r="C50">
-        <v>70.92655454485396</v>
+        <v>68.98597164115476</v>
       </c>
       <c r="D50">
-        <v>138.0185545448539</v>
+        <v>137.7319716411548</v>
       </c>
       <c r="E50">
-        <v>52.29199999999999</v>
+        <v>53.94600000000001</v>
       </c>
       <c r="F50">
-        <v>79.392</v>
+        <v>81.04600000000001</v>
       </c>
       <c r="G50">
         <v>12.3</v>
@@ -5375,28 +5375,28 @@
         <v>11.6</v>
       </c>
       <c r="M50">
-        <v>7.14528</v>
+        <v>7.294140000000001</v>
       </c>
       <c r="N50">
-        <v>4.45472</v>
+        <v>4.305859999999999</v>
       </c>
       <c r="O50">
-        <v>1.11368</v>
+        <v>1.076465</v>
       </c>
       <c r="P50">
-        <v>3.34104</v>
+        <v>3.229394999999999</v>
       </c>
       <c r="Q50">
-        <v>0.07104000000000044</v>
+        <v>-0.04060500000000022</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.122121965508664</v>
+        <v>0.1233973994242499</v>
       </c>
       <c r="T50">
-        <v>1.110577593637665</v>
+        <v>1.129136711178401</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.623449325988625</v>
+        <v>1.590317707090898</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09600767370636748</v>
+        <v>0.09611192534822968</v>
       </c>
       <c r="C51">
-        <v>68.98597164115476</v>
+        <v>67.04657639775819</v>
       </c>
       <c r="D51">
-        <v>137.7319716411548</v>
+        <v>137.4465763977582</v>
       </c>
       <c r="E51">
-        <v>53.94600000000001</v>
+        <v>55.6</v>
       </c>
       <c r="F51">
-        <v>81.04600000000001</v>
+        <v>82.7</v>
       </c>
       <c r="G51">
         <v>12.3</v>
@@ -5457,28 +5457,28 @@
         <v>11.6</v>
       </c>
       <c r="M51">
-        <v>7.294140000000001</v>
+        <v>7.443</v>
       </c>
       <c r="N51">
-        <v>4.305859999999999</v>
+        <v>4.157</v>
       </c>
       <c r="O51">
-        <v>1.076465</v>
+        <v>1.03925</v>
       </c>
       <c r="P51">
-        <v>3.229394999999999</v>
+        <v>3.11775</v>
       </c>
       <c r="Q51">
-        <v>-0.04060500000000022</v>
+        <v>-0.1522499999999996</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1233973994242499</v>
+        <v>0.1247238506964594</v>
       </c>
       <c r="T51">
-        <v>1.129136711178401</v>
+        <v>1.148438193420767</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.590317707090898</v>
+        <v>1.55851135294908</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09611192534822968</v>
+        <v>0.09621617699009187</v>
       </c>
       <c r="C52">
-        <v>67.04657639775819</v>
+        <v>65.10836144705659</v>
       </c>
       <c r="D52">
-        <v>137.4465763977582</v>
+        <v>137.1623614470566</v>
       </c>
       <c r="E52">
-        <v>55.6</v>
+        <v>57.254</v>
       </c>
       <c r="F52">
-        <v>82.7</v>
+        <v>84.354</v>
       </c>
       <c r="G52">
         <v>12.3</v>
@@ -5539,28 +5539,28 @@
         <v>11.6</v>
       </c>
       <c r="M52">
-        <v>7.443</v>
+        <v>7.59186</v>
       </c>
       <c r="N52">
-        <v>4.157</v>
+        <v>4.00814</v>
       </c>
       <c r="O52">
-        <v>1.03925</v>
+        <v>1.002035</v>
       </c>
       <c r="P52">
-        <v>3.11775</v>
+        <v>3.006105</v>
       </c>
       <c r="Q52">
-        <v>-0.1522499999999996</v>
+        <v>-0.2638949999999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1247238506964594</v>
+        <v>0.1261044428369222</v>
       </c>
       <c r="T52">
-        <v>1.148438193420767</v>
+        <v>1.168527491264862</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.55851135294908</v>
+        <v>1.527952306812823</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09621617699009187</v>
+        <v>0.120499590651414</v>
       </c>
       <c r="C53">
-        <v>65.10836144705659</v>
+        <v>18.86549111005945</v>
       </c>
       <c r="D53">
-        <v>137.1623614470566</v>
+        <v>92.57349111005946</v>
       </c>
       <c r="E53">
-        <v>57.254</v>
+        <v>58.90800000000001</v>
       </c>
       <c r="F53">
-        <v>84.354</v>
+        <v>86.00800000000001</v>
       </c>
       <c r="G53">
         <v>12.3</v>
@@ -5621,45 +5621,45 @@
         <v>11.6</v>
       </c>
       <c r="M53">
-        <v>7.59186</v>
+        <v>12.6259744</v>
       </c>
       <c r="N53">
-        <v>4.00814</v>
+        <v>-1.025974400000003</v>
       </c>
       <c r="O53">
-        <v>1.002035</v>
+        <v>-0.2564936000000007</v>
       </c>
       <c r="P53">
-        <v>3.006105</v>
+        <v>-0.769480800000002</v>
       </c>
       <c r="Q53">
-        <v>-0.2638949999999998</v>
+        <v>-4.039480800000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1261044428369222</v>
+        <v>0.1285350903585233</v>
       </c>
       <c r="T53">
-        <v>1.168527491264862</v>
+        <v>1.203896374358087</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.25</v>
+        <v>0.2296852431444815</v>
       </c>
       <c r="W53">
-        <v>0.0675</v>
+        <v>0.1130822063063901</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.527952306812823</v>
+        <v>0.9187409725779262</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.120499590651414</v>
+        <v>0.121509590651414</v>
       </c>
       <c r="C54">
-        <v>18.86549111005945</v>
+        <v>15.97651909110277</v>
       </c>
       <c r="D54">
-        <v>92.57349111005946</v>
+        <v>91.33851909110278</v>
       </c>
       <c r="E54">
-        <v>58.90800000000001</v>
+        <v>60.562</v>
       </c>
       <c r="F54">
-        <v>86.00800000000001</v>
+        <v>87.66200000000001</v>
       </c>
       <c r="G54">
         <v>12.3</v>
@@ -5703,37 +5703,37 @@
         <v>11.6</v>
       </c>
       <c r="M54">
-        <v>12.6259744</v>
+        <v>12.8687816</v>
       </c>
       <c r="N54">
-        <v>-1.025974400000003</v>
+        <v>-1.268781600000002</v>
       </c>
       <c r="O54">
-        <v>-0.2564936000000007</v>
+        <v>-0.3171954000000006</v>
       </c>
       <c r="P54">
-        <v>-0.769480800000002</v>
+        <v>-0.9515862000000017</v>
       </c>
       <c r="Q54">
-        <v>-4.039480800000002</v>
+        <v>-4.221586200000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1285350903585233</v>
+        <v>0.1302954114299812</v>
       </c>
       <c r="T54">
-        <v>1.203896374358087</v>
+        <v>1.229511190833791</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2296852431444815</v>
+        <v>0.2253515593115668</v>
       </c>
       <c r="W54">
-        <v>0.1130822063063901</v>
+        <v>0.113718391093062</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9187409725779262</v>
+        <v>0.9014062372462672</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.121509590651414</v>
+        <v>0.122519590651414</v>
       </c>
       <c r="C55">
-        <v>15.97651909110277</v>
+        <v>13.12006345364803</v>
       </c>
       <c r="D55">
-        <v>91.33851909110278</v>
+        <v>90.13606345364803</v>
       </c>
       <c r="E55">
-        <v>60.562</v>
+        <v>62.216</v>
       </c>
       <c r="F55">
-        <v>87.66200000000001</v>
+        <v>89.316</v>
       </c>
       <c r="G55">
         <v>12.3</v>
@@ -5785,37 +5785,37 @@
         <v>11.6</v>
       </c>
       <c r="M55">
-        <v>12.8687816</v>
+        <v>13.1115888</v>
       </c>
       <c r="N55">
-        <v>-1.268781600000002</v>
+        <v>-1.511588800000002</v>
       </c>
       <c r="O55">
-        <v>-0.3171954000000006</v>
+        <v>-0.3778972000000005</v>
       </c>
       <c r="P55">
-        <v>-0.9515862000000017</v>
+        <v>-1.133691600000001</v>
       </c>
       <c r="Q55">
-        <v>-4.221586200000001</v>
+        <v>-4.403691600000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1302954114299812</v>
+        <v>0.1321322682001982</v>
       </c>
       <c r="T55">
-        <v>1.229511190833791</v>
+        <v>1.256239694982351</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2253515593115668</v>
+        <v>0.2211783822872785</v>
       </c>
       <c r="W55">
-        <v>0.113718391093062</v>
+        <v>0.1143310134802275</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9014062372462672</v>
+        <v>0.8847135291491142</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.122519590651414</v>
+        <v>0.123529590651414</v>
       </c>
       <c r="C56">
-        <v>13.12006345364803</v>
+        <v>10.29485666707879</v>
       </c>
       <c r="D56">
-        <v>90.13606345364803</v>
+        <v>88.96485666707881</v>
       </c>
       <c r="E56">
-        <v>62.216</v>
+        <v>63.87000000000001</v>
       </c>
       <c r="F56">
-        <v>89.316</v>
+        <v>90.97000000000001</v>
       </c>
       <c r="G56">
         <v>12.3</v>
@@ -5867,37 +5867,37 @@
         <v>11.6</v>
       </c>
       <c r="M56">
-        <v>13.1115888</v>
+        <v>13.354396</v>
       </c>
       <c r="N56">
-        <v>-1.511588800000002</v>
+        <v>-1.754396000000003</v>
       </c>
       <c r="O56">
-        <v>-0.3778972000000005</v>
+        <v>-0.4385990000000008</v>
       </c>
       <c r="P56">
-        <v>-1.133691600000001</v>
+        <v>-1.315797000000003</v>
       </c>
       <c r="Q56">
-        <v>-4.403691600000001</v>
+        <v>-4.585797000000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1321322682001982</v>
+        <v>0.1340507630490915</v>
       </c>
       <c r="T56">
-        <v>1.256239694982351</v>
+        <v>1.284156132648626</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2211783822872785</v>
+        <v>0.2171569571547825</v>
       </c>
       <c r="W56">
-        <v>0.1143310134802275</v>
+        <v>0.1149213586896779</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8847135291491142</v>
+        <v>0.8686278286191301</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.123529590651414</v>
+        <v>0.124539590651414</v>
       </c>
       <c r="C57">
-        <v>10.29485666707879</v>
+        <v>7.499696235707702</v>
       </c>
       <c r="D57">
-        <v>88.96485666707881</v>
+        <v>87.82369623570771</v>
       </c>
       <c r="E57">
-        <v>63.87000000000001</v>
+        <v>65.524</v>
       </c>
       <c r="F57">
-        <v>90.97000000000001</v>
+        <v>92.62400000000001</v>
       </c>
       <c r="G57">
         <v>12.3</v>
@@ -5949,37 +5949,37 @@
         <v>11.6</v>
       </c>
       <c r="M57">
-        <v>13.354396</v>
+        <v>13.5972032</v>
       </c>
       <c r="N57">
-        <v>-1.754396000000003</v>
+        <v>-1.997203200000003</v>
       </c>
       <c r="O57">
-        <v>-0.4385990000000008</v>
+        <v>-0.4993008000000008</v>
       </c>
       <c r="P57">
-        <v>-1.315797000000003</v>
+        <v>-1.497902400000002</v>
       </c>
       <c r="Q57">
-        <v>-4.585797000000002</v>
+        <v>-4.767902400000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1340507630490915</v>
+        <v>0.1360564622092981</v>
       </c>
       <c r="T57">
-        <v>1.284156132648626</v>
+        <v>1.313341499299731</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2171569571547825</v>
+        <v>0.2132791543484471</v>
       </c>
       <c r="W57">
-        <v>0.1149213586896779</v>
+        <v>0.115490620141648</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8686278286191301</v>
+        <v>0.8531166173937885</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.124539590651414</v>
+        <v>0.1255495906514141</v>
       </c>
       <c r="C58">
-        <v>7.499696235707702</v>
+        <v>4.733440580556021</v>
       </c>
       <c r="D58">
-        <v>87.82369623570771</v>
+        <v>86.71144058055604</v>
       </c>
       <c r="E58">
-        <v>65.524</v>
+        <v>67.17800000000003</v>
       </c>
       <c r="F58">
-        <v>92.62400000000001</v>
+        <v>94.27800000000002</v>
       </c>
       <c r="G58">
         <v>12.3</v>
@@ -6031,37 +6031,37 @@
         <v>11.6</v>
       </c>
       <c r="M58">
-        <v>13.5972032</v>
+        <v>13.8400104</v>
       </c>
       <c r="N58">
-        <v>-1.997203200000003</v>
+        <v>-2.240010400000005</v>
       </c>
       <c r="O58">
-        <v>-0.4993008000000008</v>
+        <v>-0.5600026000000011</v>
       </c>
       <c r="P58">
-        <v>-1.497902400000002</v>
+        <v>-1.680007800000003</v>
       </c>
       <c r="Q58">
-        <v>-4.767902400000002</v>
+        <v>-4.950007800000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1360564622092981</v>
+        <v>0.1381554497025376</v>
       </c>
       <c r="T58">
-        <v>1.313341499299731</v>
+        <v>1.343884324864841</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2132791543484471</v>
+        <v>0.2095374147984743</v>
       </c>
       <c r="W58">
-        <v>0.115490620141648</v>
+        <v>0.116039907507584</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8531166173937885</v>
+        <v>0.8381496591938975</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1255495906514141</v>
+        <v>0.126559590651414</v>
       </c>
       <c r="C59">
-        <v>4.733440580556021</v>
+        <v>1.995005230154376</v>
       </c>
       <c r="D59">
-        <v>86.71144058055604</v>
+        <v>85.6270052301544</v>
       </c>
       <c r="E59">
-        <v>67.17800000000003</v>
+        <v>68.83200000000002</v>
       </c>
       <c r="F59">
-        <v>94.27800000000002</v>
+        <v>95.93200000000002</v>
       </c>
       <c r="G59">
         <v>12.3</v>
@@ -6113,37 +6113,37 @@
         <v>11.6</v>
       </c>
       <c r="M59">
-        <v>13.8400104</v>
+        <v>14.0828176</v>
       </c>
       <c r="N59">
-        <v>-2.240010400000005</v>
+        <v>-2.482817600000004</v>
       </c>
       <c r="O59">
-        <v>-0.5600026000000011</v>
+        <v>-0.620704400000001</v>
       </c>
       <c r="P59">
-        <v>-1.680007800000003</v>
+        <v>-1.862113200000003</v>
       </c>
       <c r="Q59">
-        <v>-4.950007800000003</v>
+        <v>-5.132113200000003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1381554497025376</v>
+        <v>0.1403543889811694</v>
       </c>
       <c r="T59">
-        <v>1.343884324864841</v>
+        <v>1.375881570694956</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2095374147984743</v>
+        <v>0.2059247007502248</v>
       </c>
       <c r="W59">
-        <v>0.116039907507584</v>
+        <v>0.116570253929867</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8381496591938975</v>
+        <v>0.8236988030008993</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.126559590651414</v>
+        <v>0.127569590651414</v>
       </c>
       <c r="C60">
-        <v>1.995005230154391</v>
+        <v>-0.7166407063543829</v>
       </c>
       <c r="D60">
-        <v>85.6270052301544</v>
+        <v>84.56935929364562</v>
       </c>
       <c r="E60">
-        <v>68.83199999999999</v>
+        <v>70.48599999999999</v>
       </c>
       <c r="F60">
-        <v>95.932</v>
+        <v>97.586</v>
       </c>
       <c r="G60">
         <v>12.3</v>
@@ -6195,37 +6195,37 @@
         <v>11.6</v>
       </c>
       <c r="M60">
-        <v>14.0828176</v>
+        <v>14.3256248</v>
       </c>
       <c r="N60">
-        <v>-2.482817600000002</v>
+        <v>-2.725624800000002</v>
       </c>
       <c r="O60">
-        <v>-0.6207044000000006</v>
+        <v>-0.6814062000000005</v>
       </c>
       <c r="P60">
-        <v>-1.862113200000002</v>
+        <v>-2.044218600000002</v>
       </c>
       <c r="Q60">
-        <v>-5.132113200000001</v>
+        <v>-5.314218600000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1403543889811694</v>
+        <v>0.1426605935904662</v>
       </c>
       <c r="T60">
-        <v>1.375881570694956</v>
+        <v>1.409439657785077</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2059247007502248</v>
+        <v>0.2024344515849668</v>
       </c>
       <c r="W60">
-        <v>0.116570253929867</v>
+        <v>0.1170826225073269</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8236988030008994</v>
+        <v>0.8097378063398671</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.127569590651414</v>
+        <v>0.1624281513769296</v>
       </c>
       <c r="C61">
-        <v>-0.7166407063543829</v>
+        <v>-27.64726656084456</v>
       </c>
       <c r="D61">
-        <v>84.56935929364562</v>
+        <v>59.29273343915543</v>
       </c>
       <c r="E61">
-        <v>70.48599999999999</v>
+        <v>72.13999999999999</v>
       </c>
       <c r="F61">
-        <v>97.586</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="G61">
         <v>12.3</v>
@@ -6277,45 +6277,45 @@
         <v>11.6</v>
       </c>
       <c r="M61">
-        <v>14.3256248</v>
+        <v>19.927392</v>
       </c>
       <c r="N61">
-        <v>-2.725624800000002</v>
+        <v>-8.327392000000001</v>
       </c>
       <c r="O61">
-        <v>-0.6814062000000005</v>
+        <v>-2.081848</v>
       </c>
       <c r="P61">
-        <v>-2.044218600000002</v>
+        <v>-6.245544000000001</v>
       </c>
       <c r="Q61">
-        <v>-5.314218600000001</v>
+        <v>-9.515544</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1426605935904662</v>
+        <v>0.148703510244017</v>
       </c>
       <c r="T61">
-        <v>1.409439657785077</v>
+        <v>1.497371458164241</v>
       </c>
       <c r="U61">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.2024344515849668</v>
+        <v>0.1455283260348369</v>
       </c>
       <c r="W61">
-        <v>0.1170826225073269</v>
+        <v>0.1715779121322047</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8097378063398671</v>
+        <v>0.5821133041393474</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1624281513769296</v>
+        <v>0.1639781513769296</v>
       </c>
       <c r="C62">
-        <v>-27.64726656084456</v>
+        <v>-30.07893769345152</v>
       </c>
       <c r="D62">
-        <v>59.29273343915543</v>
+        <v>58.51506230654849</v>
       </c>
       <c r="E62">
-        <v>72.13999999999999</v>
+        <v>73.79400000000001</v>
       </c>
       <c r="F62">
-        <v>99.23999999999999</v>
+        <v>100.894</v>
       </c>
       <c r="G62">
         <v>12.3</v>
@@ -6359,37 +6359,37 @@
         <v>11.6</v>
       </c>
       <c r="M62">
-        <v>19.927392</v>
+        <v>20.2595152</v>
       </c>
       <c r="N62">
-        <v>-8.327392000000001</v>
+        <v>-8.659515200000003</v>
       </c>
       <c r="O62">
-        <v>-2.081848</v>
+        <v>-2.164878800000001</v>
       </c>
       <c r="P62">
-        <v>-6.245544000000001</v>
+        <v>-6.494636400000003</v>
       </c>
       <c r="Q62">
-        <v>-9.515544</v>
+        <v>-9.764636400000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.148703510244017</v>
+        <v>0.1513420617887354</v>
       </c>
       <c r="T62">
-        <v>1.497371458164241</v>
+        <v>1.535765598117171</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1455283260348369</v>
+        <v>0.1431426157719707</v>
       </c>
       <c r="W62">
-        <v>0.1715779121322047</v>
+        <v>0.1720569627529883</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5821133041393474</v>
+        <v>0.5725704630878827</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1639781513769296</v>
+        <v>0.1655281513769296</v>
       </c>
       <c r="C63">
-        <v>-30.07893769345152</v>
+        <v>-32.49047337350736</v>
       </c>
       <c r="D63">
-        <v>58.51506230654849</v>
+        <v>57.75752662649265</v>
       </c>
       <c r="E63">
-        <v>73.79400000000001</v>
+        <v>75.44800000000001</v>
       </c>
       <c r="F63">
-        <v>100.894</v>
+        <v>102.548</v>
       </c>
       <c r="G63">
         <v>12.3</v>
@@ -6441,37 +6441,37 @@
         <v>11.6</v>
       </c>
       <c r="M63">
-        <v>20.2595152</v>
+        <v>20.5916384</v>
       </c>
       <c r="N63">
-        <v>-8.659515200000003</v>
+        <v>-8.991638400000001</v>
       </c>
       <c r="O63">
-        <v>-2.164878800000001</v>
+        <v>-2.2479096</v>
       </c>
       <c r="P63">
-        <v>-6.494636400000003</v>
+        <v>-6.743728800000001</v>
       </c>
       <c r="Q63">
-        <v>-9.764636400000002</v>
+        <v>-10.0137288</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1513420617887354</v>
+        <v>0.1541194844673863</v>
       </c>
       <c r="T63">
-        <v>1.535765598117171</v>
+        <v>1.576180482278149</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1431426157719707</v>
+        <v>0.1408338639046808</v>
       </c>
       <c r="W63">
-        <v>0.1720569627529883</v>
+        <v>0.1725205601279401</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5725704630878827</v>
+        <v>0.5633354556187233</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1655281513769296</v>
+        <v>0.1670781513769297</v>
       </c>
       <c r="C64">
-        <v>-32.49047337350736</v>
+        <v>-34.88264562675043</v>
       </c>
       <c r="D64">
-        <v>57.75752662649265</v>
+        <v>57.01935437324956</v>
       </c>
       <c r="E64">
-        <v>75.44800000000001</v>
+        <v>77.102</v>
       </c>
       <c r="F64">
-        <v>102.548</v>
+        <v>104.202</v>
       </c>
       <c r="G64">
         <v>12.3</v>
@@ -6523,37 +6523,37 @@
         <v>11.6</v>
       </c>
       <c r="M64">
-        <v>20.5916384</v>
+        <v>20.9237616</v>
       </c>
       <c r="N64">
-        <v>-8.991638400000001</v>
+        <v>-9.323761599999999</v>
       </c>
       <c r="O64">
-        <v>-2.2479096</v>
+        <v>-2.3309404</v>
       </c>
       <c r="P64">
-        <v>-6.743728800000001</v>
+        <v>-6.9928212</v>
       </c>
       <c r="Q64">
-        <v>-10.0137288</v>
+        <v>-10.2628212</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1541194844673863</v>
+        <v>0.15704703810164</v>
       </c>
       <c r="T64">
-        <v>1.576180482278149</v>
+        <v>1.618779954772153</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1408338639046808</v>
+        <v>0.1385984057474637</v>
       </c>
       <c r="W64">
-        <v>0.1725205601279401</v>
+        <v>0.1729694401259093</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5633354556187233</v>
+        <v>0.5543936229898547</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1670781513769297</v>
+        <v>0.1686281513769297</v>
       </c>
       <c r="C65">
-        <v>-34.88264562675043</v>
+        <v>-37.25618750935453</v>
       </c>
       <c r="D65">
-        <v>57.01935437324956</v>
+        <v>56.29981249064548</v>
       </c>
       <c r="E65">
-        <v>77.102</v>
+        <v>78.756</v>
       </c>
       <c r="F65">
-        <v>104.202</v>
+        <v>105.856</v>
       </c>
       <c r="G65">
         <v>12.3</v>
@@ -6605,37 +6605,37 @@
         <v>11.6</v>
       </c>
       <c r="M65">
-        <v>20.9237616</v>
+        <v>21.2558848</v>
       </c>
       <c r="N65">
-        <v>-9.323761599999999</v>
+        <v>-9.655884800000004</v>
       </c>
       <c r="O65">
-        <v>-2.3309404</v>
+        <v>-2.413971200000001</v>
       </c>
       <c r="P65">
-        <v>-6.9928212</v>
+        <v>-7.241913600000004</v>
       </c>
       <c r="Q65">
-        <v>-10.2628212</v>
+        <v>-10.5119136</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.15704703810164</v>
+        <v>0.1601372336044633</v>
       </c>
       <c r="T65">
-        <v>1.618779954772153</v>
+        <v>1.663746064626935</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1385984057474637</v>
+        <v>0.1364328056576595</v>
       </c>
       <c r="W65">
-        <v>0.1729694401259093</v>
+        <v>0.173404292623942</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5543936229898547</v>
+        <v>0.5457312226306381</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1686281513769297</v>
+        <v>0.1701781513769297</v>
       </c>
       <c r="C66">
-        <v>-37.25618750935453</v>
+        <v>-39.61179553612158</v>
       </c>
       <c r="D66">
-        <v>56.29981249064548</v>
+        <v>55.59820446387842</v>
       </c>
       <c r="E66">
-        <v>78.756</v>
+        <v>80.41</v>
       </c>
       <c r="F66">
-        <v>105.856</v>
+        <v>107.51</v>
       </c>
       <c r="G66">
         <v>12.3</v>
@@ -6687,37 +6687,37 @@
         <v>11.6</v>
       </c>
       <c r="M66">
-        <v>21.2558848</v>
+        <v>21.588008</v>
       </c>
       <c r="N66">
-        <v>-9.655884800000004</v>
+        <v>-9.988008000000002</v>
       </c>
       <c r="O66">
-        <v>-2.413971200000001</v>
+        <v>-2.497002000000001</v>
       </c>
       <c r="P66">
-        <v>-7.241913600000004</v>
+        <v>-7.491006000000002</v>
       </c>
       <c r="Q66">
-        <v>-10.5119136</v>
+        <v>-10.761006</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1601372336044633</v>
+        <v>0.163404011707448</v>
       </c>
       <c r="T66">
-        <v>1.663746064626935</v>
+        <v>1.711281666473419</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1364328056576595</v>
+        <v>0.1343338394167725</v>
       </c>
       <c r="W66">
-        <v>0.173404292623942</v>
+        <v>0.1738257650451121</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5457312226306381</v>
+        <v>0.5373353576670898</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1701781513769297</v>
+        <v>0.1717281513769296</v>
       </c>
       <c r="C67">
-        <v>-39.61179553612158</v>
+        <v>-41.95013192934843</v>
       </c>
       <c r="D67">
-        <v>55.59820446387842</v>
+        <v>54.91386807065159</v>
       </c>
       <c r="E67">
-        <v>80.41</v>
+        <v>82.06400000000002</v>
       </c>
       <c r="F67">
-        <v>107.51</v>
+        <v>109.164</v>
       </c>
       <c r="G67">
         <v>12.3</v>
@@ -6769,37 +6769,37 @@
         <v>11.6</v>
       </c>
       <c r="M67">
-        <v>21.588008</v>
+        <v>21.9201312</v>
       </c>
       <c r="N67">
-        <v>-9.988008000000002</v>
+        <v>-10.3201312</v>
       </c>
       <c r="O67">
-        <v>-2.497002000000001</v>
+        <v>-2.580032800000001</v>
       </c>
       <c r="P67">
-        <v>-7.491006000000002</v>
+        <v>-7.740098400000003</v>
       </c>
       <c r="Q67">
-        <v>-10.761006</v>
+        <v>-11.0100984</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.163404011707448</v>
+        <v>0.1668629532282553</v>
       </c>
       <c r="T67">
-        <v>1.711281666473419</v>
+        <v>1.761613480193226</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1343338394167725</v>
+        <v>0.132298478213488</v>
       </c>
       <c r="W67">
-        <v>0.1738257650451121</v>
+        <v>0.1742344655747316</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5373353576670898</v>
+        <v>0.5291939128539522</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1717281513769296</v>
+        <v>0.1732781513769296</v>
       </c>
       <c r="C68">
-        <v>-41.95013192934843</v>
+        <v>-44.27182670363045</v>
       </c>
       <c r="D68">
-        <v>54.91386807065159</v>
+        <v>54.24617329636956</v>
       </c>
       <c r="E68">
-        <v>82.06400000000002</v>
+        <v>83.71800000000002</v>
       </c>
       <c r="F68">
-        <v>109.164</v>
+        <v>110.818</v>
       </c>
       <c r="G68">
         <v>12.3</v>
@@ -6851,37 +6851,37 @@
         <v>11.6</v>
       </c>
       <c r="M68">
-        <v>21.9201312</v>
+        <v>22.2522544</v>
       </c>
       <c r="N68">
-        <v>-10.3201312</v>
+        <v>-10.6522544</v>
       </c>
       <c r="O68">
-        <v>-2.580032800000001</v>
+        <v>-2.663063600000001</v>
       </c>
       <c r="P68">
-        <v>-7.740098400000003</v>
+        <v>-7.989190800000001</v>
       </c>
       <c r="Q68">
-        <v>-11.0100984</v>
+        <v>-11.2591908</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1668629532282553</v>
+        <v>0.1705315275685054</v>
       </c>
       <c r="T68">
-        <v>1.761613480193226</v>
+        <v>1.814995706865747</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.132298478213488</v>
+        <v>0.1303238740610479</v>
       </c>
       <c r="W68">
-        <v>0.1742344655747316</v>
+        <v>0.1746309660885416</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5291939128539522</v>
+        <v>0.5212954962441918</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1732781513769296</v>
+        <v>0.1748281513769296</v>
       </c>
       <c r="C69">
-        <v>-44.27182670363045</v>
+        <v>-46.57747960039826</v>
       </c>
       <c r="D69">
-        <v>54.24617329636956</v>
+        <v>53.59452039960174</v>
       </c>
       <c r="E69">
-        <v>83.71800000000002</v>
+        <v>85.37200000000001</v>
       </c>
       <c r="F69">
-        <v>110.818</v>
+        <v>112.472</v>
       </c>
       <c r="G69">
         <v>12.3</v>
@@ -6933,37 +6933,37 @@
         <v>11.6</v>
       </c>
       <c r="M69">
-        <v>22.2522544</v>
+        <v>22.5843776</v>
       </c>
       <c r="N69">
-        <v>-10.6522544</v>
+        <v>-10.9843776</v>
       </c>
       <c r="O69">
-        <v>-2.663063600000001</v>
+        <v>-2.746094400000001</v>
       </c>
       <c r="P69">
-        <v>-7.989190800000001</v>
+        <v>-8.238283200000003</v>
       </c>
       <c r="Q69">
-        <v>-11.2591908</v>
+        <v>-11.5082832</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1705315275685054</v>
+        <v>0.1744293878050212</v>
       </c>
       <c r="T69">
-        <v>1.814995706865747</v>
+        <v>1.871714322705302</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1303238740610479</v>
+        <v>0.1284073465013266</v>
       </c>
       <c r="W69">
-        <v>0.1746309660885416</v>
+        <v>0.1750158048225336</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5212954962441918</v>
+        <v>0.5136293860053065</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1748281513769296</v>
+        <v>0.1763781513769297</v>
       </c>
       <c r="C70">
-        <v>-46.57747960039826</v>
+        <v>-48.8676618846733</v>
       </c>
       <c r="D70">
-        <v>53.59452039960174</v>
+        <v>52.95833811532673</v>
       </c>
       <c r="E70">
-        <v>85.37200000000001</v>
+        <v>87.02600000000001</v>
       </c>
       <c r="F70">
-        <v>112.472</v>
+        <v>114.126</v>
       </c>
       <c r="G70">
         <v>12.3</v>
@@ -7015,37 +7015,37 @@
         <v>11.6</v>
       </c>
       <c r="M70">
-        <v>22.5843776</v>
+        <v>22.91650080000001</v>
       </c>
       <c r="N70">
-        <v>-10.9843776</v>
+        <v>-11.31650080000001</v>
       </c>
       <c r="O70">
-        <v>-2.746094400000001</v>
+        <v>-2.829125200000001</v>
       </c>
       <c r="P70">
-        <v>-8.238283200000003</v>
+        <v>-8.487375600000004</v>
       </c>
       <c r="Q70">
-        <v>-11.5082832</v>
+        <v>-11.7573756</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1744293878050212</v>
+        <v>0.1785787228955058</v>
       </c>
       <c r="T70">
-        <v>1.871714322705302</v>
+        <v>1.932092204082893</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1284073465013266</v>
+        <v>0.1265463704650755</v>
       </c>
       <c r="W70">
-        <v>0.1750158048225336</v>
+        <v>0.1753894888106128</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5136293860053065</v>
+        <v>0.506185481860302</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1763781513769297</v>
+        <v>0.2030126631263484</v>
       </c>
       <c r="C71">
-        <v>-48.8676618846733</v>
+        <v>-59.49370936935179</v>
       </c>
       <c r="D71">
-        <v>52.95833811532673</v>
+        <v>43.98629063064822</v>
       </c>
       <c r="E71">
-        <v>87.02600000000001</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="F71">
-        <v>114.126</v>
+        <v>115.78</v>
       </c>
       <c r="G71">
         <v>12.3</v>
@@ -7097,45 +7097,45 @@
         <v>11.6</v>
       </c>
       <c r="M71">
-        <v>22.91650080000001</v>
+        <v>27.30092400000001</v>
       </c>
       <c r="N71">
-        <v>-11.31650080000001</v>
+        <v>-15.70092400000001</v>
       </c>
       <c r="O71">
-        <v>-2.829125200000001</v>
+        <v>-3.925231000000001</v>
       </c>
       <c r="P71">
-        <v>-8.487375600000004</v>
+        <v>-11.775693</v>
       </c>
       <c r="Q71">
-        <v>-11.7573756</v>
+        <v>-15.045693</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1785787228955058</v>
+        <v>0.1849530528234186</v>
       </c>
       <c r="T71">
-        <v>1.932092204082893</v>
+        <v>2.024846471418819</v>
       </c>
       <c r="U71">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1265463704650755</v>
+        <v>0.1062235109698118</v>
       </c>
       <c r="W71">
-        <v>0.1753894888106128</v>
+        <v>0.2107524961133184</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.506185481860302</v>
+        <v>0.4248940438792473</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2030126631263484</v>
+        <v>0.2049126631263485</v>
       </c>
       <c r="C72">
-        <v>-59.49370936935179</v>
+        <v>-61.67295953207369</v>
       </c>
       <c r="D72">
-        <v>43.98629063064822</v>
+        <v>43.46104046792632</v>
       </c>
       <c r="E72">
-        <v>88.68000000000001</v>
+        <v>90.334</v>
       </c>
       <c r="F72">
-        <v>115.78</v>
+        <v>117.434</v>
       </c>
       <c r="G72">
         <v>12.3</v>
@@ -7179,37 +7179,37 @@
         <v>11.6</v>
       </c>
       <c r="M72">
-        <v>27.30092400000001</v>
+        <v>27.6909372</v>
       </c>
       <c r="N72">
-        <v>-15.70092400000001</v>
+        <v>-16.09093720000001</v>
       </c>
       <c r="O72">
-        <v>-3.925231000000001</v>
+        <v>-4.022734300000002</v>
       </c>
       <c r="P72">
-        <v>-11.775693</v>
+        <v>-12.0682029</v>
       </c>
       <c r="Q72">
-        <v>-15.045693</v>
+        <v>-15.3382029</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1849530528234186</v>
+        <v>0.1897514339552606</v>
       </c>
       <c r="T72">
-        <v>2.024846471418819</v>
+        <v>2.094668763536709</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1062235109698118</v>
+        <v>0.1047274051815046</v>
       </c>
       <c r="W72">
-        <v>0.2107524961133184</v>
+        <v>0.2111052778582012</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4248940438792473</v>
+        <v>0.4189096207260185</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2049126631263484</v>
+        <v>0.2068126631263484</v>
       </c>
       <c r="C73">
-        <v>-61.67295953207368</v>
+        <v>-63.83981346098648</v>
       </c>
       <c r="D73">
-        <v>43.46104046792632</v>
+        <v>42.94818653901352</v>
       </c>
       <c r="E73">
-        <v>90.334</v>
+        <v>91.988</v>
       </c>
       <c r="F73">
-        <v>117.434</v>
+        <v>119.088</v>
       </c>
       <c r="G73">
         <v>12.3</v>
@@ -7261,37 +7261,37 @@
         <v>11.6</v>
       </c>
       <c r="M73">
-        <v>27.6909372</v>
+        <v>28.0809504</v>
       </c>
       <c r="N73">
-        <v>-16.0909372</v>
+        <v>-16.4809504</v>
       </c>
       <c r="O73">
-        <v>-4.0227343</v>
+        <v>-4.120237599999999</v>
       </c>
       <c r="P73">
-        <v>-12.0682029</v>
+        <v>-12.3607128</v>
       </c>
       <c r="Q73">
-        <v>-15.3382029</v>
+        <v>-15.6307128</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1897514339552606</v>
+        <v>0.1948925565965199</v>
       </c>
       <c r="T73">
-        <v>2.094668763536709</v>
+        <v>2.169478362234448</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1047274051815047</v>
+        <v>0.1032728578873171</v>
       </c>
       <c r="W73">
-        <v>0.2111052778582012</v>
+        <v>0.2114482601101706</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4189096207260187</v>
+        <v>0.4130914315492684</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2068126631263484</v>
+        <v>0.2087126631263484</v>
       </c>
       <c r="C74">
-        <v>-63.83981346098648</v>
+        <v>-65.99470487641217</v>
       </c>
       <c r="D74">
-        <v>42.94818653901352</v>
+        <v>42.44729512358784</v>
       </c>
       <c r="E74">
-        <v>91.988</v>
+        <v>93.642</v>
       </c>
       <c r="F74">
-        <v>119.088</v>
+        <v>120.742</v>
       </c>
       <c r="G74">
         <v>12.3</v>
@@ -7343,37 +7343,37 @@
         <v>11.6</v>
       </c>
       <c r="M74">
-        <v>28.0809504</v>
+        <v>28.4709636</v>
       </c>
       <c r="N74">
-        <v>-16.4809504</v>
+        <v>-16.8709636</v>
       </c>
       <c r="O74">
-        <v>-4.120237599999999</v>
+        <v>-4.217740900000001</v>
       </c>
       <c r="P74">
-        <v>-12.3607128</v>
+        <v>-12.6532227</v>
       </c>
       <c r="Q74">
-        <v>-15.6307128</v>
+        <v>-15.9232227</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1948925565965199</v>
+        <v>0.2004145031371317</v>
       </c>
       <c r="T74">
-        <v>2.169478362234448</v>
+        <v>2.249829412687576</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1032728578873171</v>
+        <v>0.1018581612039292</v>
       </c>
       <c r="W74">
-        <v>0.2114482601101706</v>
+        <v>0.2117818455881135</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4130914315492684</v>
+        <v>0.4074326448157166</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2087126631263484</v>
+        <v>0.2106126631263484</v>
       </c>
       <c r="C75">
-        <v>-65.99470487641217</v>
+        <v>-68.13804749854424</v>
       </c>
       <c r="D75">
-        <v>42.44729512358784</v>
+        <v>41.95795250145576</v>
       </c>
       <c r="E75">
-        <v>93.642</v>
+        <v>95.29599999999999</v>
       </c>
       <c r="F75">
-        <v>120.742</v>
+        <v>122.396</v>
       </c>
       <c r="G75">
         <v>12.3</v>
@@ -7425,37 +7425,37 @@
         <v>11.6</v>
       </c>
       <c r="M75">
-        <v>28.4709636</v>
+        <v>28.8609768</v>
       </c>
       <c r="N75">
-        <v>-16.8709636</v>
+        <v>-17.2609768</v>
       </c>
       <c r="O75">
-        <v>-4.217740900000001</v>
+        <v>-4.3152442</v>
       </c>
       <c r="P75">
-        <v>-12.6532227</v>
+        <v>-12.9457326</v>
       </c>
       <c r="Q75">
-        <v>-15.9232227</v>
+        <v>-16.2157326</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2004145031371317</v>
+        <v>0.2063612147962522</v>
       </c>
       <c r="T75">
-        <v>2.249829412687576</v>
+        <v>2.33636131317556</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1018581612039292</v>
+        <v>0.1004816995660382</v>
       </c>
       <c r="W75">
-        <v>0.2117818455881135</v>
+        <v>0.2121064152423282</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4074326448157166</v>
+        <v>0.401926798264153</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2106126631263484</v>
+        <v>0.2125126631263485</v>
       </c>
       <c r="C76">
-        <v>-68.13804749854424</v>
+        <v>-70.27023618714043</v>
       </c>
       <c r="D76">
-        <v>41.95795250145576</v>
+        <v>41.47976381285958</v>
       </c>
       <c r="E76">
-        <v>95.29599999999999</v>
+        <v>96.95000000000002</v>
       </c>
       <c r="F76">
-        <v>122.396</v>
+        <v>124.05</v>
       </c>
       <c r="G76">
         <v>12.3</v>
@@ -7507,37 +7507,37 @@
         <v>11.6</v>
       </c>
       <c r="M76">
-        <v>28.8609768</v>
+        <v>29.25099000000001</v>
       </c>
       <c r="N76">
-        <v>-17.2609768</v>
+        <v>-17.65099000000001</v>
       </c>
       <c r="O76">
-        <v>-4.3152442</v>
+        <v>-4.412747500000002</v>
       </c>
       <c r="P76">
-        <v>-12.9457326</v>
+        <v>-13.23824250000001</v>
       </c>
       <c r="Q76">
-        <v>-16.2157326</v>
+        <v>-16.50824250000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2063612147962522</v>
+        <v>0.2127836633881023</v>
       </c>
       <c r="T76">
-        <v>2.33636131317556</v>
+        <v>2.429815765702582</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1004816995660382</v>
+        <v>0.09914194357182439</v>
       </c>
       <c r="W76">
-        <v>0.2121064152423282</v>
+        <v>0.2124223297057638</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.401926798264153</v>
+        <v>0.3965677742872975</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2125126631263485</v>
+        <v>0.2144126631263484</v>
       </c>
       <c r="C77">
-        <v>-70.27023618714043</v>
+        <v>-72.39164800416023</v>
       </c>
       <c r="D77">
-        <v>41.47976381285958</v>
+        <v>41.01235199583978</v>
       </c>
       <c r="E77">
-        <v>96.95000000000002</v>
+        <v>98.60400000000001</v>
       </c>
       <c r="F77">
-        <v>124.05</v>
+        <v>125.704</v>
       </c>
       <c r="G77">
         <v>12.3</v>
@@ -7589,37 +7589,37 @@
         <v>11.6</v>
       </c>
       <c r="M77">
-        <v>29.25099000000001</v>
+        <v>29.6410032</v>
       </c>
       <c r="N77">
-        <v>-17.65099000000001</v>
+        <v>-18.04100320000001</v>
       </c>
       <c r="O77">
-        <v>-4.412747500000002</v>
+        <v>-4.510250800000001</v>
       </c>
       <c r="P77">
-        <v>-13.23824250000001</v>
+        <v>-13.5307524</v>
       </c>
       <c r="Q77">
-        <v>-16.50824250000001</v>
+        <v>-16.8007524</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2127836633881023</v>
+        <v>0.2197413160292732</v>
       </c>
       <c r="T77">
-        <v>2.429815765702582</v>
+        <v>2.531058089273523</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09914194357182439</v>
+        <v>0.09783744431430039</v>
       </c>
       <c r="W77">
-        <v>0.2124223297057638</v>
+        <v>0.212729930630688</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3965677742872975</v>
+        <v>0.3913497772572014</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2144126631263484</v>
+        <v>0.2163126631263484</v>
       </c>
       <c r="C78">
-        <v>-72.39164800416023</v>
+        <v>-74.50264320535743</v>
       </c>
       <c r="D78">
-        <v>41.01235199583978</v>
+        <v>40.55535679464257</v>
       </c>
       <c r="E78">
-        <v>98.60400000000001</v>
+        <v>100.258</v>
       </c>
       <c r="F78">
-        <v>125.704</v>
+        <v>127.358</v>
       </c>
       <c r="G78">
         <v>12.3</v>
@@ -7671,37 +7671,37 @@
         <v>11.6</v>
       </c>
       <c r="M78">
-        <v>29.6410032</v>
+        <v>30.0310164</v>
       </c>
       <c r="N78">
-        <v>-18.04100320000001</v>
+        <v>-18.4310164</v>
       </c>
       <c r="O78">
-        <v>-4.510250800000001</v>
+        <v>-4.607754100000001</v>
       </c>
       <c r="P78">
-        <v>-13.5307524</v>
+        <v>-13.8232623</v>
       </c>
       <c r="Q78">
-        <v>-16.8007524</v>
+        <v>-17.0932623</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2197413160292732</v>
+        <v>0.2273039819435894</v>
       </c>
       <c r="T78">
-        <v>2.531058089273523</v>
+        <v>2.641104093154981</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09783744431430039</v>
+        <v>0.09656682815437441</v>
       </c>
       <c r="W78">
-        <v>0.212729930630688</v>
+        <v>0.2130295419211985</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3913497772572014</v>
+        <v>0.3862673126174976</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2163126631263484</v>
+        <v>0.2182126631263484</v>
       </c>
       <c r="C79">
-        <v>-74.50264320535743</v>
+        <v>-76.60356616630808</v>
       </c>
       <c r="D79">
-        <v>40.55535679464257</v>
+        <v>40.10843383369191</v>
       </c>
       <c r="E79">
-        <v>100.258</v>
+        <v>101.912</v>
       </c>
       <c r="F79">
-        <v>127.358</v>
+        <v>129.012</v>
       </c>
       <c r="G79">
         <v>12.3</v>
@@ -7753,37 +7753,37 @@
         <v>11.6</v>
       </c>
       <c r="M79">
-        <v>30.0310164</v>
+        <v>30.4210296</v>
       </c>
       <c r="N79">
-        <v>-18.4310164</v>
+        <v>-18.8210296</v>
       </c>
       <c r="O79">
-        <v>-4.607754100000001</v>
+        <v>-4.705257400000001</v>
       </c>
       <c r="P79">
-        <v>-13.8232623</v>
+        <v>-14.1157722</v>
       </c>
       <c r="Q79">
-        <v>-17.0932623</v>
+        <v>-17.3857722</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2273039819435894</v>
+        <v>0.2355541629410253</v>
       </c>
       <c r="T79">
-        <v>2.641104093154981</v>
+        <v>2.76115427920748</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09656682815437441</v>
+        <v>0.095328791895985</v>
       </c>
       <c r="W79">
-        <v>0.2130295419211985</v>
+        <v>0.2133214708709268</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3862673126174976</v>
+        <v>0.3813151675839399</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2182126631263484</v>
+        <v>0.2201126631263484</v>
       </c>
       <c r="C80">
-        <v>-76.60356616630808</v>
+        <v>-78.69474624787668</v>
       </c>
       <c r="D80">
-        <v>40.10843383369191</v>
+        <v>39.67125375212332</v>
       </c>
       <c r="E80">
-        <v>101.912</v>
+        <v>103.566</v>
       </c>
       <c r="F80">
-        <v>129.012</v>
+        <v>130.666</v>
       </c>
       <c r="G80">
         <v>12.3</v>
@@ -7835,37 +7835,37 @@
         <v>11.6</v>
       </c>
       <c r="M80">
-        <v>30.4210296</v>
+        <v>30.8110428</v>
       </c>
       <c r="N80">
-        <v>-18.8210296</v>
+        <v>-19.2110428</v>
       </c>
       <c r="O80">
-        <v>-4.705257400000001</v>
+        <v>-4.8027607</v>
       </c>
       <c r="P80">
-        <v>-14.1157722</v>
+        <v>-14.4082821</v>
       </c>
       <c r="Q80">
-        <v>-17.3857722</v>
+        <v>-17.6782821</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2355541629410253</v>
+        <v>0.2445900754620266</v>
       </c>
       <c r="T80">
-        <v>2.76115427920748</v>
+        <v>2.892637816312599</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.095328791895985</v>
+        <v>0.0941220983276814</v>
       </c>
       <c r="W80">
-        <v>0.2133214708709268</v>
+        <v>0.2136060092143327</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3813151675839399</v>
+        <v>0.3764883933107256</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2201126631263484</v>
+        <v>0.2220126631263484</v>
       </c>
       <c r="C81">
-        <v>-78.69474624787668</v>
+        <v>-80.77649860569103</v>
       </c>
       <c r="D81">
-        <v>39.67125375212332</v>
+        <v>39.24350139430899</v>
       </c>
       <c r="E81">
-        <v>103.566</v>
+        <v>105.22</v>
       </c>
       <c r="F81">
-        <v>130.666</v>
+        <v>132.32</v>
       </c>
       <c r="G81">
         <v>12.3</v>
@@ -7917,37 +7917,37 @@
         <v>11.6</v>
       </c>
       <c r="M81">
-        <v>30.8110428</v>
+        <v>31.201056</v>
       </c>
       <c r="N81">
-        <v>-19.2110428</v>
+        <v>-19.60105600000001</v>
       </c>
       <c r="O81">
-        <v>-4.8027607</v>
+        <v>-4.900264000000002</v>
       </c>
       <c r="P81">
-        <v>-14.4082821</v>
+        <v>-14.70079200000001</v>
       </c>
       <c r="Q81">
-        <v>-17.6782821</v>
+        <v>-17.970792</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2445900754620266</v>
+        <v>0.2545295792351279</v>
       </c>
       <c r="T81">
-        <v>2.892637816312599</v>
+        <v>3.037269707128228</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0941220983276814</v>
+        <v>0.09294557209858537</v>
       </c>
       <c r="W81">
-        <v>0.2136060092143327</v>
+        <v>0.2138834340991536</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3764883933107256</v>
+        <v>0.3717822883943414</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2220126631263484</v>
+        <v>0.2239126631263484</v>
       </c>
       <c r="C82">
-        <v>-80.77649860569103</v>
+        <v>-82.84912494780737</v>
       </c>
       <c r="D82">
-        <v>39.24350139430899</v>
+        <v>38.82487505219265</v>
       </c>
       <c r="E82">
-        <v>105.22</v>
+        <v>106.874</v>
       </c>
       <c r="F82">
-        <v>132.32</v>
+        <v>133.974</v>
       </c>
       <c r="G82">
         <v>12.3</v>
@@ -7999,37 +7999,37 @@
         <v>11.6</v>
       </c>
       <c r="M82">
-        <v>31.201056</v>
+        <v>31.59106920000001</v>
       </c>
       <c r="N82">
-        <v>-19.60105600000001</v>
+        <v>-19.99106920000001</v>
       </c>
       <c r="O82">
-        <v>-4.900264000000002</v>
+        <v>-4.997767300000001</v>
       </c>
       <c r="P82">
-        <v>-14.70079200000001</v>
+        <v>-14.9933019</v>
       </c>
       <c r="Q82">
-        <v>-17.970792</v>
+        <v>-18.2633019</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2545295792351279</v>
+        <v>0.2655153465632925</v>
       </c>
       <c r="T82">
-        <v>3.037269707128228</v>
+        <v>3.197126007503398</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09294557209858537</v>
+        <v>0.0917980958998374</v>
       </c>
       <c r="W82">
-        <v>0.2138834340991536</v>
+        <v>0.2141540089868183</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3717822883943414</v>
+        <v>0.3671923835993496</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2239126631263484</v>
+        <v>0.2258126631263484</v>
       </c>
       <c r="C83">
-        <v>-82.84912494780737</v>
+        <v>-84.91291424439362</v>
       </c>
       <c r="D83">
-        <v>38.82487505219265</v>
+        <v>38.4150857556064</v>
       </c>
       <c r="E83">
-        <v>106.874</v>
+        <v>108.528</v>
       </c>
       <c r="F83">
-        <v>133.974</v>
+        <v>135.628</v>
       </c>
       <c r="G83">
         <v>12.3</v>
@@ -8081,37 +8081,37 @@
         <v>11.6</v>
       </c>
       <c r="M83">
-        <v>31.59106920000001</v>
+        <v>31.98108240000001</v>
       </c>
       <c r="N83">
-        <v>-19.99106920000001</v>
+        <v>-20.3810824</v>
       </c>
       <c r="O83">
-        <v>-4.997767300000001</v>
+        <v>-5.095270600000001</v>
       </c>
       <c r="P83">
-        <v>-14.9933019</v>
+        <v>-15.2858118</v>
       </c>
       <c r="Q83">
-        <v>-18.2633019</v>
+        <v>-18.5558118</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2655153465632925</v>
+        <v>0.2777217547056977</v>
       </c>
       <c r="T83">
-        <v>3.197126007503398</v>
+        <v>3.374744119031365</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0917980958998374</v>
+        <v>0.09067860692544913</v>
       </c>
       <c r="W83">
-        <v>0.2141540089868183</v>
+        <v>0.2144179844869791</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3671923835993496</v>
+        <v>0.3627144277017966</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2258126631263484</v>
+        <v>0.2277126631263485</v>
       </c>
       <c r="C84">
-        <v>-84.91291424439362</v>
+        <v>-86.96814339293819</v>
       </c>
       <c r="D84">
-        <v>38.4150857556064</v>
+        <v>38.01385660706183</v>
       </c>
       <c r="E84">
-        <v>108.528</v>
+        <v>110.182</v>
       </c>
       <c r="F84">
-        <v>135.628</v>
+        <v>137.282</v>
       </c>
       <c r="G84">
         <v>12.3</v>
@@ -8163,37 +8163,37 @@
         <v>11.6</v>
       </c>
       <c r="M84">
-        <v>31.98108240000001</v>
+        <v>32.3710956</v>
       </c>
       <c r="N84">
-        <v>-20.3810824</v>
+        <v>-20.7710956</v>
       </c>
       <c r="O84">
-        <v>-5.095270600000001</v>
+        <v>-5.192773900000001</v>
       </c>
       <c r="P84">
-        <v>-15.2858118</v>
+        <v>-15.5783217</v>
       </c>
       <c r="Q84">
-        <v>-18.5558118</v>
+        <v>-18.8483217</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2777217547056977</v>
+        <v>0.2913642108648564</v>
       </c>
       <c r="T84">
-        <v>3.374744119031365</v>
+        <v>3.573258478974386</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09067860692544913</v>
+        <v>0.08958609358899794</v>
       </c>
       <c r="W84">
-        <v>0.2144179844869791</v>
+        <v>0.2146755991317143</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3627144277017966</v>
+        <v>0.3583443743559919</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2277126631263485</v>
+        <v>0.2296126631263484</v>
       </c>
       <c r="C85">
-        <v>-86.96814339293819</v>
+        <v>-89.0150778422028</v>
       </c>
       <c r="D85">
-        <v>38.01385660706183</v>
+        <v>37.6209221577972</v>
       </c>
       <c r="E85">
-        <v>110.182</v>
+        <v>111.836</v>
       </c>
       <c r="F85">
-        <v>137.282</v>
+        <v>138.936</v>
       </c>
       <c r="G85">
         <v>12.3</v>
@@ -8245,37 +8245,37 @@
         <v>11.6</v>
       </c>
       <c r="M85">
-        <v>32.3710956</v>
+        <v>32.7611088</v>
       </c>
       <c r="N85">
-        <v>-20.7710956</v>
+        <v>-21.1611088</v>
       </c>
       <c r="O85">
-        <v>-5.192773900000001</v>
+        <v>-5.2902772</v>
       </c>
       <c r="P85">
-        <v>-15.5783217</v>
+        <v>-15.8708316</v>
       </c>
       <c r="Q85">
-        <v>-18.8483217</v>
+        <v>-19.1408316</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2913642108648564</v>
+        <v>0.3067119740439099</v>
       </c>
       <c r="T85">
-        <v>3.573258478974386</v>
+        <v>3.796587133910287</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08958609358899794</v>
+        <v>0.08851959247484321</v>
       </c>
       <c r="W85">
-        <v>0.2146755991317143</v>
+        <v>0.214927080094432</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3583443743559919</v>
+        <v>0.3540783698993729</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2296126631263485</v>
+        <v>0.2315126631263484</v>
       </c>
       <c r="C86">
-        <v>-89.01507784220279</v>
+        <v>-91.05397217787439</v>
       </c>
       <c r="D86">
-        <v>37.62092215779722</v>
+        <v>37.23602782212562</v>
       </c>
       <c r="E86">
-        <v>111.836</v>
+        <v>113.49</v>
       </c>
       <c r="F86">
-        <v>138.936</v>
+        <v>140.59</v>
       </c>
       <c r="G86">
         <v>12.3</v>
@@ -8327,37 +8327,37 @@
         <v>11.6</v>
       </c>
       <c r="M86">
-        <v>32.7611088</v>
+        <v>33.151122</v>
       </c>
       <c r="N86">
-        <v>-21.1611088</v>
+        <v>-21.551122</v>
       </c>
       <c r="O86">
-        <v>-5.2902772</v>
+        <v>-5.3877805</v>
       </c>
       <c r="P86">
-        <v>-15.8708316</v>
+        <v>-16.1633415</v>
       </c>
       <c r="Q86">
-        <v>-19.1408316</v>
+        <v>-19.4333415</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3067119740439098</v>
+        <v>0.3241061056468371</v>
       </c>
       <c r="T86">
-        <v>3.796587133910284</v>
+        <v>4.049692942837637</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08851959247484321</v>
+        <v>0.08747818550455094</v>
       </c>
       <c r="W86">
-        <v>0.214927080094432</v>
+        <v>0.2151726438580269</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3540783698993729</v>
+        <v>0.3499127420182038</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2315126631263484</v>
+        <v>0.2334126631263485</v>
       </c>
       <c r="C87">
-        <v>-91.05397217787439</v>
+        <v>-93.08507067263</v>
       </c>
       <c r="D87">
-        <v>37.23602782212562</v>
+        <v>36.85892932737001</v>
       </c>
       <c r="E87">
-        <v>113.49</v>
+        <v>115.144</v>
       </c>
       <c r="F87">
-        <v>140.59</v>
+        <v>142.244</v>
       </c>
       <c r="G87">
         <v>12.3</v>
@@ -8409,37 +8409,37 @@
         <v>11.6</v>
       </c>
       <c r="M87">
-        <v>33.151122</v>
+        <v>33.5411352</v>
       </c>
       <c r="N87">
-        <v>-21.551122</v>
+        <v>-21.9411352</v>
       </c>
       <c r="O87">
-        <v>-5.3877805</v>
+        <v>-5.485283799999999</v>
       </c>
       <c r="P87">
-        <v>-16.1633415</v>
+        <v>-16.4558514</v>
       </c>
       <c r="Q87">
-        <v>-19.4333415</v>
+        <v>-19.7258514</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3241061056468371</v>
+        <v>0.3439851131930398</v>
       </c>
       <c r="T87">
-        <v>4.049692942837637</v>
+        <v>4.338956724468896</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08747818550455094</v>
+        <v>0.08646099730100966</v>
       </c>
       <c r="W87">
-        <v>0.2151726438580269</v>
+        <v>0.2154124968364219</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3499127420182038</v>
+        <v>0.3458439892040387</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2334126631263485</v>
+        <v>0.2353126631263484</v>
       </c>
       <c r="C88">
-        <v>-93.08507067263</v>
+        <v>-95.10860780311349</v>
       </c>
       <c r="D88">
-        <v>36.85892932737001</v>
+        <v>36.48939219688651</v>
       </c>
       <c r="E88">
-        <v>115.144</v>
+        <v>116.798</v>
       </c>
       <c r="F88">
-        <v>142.244</v>
+        <v>143.898</v>
       </c>
       <c r="G88">
         <v>12.3</v>
@@ -8491,37 +8491,37 @@
         <v>11.6</v>
       </c>
       <c r="M88">
-        <v>33.5411352</v>
+        <v>33.9311484</v>
       </c>
       <c r="N88">
-        <v>-21.9411352</v>
+        <v>-22.3311484</v>
       </c>
       <c r="O88">
-        <v>-5.485283799999999</v>
+        <v>-5.582787099999999</v>
       </c>
       <c r="P88">
-        <v>-16.4558514</v>
+        <v>-16.7483613</v>
       </c>
       <c r="Q88">
-        <v>-19.7258514</v>
+        <v>-20.0183613</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3439851131930398</v>
+        <v>0.3669224295925044</v>
       </c>
       <c r="T88">
-        <v>4.338956724468896</v>
+        <v>4.67272262635112</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08646099730100966</v>
+        <v>0.08546719273433138</v>
       </c>
       <c r="W88">
-        <v>0.2154124968364219</v>
+        <v>0.2156468359532447</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3458439892040387</v>
+        <v>0.3418687709373256</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2353126631263484</v>
+        <v>0.2372126631263484</v>
       </c>
       <c r="C89">
-        <v>-95.10860780311349</v>
+        <v>-97.1248087361224</v>
       </c>
       <c r="D89">
-        <v>36.48939219688651</v>
+        <v>36.12719126387758</v>
       </c>
       <c r="E89">
-        <v>116.798</v>
+        <v>118.452</v>
       </c>
       <c r="F89">
-        <v>143.898</v>
+        <v>145.552</v>
       </c>
       <c r="G89">
         <v>12.3</v>
@@ -8573,37 +8573,37 @@
         <v>11.6</v>
       </c>
       <c r="M89">
-        <v>33.9311484</v>
+        <v>34.3211616</v>
       </c>
       <c r="N89">
-        <v>-22.3311484</v>
+        <v>-22.72116159999999</v>
       </c>
       <c r="O89">
-        <v>-5.582787099999999</v>
+        <v>-5.680290399999999</v>
       </c>
       <c r="P89">
-        <v>-16.7483613</v>
+        <v>-17.0408712</v>
       </c>
       <c r="Q89">
-        <v>-20.0183613</v>
+        <v>-20.3108712</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3669224295925044</v>
+        <v>0.3936826320585465</v>
       </c>
       <c r="T89">
-        <v>4.67272262635112</v>
+        <v>5.062116178547047</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08546719273433138</v>
+        <v>0.08449597463507763</v>
       </c>
       <c r="W89">
-        <v>0.2156468359532447</v>
+        <v>0.2158758491810487</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3418687709373256</v>
+        <v>0.3379838985403105</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2372126631263484</v>
+        <v>0.2391126631263484</v>
       </c>
       <c r="C90">
-        <v>-97.1248087361224</v>
+        <v>-99.13388978612332</v>
       </c>
       <c r="D90">
-        <v>36.12719126387758</v>
+        <v>35.77211021387669</v>
       </c>
       <c r="E90">
-        <v>118.452</v>
+        <v>120.106</v>
       </c>
       <c r="F90">
-        <v>145.552</v>
+        <v>147.206</v>
       </c>
       <c r="G90">
         <v>12.3</v>
@@ -8655,37 +8655,37 @@
         <v>11.6</v>
       </c>
       <c r="M90">
-        <v>34.3211616</v>
+        <v>34.7111748</v>
       </c>
       <c r="N90">
-        <v>-22.72116159999999</v>
+        <v>-23.1111748</v>
       </c>
       <c r="O90">
-        <v>-5.680290399999999</v>
+        <v>-5.7777937</v>
       </c>
       <c r="P90">
-        <v>-17.0408712</v>
+        <v>-17.3333811</v>
       </c>
       <c r="Q90">
-        <v>-20.3108712</v>
+        <v>-20.6033811</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3936826320585465</v>
+        <v>0.4253083258820506</v>
       </c>
       <c r="T90">
-        <v>5.062116178547047</v>
+        <v>5.522308558414959</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08449597463507763</v>
+        <v>0.08354658166164977</v>
       </c>
       <c r="W90">
-        <v>0.2158758491810487</v>
+        <v>0.216099716044183</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3379838985403105</v>
+        <v>0.3341863266465992</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2391126631263484</v>
+        <v>0.2410126631263484</v>
       </c>
       <c r="C91">
-        <v>-99.13388978612332</v>
+        <v>-101.1360588460494</v>
       </c>
       <c r="D91">
-        <v>35.77211021387669</v>
+        <v>35.42394115395062</v>
       </c>
       <c r="E91">
-        <v>120.106</v>
+        <v>121.76</v>
       </c>
       <c r="F91">
-        <v>147.206</v>
+        <v>148.86</v>
       </c>
       <c r="G91">
         <v>12.3</v>
@@ -8737,37 +8737,37 @@
         <v>11.6</v>
       </c>
       <c r="M91">
-        <v>34.7111748</v>
+        <v>35.10118800000001</v>
       </c>
       <c r="N91">
-        <v>-23.1111748</v>
+        <v>-23.50118800000001</v>
       </c>
       <c r="O91">
-        <v>-5.7777937</v>
+        <v>-5.875297000000002</v>
       </c>
       <c r="P91">
-        <v>-17.3333811</v>
+        <v>-17.625891</v>
       </c>
       <c r="Q91">
-        <v>-20.6033811</v>
+        <v>-20.895891</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4253083258820506</v>
+        <v>0.4632591584702558</v>
       </c>
       <c r="T91">
-        <v>5.522308558414959</v>
+        <v>6.074539414256456</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08354658166164977</v>
+        <v>0.08261828630985366</v>
       </c>
       <c r="W91">
-        <v>0.216099716044183</v>
+        <v>0.2163186080881365</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3341863266465992</v>
+        <v>0.3304731452394146</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2410126631263484</v>
+        <v>0.2429126631263484</v>
       </c>
       <c r="C92">
-        <v>-101.1360588460494</v>
+        <v>-103.131515793183</v>
       </c>
       <c r="D92">
-        <v>35.42394115395062</v>
+        <v>35.08248420681701</v>
       </c>
       <c r="E92">
-        <v>121.76</v>
+        <v>123.414</v>
       </c>
       <c r="F92">
-        <v>148.86</v>
+        <v>150.514</v>
       </c>
       <c r="G92">
         <v>12.3</v>
@@ -8819,37 +8819,37 @@
         <v>11.6</v>
       </c>
       <c r="M92">
-        <v>35.10118800000001</v>
+        <v>35.49120120000001</v>
       </c>
       <c r="N92">
-        <v>-23.50118800000001</v>
+        <v>-23.8912012</v>
       </c>
       <c r="O92">
-        <v>-5.875297000000002</v>
+        <v>-5.972800300000001</v>
       </c>
       <c r="P92">
-        <v>-17.625891</v>
+        <v>-17.9184009</v>
       </c>
       <c r="Q92">
-        <v>-20.895891</v>
+        <v>-21.1884009</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4632591584702558</v>
+        <v>0.5096435094113954</v>
       </c>
       <c r="T92">
-        <v>6.074539414256456</v>
+        <v>6.74948823806273</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08261828630985366</v>
+        <v>0.08171039305370141</v>
       </c>
       <c r="W92">
-        <v>0.2163186080881365</v>
+        <v>0.2165326893179372</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3304731452394146</v>
+        <v>0.3268415722148057</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2429126631263484</v>
+        <v>0.2448126631263484</v>
       </c>
       <c r="C93">
-        <v>-103.131515793183</v>
+        <v>-105.1204528717881</v>
       </c>
       <c r="D93">
-        <v>35.08248420681701</v>
+        <v>34.74754712821193</v>
       </c>
       <c r="E93">
-        <v>123.414</v>
+        <v>125.068</v>
       </c>
       <c r="F93">
-        <v>150.514</v>
+        <v>152.168</v>
       </c>
       <c r="G93">
         <v>12.3</v>
@@ -8901,37 +8901,37 @@
         <v>11.6</v>
       </c>
       <c r="M93">
-        <v>35.49120120000001</v>
+        <v>35.8812144</v>
       </c>
       <c r="N93">
-        <v>-23.8912012</v>
+        <v>-24.2812144</v>
       </c>
       <c r="O93">
-        <v>-5.972800300000001</v>
+        <v>-6.070303600000001</v>
       </c>
       <c r="P93">
-        <v>-17.9184009</v>
+        <v>-18.2109108</v>
       </c>
       <c r="Q93">
-        <v>-21.1884009</v>
+        <v>-21.4809108</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5096435094113954</v>
+        <v>0.5676239480878198</v>
       </c>
       <c r="T93">
-        <v>6.74948823806273</v>
+        <v>7.593174267820573</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08171039305370141</v>
+        <v>0.08082223660746554</v>
       </c>
       <c r="W93">
-        <v>0.2165326893179372</v>
+        <v>0.2167421166079596</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3268415722148057</v>
+        <v>0.3232889464298622</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2448126631263484</v>
+        <v>0.2467126631263484</v>
       </c>
       <c r="C94">
-        <v>-105.1204528717881</v>
+        <v>-107.1030550540312</v>
       </c>
       <c r="D94">
-        <v>34.74754712821193</v>
+        <v>34.41894494596876</v>
       </c>
       <c r="E94">
-        <v>125.068</v>
+        <v>126.722</v>
       </c>
       <c r="F94">
-        <v>152.168</v>
+        <v>153.822</v>
       </c>
       <c r="G94">
         <v>12.3</v>
@@ -8983,37 +8983,37 @@
         <v>11.6</v>
       </c>
       <c r="M94">
-        <v>35.8812144</v>
+        <v>36.2712276</v>
       </c>
       <c r="N94">
-        <v>-24.2812144</v>
+        <v>-24.6712276</v>
       </c>
       <c r="O94">
-        <v>-6.070303600000001</v>
+        <v>-6.1678069</v>
       </c>
       <c r="P94">
-        <v>-18.2109108</v>
+        <v>-18.5034207</v>
       </c>
       <c r="Q94">
-        <v>-21.4809108</v>
+        <v>-21.7734207</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5676239480878198</v>
+        <v>0.6421702263860799</v>
       </c>
       <c r="T94">
-        <v>7.593174267820573</v>
+        <v>8.677913448937799</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08082223660746554</v>
+        <v>0.07995318029985839</v>
       </c>
       <c r="W94">
-        <v>0.2167421166079596</v>
+        <v>0.2169470400852934</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3232889464298622</v>
+        <v>0.3198127211994336</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2467126631263484</v>
+        <v>0.2486126631263484</v>
       </c>
       <c r="C95">
-        <v>-107.1030550540312</v>
+        <v>-109.0795003806162</v>
       </c>
       <c r="D95">
-        <v>34.41894494596876</v>
+        <v>34.09649961938381</v>
       </c>
       <c r="E95">
-        <v>126.722</v>
+        <v>128.376</v>
       </c>
       <c r="F95">
-        <v>153.822</v>
+        <v>155.476</v>
       </c>
       <c r="G95">
         <v>12.3</v>
@@ -9065,37 +9065,37 @@
         <v>11.6</v>
       </c>
       <c r="M95">
-        <v>36.2712276</v>
+        <v>36.66124080000001</v>
       </c>
       <c r="N95">
-        <v>-24.6712276</v>
+        <v>-25.06124080000001</v>
       </c>
       <c r="O95">
-        <v>-6.1678069</v>
+        <v>-6.265310200000002</v>
       </c>
       <c r="P95">
-        <v>-18.5034207</v>
+        <v>-18.79593060000001</v>
       </c>
       <c r="Q95">
-        <v>-21.7734207</v>
+        <v>-22.06593060000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6421702263860799</v>
+        <v>0.7415652641170933</v>
       </c>
       <c r="T95">
-        <v>8.677913448937799</v>
+        <v>10.1242323570941</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07995318029985839</v>
+        <v>0.07910261455198754</v>
       </c>
       <c r="W95">
-        <v>0.2169470400852934</v>
+        <v>0.2171476034886413</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3198127211994336</v>
+        <v>0.3164104582079502</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2486126631263484</v>
+        <v>0.2505126631263485</v>
       </c>
       <c r="C96">
-        <v>-109.0795003806162</v>
+        <v>-111.0499602824487</v>
       </c>
       <c r="D96">
-        <v>34.09649961938381</v>
+        <v>33.78003971755131</v>
       </c>
       <c r="E96">
-        <v>128.376</v>
+        <v>130.03</v>
       </c>
       <c r="F96">
-        <v>155.476</v>
+        <v>157.13</v>
       </c>
       <c r="G96">
         <v>12.3</v>
@@ -9147,37 +9147,37 @@
         <v>11.6</v>
       </c>
       <c r="M96">
-        <v>36.66124080000001</v>
+        <v>37.05125400000001</v>
       </c>
       <c r="N96">
-        <v>-25.06124080000001</v>
+        <v>-25.45125400000001</v>
       </c>
       <c r="O96">
-        <v>-6.265310200000002</v>
+        <v>-6.362813500000001</v>
       </c>
       <c r="P96">
-        <v>-18.79593060000001</v>
+        <v>-19.0884405</v>
       </c>
       <c r="Q96">
-        <v>-22.06593060000001</v>
+        <v>-22.3584405</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7415652641170933</v>
+        <v>0.8807183169405126</v>
       </c>
       <c r="T96">
-        <v>10.1242323570941</v>
+        <v>12.14907882851293</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07910261455198754</v>
+        <v>0.0782699554514403</v>
       </c>
       <c r="W96">
-        <v>0.2171476034886413</v>
+        <v>0.2173439445045504</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3164104582079502</v>
+        <v>0.3130798218057612</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2505126631263485</v>
+        <v>0.2524126631263485</v>
       </c>
       <c r="C97">
-        <v>-111.0499602824487</v>
+        <v>-113.0145998845533</v>
       </c>
       <c r="D97">
-        <v>33.78003971755131</v>
+        <v>33.46940011544669</v>
       </c>
       <c r="E97">
-        <v>130.03</v>
+        <v>131.684</v>
       </c>
       <c r="F97">
-        <v>157.13</v>
+        <v>158.784</v>
       </c>
       <c r="G97">
         <v>12.3</v>
@@ -9229,37 +9229,37 @@
         <v>11.6</v>
       </c>
       <c r="M97">
-        <v>37.05125400000001</v>
+        <v>37.44126720000001</v>
       </c>
       <c r="N97">
-        <v>-25.45125400000001</v>
+        <v>-25.8412672</v>
       </c>
       <c r="O97">
-        <v>-6.362813500000001</v>
+        <v>-6.460316800000001</v>
       </c>
       <c r="P97">
-        <v>-19.0884405</v>
+        <v>-19.3809504</v>
       </c>
       <c r="Q97">
-        <v>-22.3584405</v>
+        <v>-22.6509504</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8807183169405126</v>
+        <v>1.089447896175641</v>
       </c>
       <c r="T97">
-        <v>12.14907882851293</v>
+        <v>15.18634853564117</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0782699554514403</v>
+        <v>0.0774546434154878</v>
       </c>
       <c r="W97">
-        <v>0.2173439445045504</v>
+        <v>0.217536195082628</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3130798218057612</v>
+        <v>0.3098185736619513</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2524126631263484</v>
+        <v>0.2543126631263484</v>
       </c>
       <c r="C98">
-        <v>-113.0145998845533</v>
+        <v>-114.9735782933745</v>
       </c>
       <c r="D98">
-        <v>33.4694001154467</v>
+        <v>33.16442170662549</v>
       </c>
       <c r="E98">
-        <v>131.684</v>
+        <v>133.338</v>
       </c>
       <c r="F98">
-        <v>158.784</v>
+        <v>160.438</v>
       </c>
       <c r="G98">
         <v>12.3</v>
@@ -9311,37 +9311,37 @@
         <v>11.6</v>
       </c>
       <c r="M98">
-        <v>37.4412672</v>
+        <v>37.8312804</v>
       </c>
       <c r="N98">
-        <v>-25.8412672</v>
+        <v>-26.2312804</v>
       </c>
       <c r="O98">
-        <v>-6.460316799999999</v>
+        <v>-6.557820099999999</v>
       </c>
       <c r="P98">
-        <v>-19.3809504</v>
+        <v>-19.6734603</v>
       </c>
       <c r="Q98">
-        <v>-22.6509504</v>
+        <v>-22.94346029999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.089447896175638</v>
+        <v>1.437330528234184</v>
       </c>
       <c r="T98">
-        <v>15.18634853564112</v>
+        <v>20.24846471418817</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07745464341548781</v>
+        <v>0.07665614193697763</v>
       </c>
       <c r="W98">
-        <v>0.217536195082628</v>
+        <v>0.2177244817312607</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3098185736619513</v>
+        <v>0.3066245677479106</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2543126631263484</v>
+        <v>0.2562126631263484</v>
       </c>
       <c r="C99">
-        <v>-114.9735782933745</v>
+        <v>-116.9270488685117</v>
       </c>
       <c r="D99">
-        <v>33.16442170662549</v>
+        <v>32.86495113148832</v>
       </c>
       <c r="E99">
-        <v>133.338</v>
+        <v>134.992</v>
       </c>
       <c r="F99">
-        <v>160.438</v>
+        <v>162.092</v>
       </c>
       <c r="G99">
         <v>12.3</v>
@@ -9393,37 +9393,37 @@
         <v>11.6</v>
       </c>
       <c r="M99">
-        <v>37.8312804</v>
+        <v>38.2212936</v>
       </c>
       <c r="N99">
-        <v>-26.2312804</v>
+        <v>-26.6212936</v>
       </c>
       <c r="O99">
-        <v>-6.557820099999999</v>
+        <v>-6.6553234</v>
       </c>
       <c r="P99">
-        <v>-19.6734603</v>
+        <v>-19.9659702</v>
       </c>
       <c r="Q99">
-        <v>-22.94346029999999</v>
+        <v>-23.2359702</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.437330528234184</v>
+        <v>2.133095792351277</v>
       </c>
       <c r="T99">
-        <v>20.24846471418817</v>
+        <v>30.37269707128225</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07665614193697763</v>
+        <v>0.07587393640700847</v>
       </c>
       <c r="W99">
-        <v>0.2177244817312607</v>
+        <v>0.2179089257952274</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3066245677479106</v>
+        <v>0.3034957456280339</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2562126631263484</v>
+        <v>0.2581126631263484</v>
       </c>
       <c r="C100">
-        <v>-116.9270488685117</v>
+        <v>-118.8751594798635</v>
       </c>
       <c r="D100">
-        <v>32.86495113148832</v>
+        <v>32.57084052013648</v>
       </c>
       <c r="E100">
-        <v>134.992</v>
+        <v>136.646</v>
       </c>
       <c r="F100">
-        <v>162.092</v>
+        <v>163.746</v>
       </c>
       <c r="G100">
         <v>12.3</v>
@@ -9475,37 +9475,37 @@
         <v>11.6</v>
       </c>
       <c r="M100">
-        <v>38.2212936</v>
+        <v>38.6113068</v>
       </c>
       <c r="N100">
-        <v>-26.6212936</v>
+        <v>-27.0113068</v>
       </c>
       <c r="O100">
-        <v>-6.6553234</v>
+        <v>-6.7528267</v>
       </c>
       <c r="P100">
-        <v>-19.9659702</v>
+        <v>-20.2584801</v>
       </c>
       <c r="Q100">
-        <v>-23.2359702</v>
+        <v>-23.5284801</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.133095792351277</v>
+        <v>4.220391584702553</v>
       </c>
       <c r="T100">
-        <v>30.37269707128225</v>
+        <v>60.7453941425645</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07587393640700847</v>
+        <v>0.07510753300895788</v>
       </c>
       <c r="W100">
-        <v>0.2179089257952274</v>
+        <v>0.2180896437164877</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3034957456280339</v>
+        <v>0.3004301320358316</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2581126631263484</v>
-      </c>
-      <c r="C101">
-        <v>-118.8751594798635</v>
-      </c>
-      <c r="D101">
-        <v>32.57084052013648</v>
-      </c>
-      <c r="E101">
-        <v>136.646</v>
-      </c>
-      <c r="F101">
-        <v>163.746</v>
-      </c>
-      <c r="G101">
-        <v>12.3</v>
-      </c>
-      <c r="H101">
-        <v>138.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.33</v>
-      </c>
-      <c r="K101">
-        <v>-3.27</v>
-      </c>
-      <c r="L101">
-        <v>11.6</v>
-      </c>
-      <c r="M101">
-        <v>38.6113068</v>
-      </c>
-      <c r="N101">
-        <v>-27.0113068</v>
-      </c>
-      <c r="O101">
-        <v>-6.7528267</v>
-      </c>
-      <c r="P101">
-        <v>-20.2584801</v>
-      </c>
-      <c r="Q101">
-        <v>-23.5284801</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.220391584702553</v>
-      </c>
-      <c r="T101">
-        <v>60.7453941425645</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07510753300895788</v>
-      </c>
-      <c r="W101">
-        <v>0.2180896437164877</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3004301320358316</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
